--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72F8FD0-4CA3-4C6D-9DA7-37EE69A73521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803212F3-03E7-47AB-96E0-04DAC51B5281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2907,11 +2907,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ecd9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtal/images/RHEL_9.6_Base_Image/versions/0.0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ecd9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtal/images/Windows_Server_2025_Base_Image/versions/0.0.1</t>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtal/images/RHEL_9.6_Base_Image/versions/0.0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtal/images/Windows_Server_2025_Base_Image/versions/0.0.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3323,7 +3323,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3580,9 +3580,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3590,54 +3587,6 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="28">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3765,6 +3714,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -3810,6 +3760,53 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -4060,26 +4057,26 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="16"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="15"/>
     <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="2">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="13">
       <calculatedColumnFormula>표1[[#This Row],[Name]]&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="1">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="10">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-disk"&amp;"01"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="11"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="0">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="7">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="6"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="5"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="4"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="3"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4877,40 +4874,40 @@
       <c r="N2" s="56" t="s">
         <v>202</v>
       </c>
-      <c r="O2" s="86" t="s">
+      <c r="O2" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="P2" s="86" t="s">
+      <c r="P2" s="56" t="s">
         <v>216</v>
       </c>
-      <c r="Q2" s="86" t="s">
+      <c r="Q2" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="R2" s="86" t="s">
+      <c r="R2" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="S2" s="86" t="s">
+      <c r="S2" s="56" t="s">
         <v>219</v>
       </c>
-      <c r="T2" s="86" t="s">
+      <c r="T2" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="U2" s="86" t="s">
+      <c r="U2" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="V2" s="86" t="s">
+      <c r="V2" s="56" t="s">
         <v>222</v>
       </c>
-      <c r="W2" s="86" t="s">
+      <c r="W2" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="X2" s="86" t="s">
+      <c r="X2" s="56" t="s">
         <v>224</v>
       </c>
-      <c r="Y2" s="86" t="s">
+      <c r="Y2" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="Z2" s="86" t="s">
+      <c r="Z2" s="56" t="s">
         <v>226</v>
       </c>
       <c r="AA2" s="56"/>
@@ -5029,10 +5026,10 @@
       <c r="Z3" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="AA3" s="86" t="s">
+      <c r="AA3" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="AB3" s="86" t="s">
+      <c r="AB3" s="56" t="s">
         <v>262</v>
       </c>
       <c r="AC3" s="56" t="s">
@@ -5059,40 +5056,40 @@
       <c r="AJ3" s="56" t="s">
         <v>269</v>
       </c>
-      <c r="AK3" s="86" t="s">
+      <c r="AK3" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="AL3" s="86" t="s">
+      <c r="AL3" s="56" t="s">
         <v>292</v>
       </c>
-      <c r="AM3" s="86" t="s">
+      <c r="AM3" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="AN3" s="86" t="s">
+      <c r="AN3" s="56" t="s">
         <v>296</v>
       </c>
-      <c r="AO3" s="86" t="s">
+      <c r="AO3" s="56" t="s">
         <v>294</v>
       </c>
-      <c r="AP3" s="86" t="s">
+      <c r="AP3" s="56" t="s">
         <v>297</v>
       </c>
-      <c r="AQ3" s="86" t="s">
+      <c r="AQ3" s="56" t="s">
         <v>295</v>
       </c>
-      <c r="AR3" s="86" t="s">
+      <c r="AR3" s="56" t="s">
         <v>298</v>
       </c>
       <c r="AS3" s="52" t="s">
         <v>299</v>
       </c>
-      <c r="AT3" s="86" t="s">
+      <c r="AT3" s="56" t="s">
         <v>302</v>
       </c>
       <c r="AU3" s="52" t="s">
         <v>300</v>
       </c>
-      <c r="AV3" s="86" t="s">
+      <c r="AV3" s="56" t="s">
         <v>303</v>
       </c>
       <c r="AW3" s="52" t="s">
@@ -8151,21 +8148,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -8309,31 +8291,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8349,4 +8322,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803212F3-03E7-47AB-96E0-04DAC51B5281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD728A87-B00D-4D3B-B8F5-1B5574A2AFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RG" sheetId="5" r:id="rId1"/>
@@ -21,8 +21,9 @@
     <sheet name="LB_PRD" sheetId="6" r:id="rId6"/>
     <sheet name="LB_PRD_Probe" sheetId="10" r:id="rId7"/>
     <sheet name="LB_PRD_Rule" sheetId="11" r:id="rId8"/>
-    <sheet name="KV_PRD_Old" sheetId="8" r:id="rId9"/>
-    <sheet name="DES_PRD_Old" sheetId="12" r:id="rId10"/>
+    <sheet name="VM_DEV_Old" sheetId="13" r:id="rId9"/>
+    <sheet name="KV_PRD_Old" sheetId="8" r:id="rId10"/>
+    <sheet name="DES_PRD_Old" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1632,7 +1633,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="336">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3586,7 +3587,448 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="56">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4042,41 +4484,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Z3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A1:Z3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="26">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="49"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="48"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="47"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="42"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="41">
+      <calculatedColumnFormula>표1[[#This Row],[Name]]&amp;"-osdisk"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="37"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="36"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="35">
+      <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="33"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="32"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="31"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="30"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="29"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:Z5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="21"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="20"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="19"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="13">
-      <calculatedColumnFormula>표1[[#This Row],[Name]]&amp;"-osdisk"</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="21"/>
+    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="20"/>
+    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="19"/>
+    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="13">
+      <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="10">
+    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="10">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-disk"&amp;"01"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="7">
+    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="7">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="3"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="1"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="0"/>
+    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="3"/>
+    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4517,6 +4998,100 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75DC398-4852-44DE-9492-2B7CF2EB859C}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.75" customWidth="1"/>
+    <col min="13" max="13" width="62.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1" s="63" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="K1" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="L1" s="63" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L9" s="64"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F31AB6-04B6-41AA-A28C-C9A8D21D56C8}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5243,6 +5818,2646 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.25" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.875" customWidth="1"/>
+    <col min="11" max="11" width="16.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="155.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.125" customWidth="1"/>
+    <col min="24" max="24" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15" customWidth="1"/>
+    <col min="26" max="26" width="17" customWidth="1"/>
+    <col min="27" max="27" width="58.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="V1" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="M2" s="1" t="str">
+        <f>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-ap01-osdisk</v>
+      </c>
+      <c r="N2" s="1">
+        <v>64</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1" t="str">
+        <f t="shared" ref="S2:S3" si="0">SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-ap01-nic</v>
+      </c>
+      <c r="T2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="X2" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="M3" s="1" t="str">
+        <f>SUBSTITUTE(D3,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-adm01-osdisk</v>
+      </c>
+      <c r="N3" s="1">
+        <v>64</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>d-dis-adm01-nic</v>
+      </c>
+      <c r="T3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="X3" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5" customWidth="1"/>
+    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="4" t="str">
+        <f>IF(I2="O",H2&amp;"-NSG",G2&amp;"-NSG")</f>
+        <v>PRDWEB01-nic-NSG</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <f>IF(I3="O",H3&amp;"-NSG",G3&amp;"-NSG")</f>
+        <v>PRDWEB02-nic-NSG</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="4" t="str">
+        <f>IF(I4="O",A4&amp;H4&amp;"-NSG",A4&amp;G4&amp;"-NSG")</f>
+        <v>PRDWEBSubnet-NSG</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f>IF(I5="O",A5&amp;H5&amp;"-NSG",A5&amp;G5&amp;"-NSG")</f>
+        <v>STGWEBSubnet-NSG</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="4" t="str">
+        <f>IF(I6="O",A6&amp;H6&amp;"-NSG",A6&amp;G6&amp;"-NSG")</f>
+        <v>DEVAPPSubnet-NSG</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="53"/>
+      <c r="I6" s="54" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16413697-3740-4555-9E10-C39D5D5DCDBB}">
+  <dimension ref="A1:P36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.625" customWidth="1"/>
+    <col min="6" max="6" width="16.125" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" s="50" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="15">
+        <v>100</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="30">
+        <v>22</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="4">
+        <v>110</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" s="31">
+        <v>80</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="9">
+        <v>4095</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="9">
+        <v>4096</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="12">
+        <v>100</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="28"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="28"/>
+    </row>
+    <row r="9" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="22">
+        <v>4096</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="38"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="42"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="13">
+        <v>100</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="36">
+        <v>22</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="9">
+        <v>4095</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="9">
+        <v>4096</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="67"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="68"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="67"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="67"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="71" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="72">
+        <v>4096</v>
+      </c>
+      <c r="E18" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="72" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="K18" s="74" t="s">
+        <v>71</v>
+      </c>
+      <c r="L18" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="72" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="38"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="42"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="15">
+        <v>150</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="30">
+        <v>22</v>
+      </c>
+      <c r="M20" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="4">
+        <v>160</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" s="25"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="9">
+        <v>4095</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M22" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="9">
+        <v>4096</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="L23" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="67"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="76"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="77"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="77"/>
+    </row>
+    <row r="27" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="79" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" s="80">
+        <v>4096</v>
+      </c>
+      <c r="E27" s="80" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="81" t="s">
+        <v>62</v>
+      </c>
+      <c r="I27" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="J27" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="K27" s="82" t="s">
+        <v>71</v>
+      </c>
+      <c r="L27" s="82" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="83" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="42"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="13"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="13"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="4"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="9">
+        <v>4095</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I31" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="J31" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K31" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M31" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="9">
+        <v>4096</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="J32" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K32" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="12">
+        <v>200</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="J33" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="L33" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="M33" s="27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="11">
+        <v>4096</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="L36" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="J3 L6 L33 L21" numberStoredAsText="1"/>
+  </ignoredErrors>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.375" customWidth="1"/>
+    <col min="11" max="11" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" s="58" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="J1" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="L1" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="M1" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="N1" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="58" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>160</v>
+      </c>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="J2" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="M2" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="N2" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="O2" s="56" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="56">
+        <v>1</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="L3" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="M3" s="56" t="s">
+        <v>130</v>
+      </c>
+      <c r="N3" s="56" t="s">
+        <v>150</v>
+      </c>
+      <c r="O3" s="56" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E6DC6D-4CAC-4686-B15B-DE2A4B4502D8}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="59" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1" s="59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="56">
+        <v>80</v>
+      </c>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56">
+        <v>5</v>
+      </c>
+      <c r="H2" s="56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="56">
+        <v>8080</v>
+      </c>
+      <c r="F3" s="60"/>
+      <c r="G3" s="56">
+        <v>5</v>
+      </c>
+      <c r="H3" s="56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="56">
+        <v>443</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="G4" s="56">
+        <v>5</v>
+      </c>
+      <c r="H4" s="56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="56">
+        <v>80</v>
+      </c>
+      <c r="F5" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="56">
+        <v>5</v>
+      </c>
+      <c r="H5" s="56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="61">
+        <v>80</v>
+      </c>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61">
+        <v>5</v>
+      </c>
+      <c r="H6" s="61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="61">
+        <v>22</v>
+      </c>
+      <c r="F7" s="62"/>
+      <c r="G7" s="61">
+        <v>5</v>
+      </c>
+      <c r="H7" s="61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="61">
+        <v>443</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8" s="61">
+        <v>5</v>
+      </c>
+      <c r="H8" s="61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="61">
+        <v>80</v>
+      </c>
+      <c r="F9" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" s="61">
+        <v>5</v>
+      </c>
+      <c r="H9" s="61">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="59" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="59" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="L1" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="M1" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="N1" s="59" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="56">
+        <v>80</v>
+      </c>
+      <c r="G2" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="I2" s="56">
+        <v>80</v>
+      </c>
+      <c r="J2" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="K2" s="56">
+        <v>4</v>
+      </c>
+      <c r="L2" s="56" t="s">
+        <v>158</v>
+      </c>
+      <c r="M2" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="56">
+        <v>8080</v>
+      </c>
+      <c r="G3" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="56">
+        <v>8080</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="K3" s="56">
+        <v>4</v>
+      </c>
+      <c r="L3" s="56" t="s">
+        <v>158</v>
+      </c>
+      <c r="M3" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" s="56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="56">
+        <v>443</v>
+      </c>
+      <c r="G4" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="56">
+        <v>443</v>
+      </c>
+      <c r="J4" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="K4" s="56">
+        <v>4</v>
+      </c>
+      <c r="L4" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="M4" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" s="56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="56">
+        <v>22</v>
+      </c>
+      <c r="G5" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="I5" s="56">
+        <v>22</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" s="56">
+        <v>4</v>
+      </c>
+      <c r="L5" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="M5" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="N11" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{943262AD-45E3-45BA-806E-91D666EC9E20}">
   <dimension ref="A1:Z5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5680,2474 +8895,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.5" customWidth="1"/>
-    <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="H1" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="46" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" s="4" t="str">
-        <f>IF(I2="O",H2&amp;"-NSG",G2&amp;"-NSG")</f>
-        <v>PRDWEB01-nic-NSG</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" s="6" t="str">
-        <f>IF(I3="O",H3&amp;"-NSG",G3&amp;"-NSG")</f>
-        <v>PRDWEB02-nic-NSG</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="4" t="str">
-        <f>IF(I4="O",A4&amp;H4&amp;"-NSG",A4&amp;G4&amp;"-NSG")</f>
-        <v>PRDWEBSubnet-NSG</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="6" t="str">
-        <f>IF(I5="O",A5&amp;H5&amp;"-NSG",A5&amp;G5&amp;"-NSG")</f>
-        <v>STGWEBSubnet-NSG</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="4" t="str">
-        <f>IF(I6="O",A6&amp;H6&amp;"-NSG",A6&amp;G6&amp;"-NSG")</f>
-        <v>DEVAPPSubnet-NSG</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="54" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16413697-3740-4555-9E10-C39D5D5DCDBB}">
-  <dimension ref="A1:P36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.625" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
-    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="M1" s="50" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="15">
-        <v>100</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="30">
-        <v>22</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="4">
-        <v>110</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="L3" s="31">
-        <v>80</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="9">
-        <v>4095</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="9">
-        <v>4096</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="12">
-        <v>100</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="M6" s="27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="28"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="28"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="22">
-        <v>4096</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="38"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="42"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="13">
-        <v>100</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="K11" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="36">
-        <v>22</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" s="9">
-        <v>4095</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K13" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M13" s="26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" s="9">
-        <v>4096</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K14" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="L14" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="68"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="67"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="67"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="67" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="67"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="71" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="72">
-        <v>4096</v>
-      </c>
-      <c r="E18" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="71" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="72" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" s="73" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="J18" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="K18" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="L18" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18" s="72" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="38"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="42"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="15">
-        <v>150</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="K20" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="30">
-        <v>22</v>
-      </c>
-      <c r="M20" s="24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="4">
-        <v>160</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="J21" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="K21" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="L21" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="M21" s="25"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="9">
-        <v>4095</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="L22" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M22" s="26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" s="9">
-        <v>4096</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="J23" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K23" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="L23" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M23" s="26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="67" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="67" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="G24" s="67"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="69"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="76"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="67" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="67" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="77"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="67" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="67" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="77"/>
-    </row>
-    <row r="27" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="79" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="79" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="80">
-        <v>4096</v>
-      </c>
-      <c r="E27" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="G27" s="80" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="81" t="s">
-        <v>62</v>
-      </c>
-      <c r="I27" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="J27" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="K27" s="82" t="s">
-        <v>71</v>
-      </c>
-      <c r="L27" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="M27" s="83" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="42"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="13"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="4"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" s="9">
-        <v>4095</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I31" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="J31" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K31" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="L31" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="9">
-        <v>4096</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="J32" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="K32" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="L32" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="12">
-        <v>200</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I33" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="J33" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="K33" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="L33" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="M33" s="27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="6"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="6"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D36" s="11">
-        <v>4096</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="L36" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="M36" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="J3 L6 L33 L21" numberStoredAsText="1"/>
-  </ignoredErrors>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD1A3252-EF11-4361-BCDB-10417C7A0940}">
-  <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" customWidth="1"/>
-    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.375" customWidth="1"/>
-    <col min="11" max="11" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="F1" s="58" t="s">
-        <v>162</v>
-      </c>
-      <c r="G1" s="58" t="s">
-        <v>159</v>
-      </c>
-      <c r="H1" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="I1" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="J1" s="58" t="s">
-        <v>174</v>
-      </c>
-      <c r="K1" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="L1" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="M1" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="N1" s="59" t="s">
-        <v>131</v>
-      </c>
-      <c r="O1" s="58" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="K2" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="56" t="s">
-        <v>99</v>
-      </c>
-      <c r="M2" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="N2" s="56" t="s">
-        <v>132</v>
-      </c>
-      <c r="O2" s="56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="G3" s="56">
-        <v>1</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="I3" s="56" t="s">
-        <v>170</v>
-      </c>
-      <c r="J3" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>100</v>
-      </c>
-      <c r="M3" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="N3" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="O3" s="56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E6DC6D-4CAC-4686-B15B-DE2A4B4502D8}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="58" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="58" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="H1" s="59" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="56">
-        <v>80</v>
-      </c>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56">
-        <v>5</v>
-      </c>
-      <c r="H2" s="56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="56">
-        <v>8080</v>
-      </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="56">
-        <v>5</v>
-      </c>
-      <c r="H3" s="56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="56">
-        <v>443</v>
-      </c>
-      <c r="F4" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="G4" s="56">
-        <v>5</v>
-      </c>
-      <c r="H4" s="56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="56" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" s="56">
-        <v>80</v>
-      </c>
-      <c r="F5" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5" s="56">
-        <v>5</v>
-      </c>
-      <c r="H5" s="56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="61" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="61">
-        <v>80</v>
-      </c>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61">
-        <v>5</v>
-      </c>
-      <c r="H6" s="61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="61">
-        <v>22</v>
-      </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="61">
-        <v>5</v>
-      </c>
-      <c r="H7" s="61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" s="61" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="61">
-        <v>443</v>
-      </c>
-      <c r="F8" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="G8" s="61">
-        <v>5</v>
-      </c>
-      <c r="H8" s="61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="61">
-        <v>80</v>
-      </c>
-      <c r="F9" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="G9" s="61">
-        <v>5</v>
-      </c>
-      <c r="H9" s="61">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4BC862D-08E7-4593-9A34-4D2B508CF25B}">
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="E1" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="F1" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="G1" s="59" t="s">
-        <v>173</v>
-      </c>
-      <c r="H1" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1" s="59" t="s">
-        <v>154</v>
-      </c>
-      <c r="J1" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="K1" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L1" s="59" t="s">
-        <v>157</v>
-      </c>
-      <c r="M1" s="59" t="s">
-        <v>172</v>
-      </c>
-      <c r="N1" s="59" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="56">
-        <v>80</v>
-      </c>
-      <c r="G2" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" s="56" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" s="56">
-        <v>80</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="K2" s="56">
-        <v>4</v>
-      </c>
-      <c r="L2" s="56" t="s">
-        <v>158</v>
-      </c>
-      <c r="M2" s="56" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="56">
-        <v>8080</v>
-      </c>
-      <c r="G3" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="I3" s="56">
-        <v>8080</v>
-      </c>
-      <c r="J3" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="K3" s="56">
-        <v>4</v>
-      </c>
-      <c r="L3" s="56" t="s">
-        <v>158</v>
-      </c>
-      <c r="M3" s="56" t="b">
-        <v>1</v>
-      </c>
-      <c r="N3" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="56">
-        <v>443</v>
-      </c>
-      <c r="G4" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="I4" s="56">
-        <v>443</v>
-      </c>
-      <c r="J4" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="K4" s="56">
-        <v>4</v>
-      </c>
-      <c r="L4" s="56" t="s">
-        <v>167</v>
-      </c>
-      <c r="M4" s="56" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="56" t="s">
-        <v>166</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="56">
-        <v>22</v>
-      </c>
-      <c r="G5" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="I5" s="56">
-        <v>22</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>171</v>
-      </c>
-      <c r="K5" s="56">
-        <v>4</v>
-      </c>
-      <c r="L5" s="56" t="s">
-        <v>168</v>
-      </c>
-      <c r="M5" s="56" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="N11" s="1"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75DC398-4852-44DE-9492-2B7CF2EB859C}">
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.75" customWidth="1"/>
-    <col min="13" max="13" width="62.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="66" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="66" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="66" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1" s="66" t="s">
-        <v>106</v>
-      </c>
-      <c r="G1" s="63" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="I1" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="J1" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="K1" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="L1" s="63" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>186</v>
-      </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L9" s="64"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -8291,22 +9054,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8322,28 +9094,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD728A87-B00D-4D3B-B8F5-1B5574A2AFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48851643-8D11-4756-84A1-5A08E95A42B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1633,7 +1633,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="337">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2913,6 +2913,10 @@
   </si>
   <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtal/images/Windows_Server_2025_Base_Image/versions/0.0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/38befed7-7226-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/hazrddchgal/images/RHEL_9.6_Base_Image/versions/0.0.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4484,8 +4488,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Z3" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:Z3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Z2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A1:Z2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="53"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="52"/>
@@ -5818,7 +5822,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.25" customWidth="1"/>
@@ -5964,7 +5968,7 @@
         <v>25</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M2" s="1" t="str">
         <f>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</f>
@@ -5980,7 +5984,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1" t="str">
-        <f t="shared" ref="S2:S3" si="0">SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="S2" si="0">SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</f>
         <v>d-dis-ap01-nic</v>
       </c>
       <c r="T2" s="1" t="b">
@@ -6000,78 +6004,6 @@
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-      <c r="H3" s="1">
-        <v>8</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="M3" s="1" t="str">
-        <f>SUBSTITUTE(D3,"hazr-","")&amp;"-osdisk"</f>
-        <v>d-dis-adm01-osdisk</v>
-      </c>
-      <c r="N3" s="1">
-        <v>64</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>d-dis-adm01-nic</v>
-      </c>
-      <c r="T3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="X3" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48851643-8D11-4756-84A1-5A08E95A42B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76C4882-BA95-4CD0-A8CC-F9035255F262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1633,7 +1633,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="338">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2917,6 +2917,10 @@
   </si>
   <si>
     <t>/subscriptions/38befed7-7226-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/hazrddchgal/images/RHEL_9.6_Base_Image/versions/0.0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D2s_v5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5950,7 +5954,7 @@
         <v>325</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="G2" s="1">
         <v>2</v>
@@ -8828,21 +8832,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -8986,31 +8975,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9026,4 +9006,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76C4882-BA95-4CD0-A8CC-F9035255F262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE55722-A528-4AD0-B571-A6837EE1D585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RG" sheetId="5" r:id="rId1"/>
-    <sheet name="VNET" sheetId="4" r:id="rId2"/>
+    <sheet name="VNET" sheetId="4" r:id="rId1"/>
+    <sheet name="RG" sheetId="5" r:id="rId2"/>
     <sheet name="VM_DEV" sheetId="1" r:id="rId3"/>
     <sheet name="NSG_PRD" sheetId="2" r:id="rId4"/>
     <sheet name="NSG_PRD_Rule" sheetId="3" r:id="rId5"/>
@@ -1633,7 +1633,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="344">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2916,11 +2916,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/38befed7-7226-4784-910e-0cea5422077d/resourceGroups/hazr-d-dch-rg/providers/Microsoft.Compute/galleries/hazrddchgal/images/RHEL_9.6_Base_Image/versions/0.0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>D2s_v5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-ap01</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-int-vnet</t>
+  </si>
+  <si>
+    <t>d-dis-ap-sbn</t>
+  </si>
+  <si>
+    <t>10.156.144.10</t>
+  </si>
+  <si>
+    <t>Linux</t>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3332,7 +3350,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3591,11 +3609,446 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="56">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4052,432 +4505,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4492,80 +4519,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Z2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
-  <autoFilter ref="A1:Z2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Z71" totalsRowShown="0" headerRowDxfId="55" dataDxfId="0">
+  <autoFilter ref="A1:Z71" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="49"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="48"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="47"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="42"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="41">
-      <calculatedColumnFormula>표1[[#This Row],[Name]]&amp;"-osdisk"</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="21"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="20"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="14">
+      <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="39"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="38"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="37"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="36"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="35">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="11"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="10"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="8">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="33"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="32"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="31"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="30"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="29"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="5"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="2"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
   <autoFilter ref="A1:Z5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="21"/>
-    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="20"/>
-    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="19"/>
-    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="48"/>
+    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="47"/>
+    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="46"/>
+    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="40">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="10">
+    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="39"/>
+    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="38"/>
+    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="37">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-disk"&amp;"01"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="7">
+    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="36"/>
+    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="35"/>
+    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="34">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="3"/>
-    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="1"/>
-    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="0"/>
+    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="32"/>
+    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="31"/>
+    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="30"/>
+    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="29"/>
+    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="28"/>
+    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4867,304 +4894,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551C21F-24D7-4C3A-A8CD-5A629D1AA37B}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="55" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="56"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="D3" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="56"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>190</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="56"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="56" t="s">
-        <v>191</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="56"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="56"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="56" t="s">
-        <v>193</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="56"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="56" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="56" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="56"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75DC398-4852-44DE-9492-2B7CF2EB859C}">
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.75" customWidth="1"/>
-    <col min="13" max="13" width="62.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="66" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="66" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="66" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1" s="66" t="s">
-        <v>106</v>
-      </c>
-      <c r="G1" s="63" t="s">
-        <v>177</v>
-      </c>
-      <c r="H1" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="I1" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="J1" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="K1" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="L1" s="63" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>186</v>
-      </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L9" s="64"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F31AB6-04B6-41AA-A28C-C9A8D21D56C8}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.75" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="85" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="F1" s="85" t="s">
-        <v>105</v>
-      </c>
-      <c r="G1" s="51" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="52" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="52" t="s">
-        <v>185</v>
-      </c>
-      <c r="F2" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="52" t="s">
-        <v>186</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721B19D1-383B-4C42-B4E9-A7935F09393B}">
   <dimension ref="A1:BJ5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5824,17 +5553,315 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75DC398-4852-44DE-9492-2B7CF2EB859C}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.75" customWidth="1"/>
+    <col min="13" max="13" width="62.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1" s="63" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="K1" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="L1" s="63" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L9" s="64"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F31AB6-04B6-41AA-A28C-C9A8D21D56C8}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551C21F-24D7-4C3A-A8CD-5A629D1AA37B}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="56"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="56"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="56"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="56"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="56"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="56"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="56"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.25" customWidth="1"/>
     <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
@@ -5847,10 +5874,10 @@
     <col min="16" max="16" width="15.375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.625" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.125" customWidth="1"/>
+    <col min="22" max="22" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.75" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="13.5" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15" customWidth="1"/>
     <col min="26" max="26" width="17" customWidth="1"/>
@@ -5942,19 +5969,19 @@
         <v>82</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>337</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
+      </c>
+      <c r="F2" s="88" t="s">
+        <v>336</v>
       </c>
       <c r="G2" s="1">
         <v>2</v>
@@ -5969,10 +5996,10 @@
         <v>321</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="M2" s="1" t="str">
         <f>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</f>
@@ -5998,16 +6025,1879 @@
         <v>188</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>196</v>
+        <v>339</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>230</v>
+        <v>340</v>
       </c>
       <c r="X2" s="1">
         <v>1</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="86"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="86"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="86"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="86"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="86"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="86"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="86"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="86"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="86"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="86"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="86"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="86"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="86"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="86"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="86"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="86"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="86"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="86"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="86"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="86"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="87"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="86"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="86"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="86"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="86"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="86"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="86"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="86"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="86"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="86"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="86"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="86"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="86"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="86"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="86"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="86"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="86"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="88"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="86"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="86"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="87"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="86"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="86"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="86"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="86"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="87"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="86"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="86"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="86"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="86"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="87"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="86"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="88"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="86"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="86"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="88"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="87"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="86"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="86"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="86"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="88"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="87"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="86"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="86"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="88"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="86"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="86"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="87"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="86"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="86"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="86"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="86"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="87"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="86"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="86"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="86"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="86"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="87"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="86"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="86"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="88"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="86"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="86"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="87"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="86"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="86"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="88"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="86"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="86"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="88"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="87"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="86"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="86"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="86"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="86"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="88"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="87"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="86"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="86"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="88"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="86"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="86"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="87"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="86"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="86"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="88"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="86"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="86"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1"/>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="88"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="87"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="86"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="86"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="86"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="86"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="88"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="87"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="86"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+      <c r="S63" s="86"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1"/>
+      <c r="V63" s="1"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="88"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="86"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+      <c r="S64" s="86"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="87"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="86"/>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="86"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="88"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="86"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+      <c r="S66" s="86"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="88"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="87"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="86"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+      <c r="S67" s="86"/>
+      <c r="T67" s="1"/>
+      <c r="U67" s="1"/>
+      <c r="V67" s="1"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="86"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="86"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="88"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="87"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="86"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="86"/>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="88"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="86"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+      <c r="S70" s="86"/>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="87"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="86"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="86"/>
+      <c r="T71" s="1"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="1"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8832,6 +10722,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -8975,22 +10880,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9006,28 +10920,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE55722-A528-4AD0-B571-A6837EE1D585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEB6D1F-8CB8-40D7-8A5C-313ABA03A4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1632,8 +1632,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="502">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2940,6 +2962,481 @@
   <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-adm01</t>
+  </si>
+  <si>
+    <t>10.156.144.20</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-bbiweb01</t>
+  </si>
+  <si>
+    <t>10.156.128.10</t>
+  </si>
+  <si>
+    <t>D2s_v5</t>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_Base_Image/versions/0.0.2</t>
+  </si>
+  <si>
+    <t>hazr-d-dch-ext-vnet</t>
+  </si>
+  <si>
+    <t>d-dis-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-bbicltap01</t>
+  </si>
+  <si>
+    <t>10.156.144.30</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-bbimsgap01</t>
+  </si>
+  <si>
+    <t>10.156.144.40</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-walkap01</t>
+  </si>
+  <si>
+    <t>10.156.144.50</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-bat01</t>
+  </si>
+  <si>
+    <t>10.156.144.60</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-bat02</t>
+  </si>
+  <si>
+    <t>10.156.144.70</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-drvcltap01</t>
+  </si>
+  <si>
+    <t>10.156.144.80</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-walkweb01</t>
+  </si>
+  <si>
+    <t>10.156.128.20</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-drvmsgap01</t>
+  </si>
+  <si>
+    <t>10.156.144.90</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-web01</t>
+  </si>
+  <si>
+    <t>10.156.128.30</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-cmsadm01</t>
+  </si>
+  <si>
+    <t>10.156.144.100</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-cmsap01</t>
+  </si>
+  <si>
+    <t>10.156.144.110</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-cmsweb01</t>
+  </si>
+  <si>
+    <t>10.156.128.40</t>
+  </si>
+  <si>
+    <t>hazr-d-dis-cmbsap01</t>
+  </si>
+  <si>
+    <t>10.156.144.120</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-ingap01</t>
+  </si>
+  <si>
+    <t>10.156.153.10</t>
+  </si>
+  <si>
+    <t>d-dtg-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-ap01</t>
+  </si>
+  <si>
+    <t>10.156.153.20</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-extgeoap01</t>
+  </si>
+  <si>
+    <t>10.156.153.30</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-geoap01</t>
+  </si>
+  <si>
+    <t>10.156.153.40</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-mq01</t>
+  </si>
+  <si>
+    <t>10.156.131.10</t>
+  </si>
+  <si>
+    <t>d-dtg-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-admweb01</t>
+  </si>
+  <si>
+    <t>10.156.153.50</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-admap01</t>
+  </si>
+  <si>
+    <t>10.156.153.60</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-dtoms01</t>
+  </si>
+  <si>
+    <t>10.156.153.70</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-tsdb01</t>
+  </si>
+  <si>
+    <t>10.156.154.10</t>
+  </si>
+  <si>
+    <t>E4s_v5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d-dtg-db-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-web01</t>
+  </si>
+  <si>
+    <t>10.156.131.20</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-zkp01</t>
+  </si>
+  <si>
+    <t>10.156.153.81</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-zkp02</t>
+  </si>
+  <si>
+    <t>10.156.153.82</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-zkp03</t>
+  </si>
+  <si>
+    <t>10.156.153.83</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-kfk01</t>
+  </si>
+  <si>
+    <t>10.156.153.91</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-kfk02</t>
+  </si>
+  <si>
+    <t>10.156.153.92</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-kfk03</t>
+  </si>
+  <si>
+    <t>10.156.153.93</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-mdoms01</t>
+  </si>
+  <si>
+    <t>10.156.153.100</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-cdmlap01</t>
+  </si>
+  <si>
+    <t>10.156.153.110</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-cdstap01</t>
+  </si>
+  <si>
+    <t>10.156.153.120</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-cdsvap01</t>
+  </si>
+  <si>
+    <t>10.156.153.130</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-diosap01</t>
+  </si>
+  <si>
+    <t>10.156.153.140</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-diosweb01</t>
+  </si>
+  <si>
+    <t>10.156.153.150</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-dprweb01</t>
+  </si>
+  <si>
+    <t>10.156.131.30</t>
+  </si>
+  <si>
+    <t>hazr-d-dtg-dprap01</t>
+  </si>
+  <si>
+    <t>10.156.153.160</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-airfw01</t>
+  </si>
+  <si>
+    <t>10.156.156.10</t>
+  </si>
+  <si>
+    <t>d-bdp-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-kepler01</t>
+  </si>
+  <si>
+    <t>10.156.156.20</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-cxmap01</t>
+  </si>
+  <si>
+    <t>10.156.156.30</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-slap01</t>
+  </si>
+  <si>
+    <t>10.156.156.40</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-adm01</t>
+  </si>
+  <si>
+    <t>10.156.159.10</t>
+  </si>
+  <si>
+    <t>d-dip-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-ap01</t>
+  </si>
+  <si>
+    <t>10.156.159.20</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-flk01</t>
+  </si>
+  <si>
+    <t>10.156.159.31</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-flk02</t>
+  </si>
+  <si>
+    <t>10.156.159.32</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-flk03</t>
+  </si>
+  <si>
+    <t>10.156.159.33</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-geoap01</t>
+  </si>
+  <si>
+    <t>10.156.159.40</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-kfk01</t>
+  </si>
+  <si>
+    <t>10.156.159.51</t>
+  </si>
+  <si>
+    <t>10.156.159.52</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-kfk02</t>
+  </si>
+  <si>
+    <t>10.156.159.53</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-mqap01</t>
+  </si>
+  <si>
+    <t>10.156.159.60</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-mqweb01</t>
+  </si>
+  <si>
+    <t>10.156.159.70</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-oms01</t>
+  </si>
+  <si>
+    <t>10.156.159.80</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-web01</t>
+  </si>
+  <si>
+    <t>10.156.159.90</t>
+  </si>
+  <si>
+    <t>hazr-d-com-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-com-auth01</t>
+  </si>
+  <si>
+    <t>10.156.162.10</t>
+  </si>
+  <si>
+    <t>d-com-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-com-proxy01</t>
+  </si>
+  <si>
+    <t>10.156.134.10</t>
+  </si>
+  <si>
+    <t>d-com-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-if-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-if-gramon01</t>
+  </si>
+  <si>
+    <t>10.156.165.10</t>
+  </si>
+  <si>
+    <t>d-if-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-cs-chtap01</t>
+  </si>
+  <si>
+    <t>10.156.168.10</t>
+  </si>
+  <si>
+    <t>d-cs-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-cs-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-cs-chtweb01</t>
+  </si>
+  <si>
+    <t>10.156.136.10</t>
+  </si>
+  <si>
+    <t>d-cs-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-cs-chtintweb01</t>
+  </si>
+  <si>
+    <t>10.156.168.20</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-web01</t>
+  </si>
+  <si>
+    <t>10.156.150.10</t>
+  </si>
+  <si>
+    <t>d-doip-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-ap01</t>
+  </si>
+  <si>
+    <t>10.156.150.20</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-adm01</t>
+  </si>
+  <si>
+    <t>10.156.150.30</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkweb01</t>
+  </si>
+  <si>
+    <t>10.156.132.10</t>
+  </si>
+  <si>
+    <t>d-bdp-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkap01</t>
+  </si>
+  <si>
+    <t>10.156.156.50</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkml01</t>
+  </si>
+  <si>
+    <t>10.156.156.60</t>
   </si>
 </sst>
 </file>
@@ -3350,7 +3847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3609,9 +4106,6 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -3622,7 +4116,26 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
+  <dxfs count="57">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3972,6 +4485,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4519,80 +5033,83 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Z71" totalsRowShown="0" headerRowDxfId="55" dataDxfId="0">
-  <autoFilter ref="A1:Z71" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="22"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="21"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="20"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="14">
-      <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:AA70" totalsRowShown="0" headerRowDxfId="56" dataDxfId="1">
+  <autoFilter ref="A1:AA70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="27">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="0">
+      <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($C2, "-"), 3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="11"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="10"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="8">
-      <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="22"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="21"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="15">
+      <calculatedColumnFormula>SUBSTITUTE(E2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="13"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="12"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="11"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="9">
+      <calculatedColumnFormula>SUBSTITUTE(E2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="6"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="5"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="3"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:Z5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="48"/>
-    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="47"/>
-    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="46"/>
-    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="40">
+    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="49"/>
+    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="48"/>
+    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="47"/>
+    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="42"/>
+    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="41">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="39"/>
-    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="38"/>
-    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="37">
+    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="38">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-disk"&amp;"01"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="36"/>
-    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="35"/>
-    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="34">
+    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="37"/>
+    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="36"/>
+    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="35">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="33"/>
-    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="32"/>
-    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="31"/>
-    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="30"/>
-    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="29"/>
-    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="28"/>
-    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="27"/>
+    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="33"/>
+    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="32"/>
+    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="31"/>
+    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="30"/>
+    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="29"/>
+    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5853,2051 +6370,5364 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z71"/>
+  <dimension ref="A1:AA70"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.25" customWidth="1"/>
-    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.875" customWidth="1"/>
-    <col min="11" max="11" width="16.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="155.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15" customWidth="1"/>
-    <col min="26" max="26" width="17" customWidth="1"/>
-    <col min="27" max="27" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
+    <col min="12" max="12" width="16.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="155.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="21" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15" customWidth="1"/>
+    <col min="27" max="27" width="17" customWidth="1"/>
+    <col min="28" max="28" width="58.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="J1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="K1" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="L1" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="L1" s="43" t="s">
+      <c r="M1" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="43" t="s">
+      <c r="N1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="O1" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="43" t="s">
+      <c r="P1" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="43" t="s">
+      <c r="T1" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="43" t="s">
+      <c r="U1" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="43" t="s">
+      <c r="V1" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="V1" s="43" t="s">
+      <c r="W1" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="X1" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="43" t="s">
+      <c r="Y1" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>337</v>
+      <c r="B2" s="1" t="str" cm="1">
+        <f t="array" ref="B2">UPPER(INDEX(_xlfn.TEXTSPLIT($C2, "-"), 3))</f>
+        <v>DIS</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F2" s="88" t="s">
+      <c r="G2" s="87" t="s">
         <v>336</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>2</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="M2" s="1" t="str">
-        <f>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</f>
+      <c r="N2" s="1" t="str">
+        <f>SUBSTITUTE(E2,"hazr-","")&amp;"-osdisk"</f>
         <v>d-dis-ap01-osdisk</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>64</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
-      <c r="S2" s="1" t="str">
-        <f t="shared" ref="S2" si="0">SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</f>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1" t="str">
+        <f t="shared" ref="T2" si="0">SUBSTITUTE(E2,"hazr-","")&amp;"-nic"</f>
         <v>d-dis-ap01-nic</v>
       </c>
-      <c r="T2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="X2" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="1"/>
+      <c r="Y2" s="1">
+        <v>1</v>
+      </c>
       <c r="Z2" s="1"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="86"/>
+      <c r="AA2" s="1"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="1" t="str" cm="1">
+        <f t="array" ref="B3">UPPER(INDEX(_xlfn.TEXTSPLIT($C3, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1">
+        <v>8</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K3" s="86" t="s">
+        <v>321</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="N3" s="1" t="str">
+        <f>SUBSTITUTE(E3,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-adm01-osdisk</v>
+      </c>
+      <c r="O3" s="1">
+        <v>64</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1" t="str">
+        <f>SUBSTITUTE(E3,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-adm01-nic</v>
+      </c>
+      <c r="U3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>1</v>
+      </c>
       <c r="Z3" s="1"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="86"/>
+      <c r="AA3" s="1"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="1" t="str" cm="1">
+        <f t="array" ref="B4">UPPER(INDEX(_xlfn.TEXTSPLIT($C4, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G4" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2</v>
+      </c>
+      <c r="I4" s="1">
+        <v>8</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N4" s="1" t="str">
+        <f>SUBSTITUTE(E4,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-bbiweb01-osdisk</v>
+      </c>
+      <c r="O4" s="1">
+        <v>64</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="86"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1" t="str">
+        <f>SUBSTITUTE(E4,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-bbiweb01-nic</v>
+      </c>
+      <c r="U4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>1</v>
+      </c>
       <c r="Z4" s="1"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="86"/>
+      <c r="AA4" s="1"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="1" t="str" cm="1">
+        <f t="array" ref="B5">UPPER(INDEX(_xlfn.TEXTSPLIT($C5, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>8</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K5" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N5" s="1" t="str">
+        <f>SUBSTITUTE(E5,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-bbicltap01-osdisk</v>
+      </c>
+      <c r="O5" s="1">
+        <v>64</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-      <c r="S5" s="86"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1" t="str">
+        <f>SUBSTITUTE(E5,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-bbicltap01-nic</v>
+      </c>
+      <c r="U5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>1</v>
+      </c>
       <c r="Z5" s="1"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="86"/>
+      <c r="AA5" s="1"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="1" t="str" cm="1">
+        <f t="array" ref="B6">UPPER(INDEX(_xlfn.TEXTSPLIT($C6, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G6" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>8</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N6" s="1" t="str">
+        <f>SUBSTITUTE(E6,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-bbimsgap01-osdisk</v>
+      </c>
+      <c r="O6" s="1">
+        <v>64</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="86"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1" t="str">
+        <f>SUBSTITUTE(E6,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-bbimsgap01-nic</v>
+      </c>
+      <c r="U6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>1</v>
+      </c>
       <c r="Z6" s="1"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="86"/>
+      <c r="AA6" s="1"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="1" t="str" cm="1">
+        <f t="array" ref="B7">UPPER(INDEX(_xlfn.TEXTSPLIT($C7, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>8</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K7" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N7" s="1" t="str">
+        <f>SUBSTITUTE(E7,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-walkap01-osdisk</v>
+      </c>
+      <c r="O7" s="1">
+        <v>64</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="86"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1" t="str">
+        <f>SUBSTITUTE(E7,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-walkap01-nic</v>
+      </c>
+      <c r="U7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1</v>
+      </c>
       <c r="Z7" s="1"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="86"/>
+      <c r="AA7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="1" t="str" cm="1">
+        <f t="array" ref="B8">UPPER(INDEX(_xlfn.TEXTSPLIT($C8, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G8" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>8</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N8" s="1" t="str">
+        <f>SUBSTITUTE(E8,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-bat01-osdisk</v>
+      </c>
+      <c r="O8" s="1">
+        <v>64</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
-      <c r="S8" s="86"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1" t="str">
+        <f>SUBSTITUTE(E8,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-bat01-nic</v>
+      </c>
+      <c r="U8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>1</v>
+      </c>
       <c r="Z8" s="1"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="86"/>
+      <c r="AA8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="1" t="str" cm="1">
+        <f t="array" ref="B9">UPPER(INDEX(_xlfn.TEXTSPLIT($C9, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1">
+        <v>8</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K9" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N9" s="1" t="str">
+        <f>SUBSTITUTE(E9,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-bat02-osdisk</v>
+      </c>
+      <c r="O9" s="1">
+        <v>64</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
-      <c r="S9" s="86"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1" t="str">
+        <f>SUBSTITUTE(E9,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-bat02-nic</v>
+      </c>
+      <c r="U9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>1</v>
+      </c>
       <c r="Z9" s="1"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="86"/>
+      <c r="AA9" s="1"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="1" t="str" cm="1">
+        <f t="array" ref="B10">UPPER(INDEX(_xlfn.TEXTSPLIT($C10, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G10" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1">
+        <v>8</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N10" s="1" t="str">
+        <f>SUBSTITUTE(E10,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-drvcltap01-osdisk</v>
+      </c>
+      <c r="O10" s="1">
+        <v>64</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
-      <c r="S10" s="86"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1" t="str">
+        <f>SUBSTITUTE(E10,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-drvcltap01-nic</v>
+      </c>
+      <c r="U10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>1</v>
+      </c>
       <c r="Z10" s="1"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="87"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="86"/>
+      <c r="AA10" s="1"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="1" t="str" cm="1">
+        <f t="array" ref="B11">UPPER(INDEX(_xlfn.TEXTSPLIT($C11, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>8</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N11" s="1" t="str">
+        <f>SUBSTITUTE(E11,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-walkweb01-osdisk</v>
+      </c>
+      <c r="O11" s="1">
+        <v>64</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
-      <c r="S11" s="86"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1" t="str">
+        <f>SUBSTITUTE(E11,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-walkweb01-nic</v>
+      </c>
+      <c r="U11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>1</v>
+      </c>
       <c r="Z11" s="1"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="86"/>
+      <c r="AA11" s="1"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="1" t="str" cm="1">
+        <f t="array" ref="B12">UPPER(INDEX(_xlfn.TEXTSPLIT($C12, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G12" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1">
+        <v>8</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N12" s="1" t="str">
+        <f>SUBSTITUTE(E12,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-drvmsgap01-osdisk</v>
+      </c>
+      <c r="O12" s="1">
+        <v>64</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
-      <c r="S12" s="86"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1" t="str">
+        <f>SUBSTITUTE(E12,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-drvmsgap01-nic</v>
+      </c>
+      <c r="U12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>1</v>
+      </c>
       <c r="Z12" s="1"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="86"/>
+      <c r="AA12" s="1"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="1" t="str" cm="1">
+        <f t="array" ref="B13">UPPER(INDEX(_xlfn.TEXTSPLIT($C13, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1">
+        <v>8</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K13" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N13" s="1" t="str">
+        <f>SUBSTITUTE(E13,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-web01-osdisk</v>
+      </c>
+      <c r="O13" s="1">
+        <v>64</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="86"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1" t="str">
+        <f>SUBSTITUTE(E13,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-web01-nic</v>
+      </c>
+      <c r="U13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>1</v>
+      </c>
       <c r="Z13" s="1"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="86"/>
+      <c r="AA13" s="1"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="1" t="str" cm="1">
+        <f t="array" ref="B14">UPPER(INDEX(_xlfn.TEXTSPLIT($C14, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G14" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1">
+        <v>8</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N14" s="1" t="str">
+        <f>SUBSTITUTE(E14,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-cmsadm01-osdisk</v>
+      </c>
+      <c r="O14" s="1">
+        <v>64</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="86"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1" t="str">
+        <f>SUBSTITUTE(E14,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-cmsadm01-nic</v>
+      </c>
+      <c r="U14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>1</v>
+      </c>
       <c r="Z14" s="1"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="86"/>
+      <c r="AA14" s="1"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="1" t="str" cm="1">
+        <f t="array" ref="B15">UPPER(INDEX(_xlfn.TEXTSPLIT($C15, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1">
+        <v>8</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K15" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N15" s="1" t="str">
+        <f>SUBSTITUTE(E15,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-cmsap01-osdisk</v>
+      </c>
+      <c r="O15" s="1">
+        <v>64</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="86"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1" t="str">
+        <f>SUBSTITUTE(E15,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-cmsap01-nic</v>
+      </c>
+      <c r="U15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>1</v>
+      </c>
       <c r="Z15" s="1"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="86"/>
+      <c r="AA15" s="1"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="1" t="str" cm="1">
+        <f t="array" ref="B16">UPPER(INDEX(_xlfn.TEXTSPLIT($C16, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G16" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2</v>
+      </c>
+      <c r="I16" s="1">
+        <v>8</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N16" s="1" t="str">
+        <f>SUBSTITUTE(E16,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-cmsweb01-osdisk</v>
+      </c>
+      <c r="O16" s="1">
+        <v>64</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="86"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1" t="str">
+        <f>SUBSTITUTE(E16,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-cmsweb01-nic</v>
+      </c>
+      <c r="U16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>1</v>
+      </c>
       <c r="Z16" s="1"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="87"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="86"/>
+      <c r="AA16" s="1"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="1" t="str" cm="1">
+        <f t="array" ref="B17">UPPER(INDEX(_xlfn.TEXTSPLIT($C17, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1">
+        <v>8</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K17" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N17" s="1" t="str">
+        <f>SUBSTITUTE(E17,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dis-cmbsap01-osdisk</v>
+      </c>
+      <c r="O17" s="1">
+        <v>64</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="86"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1" t="str">
+        <f>SUBSTITUTE(E17,"hazr-","")&amp;"-nic"</f>
+        <v>d-dis-cmbsap01-nic</v>
+      </c>
+      <c r="U17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>1</v>
+      </c>
       <c r="Z17" s="1"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="86"/>
+      <c r="AA17" s="1"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="1" t="str" cm="1">
+        <f t="array" ref="B18">UPPER(INDEX(_xlfn.TEXTSPLIT($C18, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K18" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N18" s="1" t="str">
+        <f>SUBSTITUTE(E18,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-ingap01-osdisk</v>
+      </c>
+      <c r="O18" s="1">
+        <v>64</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1" t="str">
+        <f>SUBSTITUTE(E18,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-ingap01-nic</v>
+      </c>
+      <c r="U18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>1</v>
+      </c>
       <c r="Z18" s="1"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="86"/>
+      <c r="AA18" s="1"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="1" t="str" cm="1">
+        <f t="array" ref="B19">UPPER(INDEX(_xlfn.TEXTSPLIT($C19, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G19" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1">
+        <v>8</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N19" s="1" t="str">
+        <f>SUBSTITUTE(E19,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-ap01-osdisk</v>
+      </c>
+      <c r="O19" s="1">
+        <v>64</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
-      <c r="S19" s="86"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1" t="str">
+        <f>SUBSTITUTE(E19,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-ap01-nic</v>
+      </c>
+      <c r="U19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>1</v>
+      </c>
       <c r="Z19" s="1"/>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="86"/>
+      <c r="AA19" s="1"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="1" t="str" cm="1">
+        <f t="array" ref="B20">UPPER(INDEX(_xlfn.TEXTSPLIT($C20, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
+      </c>
+      <c r="I20" s="1">
+        <v>8</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K20" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N20" s="1" t="str">
+        <f>SUBSTITUTE(E20,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-extgeoap01-osdisk</v>
+      </c>
+      <c r="O20" s="1">
+        <v>64</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
-      <c r="S20" s="86"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1" t="str">
+        <f>SUBSTITUTE(E20,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-extgeoap01-nic</v>
+      </c>
+      <c r="U20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>1</v>
+      </c>
       <c r="Z20" s="1"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="87"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="86"/>
+      <c r="AA20" s="1"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="1" t="str" cm="1">
+        <f t="array" ref="B21">UPPER(INDEX(_xlfn.TEXTSPLIT($C21, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G21" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1">
+        <v>8</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N21" s="1" t="str">
+        <f>SUBSTITUTE(E21,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-geoap01-osdisk</v>
+      </c>
+      <c r="O21" s="1">
+        <v>64</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="86"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1" t="str">
+        <f>SUBSTITUTE(E21,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-geoap01-nic</v>
+      </c>
+      <c r="U21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>1</v>
+      </c>
       <c r="Z21" s="1"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="88"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="86"/>
+      <c r="AA21" s="1"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="1" t="str" cm="1">
+        <f t="array" ref="B22">UPPER(INDEX(_xlfn.TEXTSPLIT($C22, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1">
+        <v>8</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K22" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N22" s="1" t="str">
+        <f>SUBSTITUTE(E22,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-mq01-osdisk</v>
+      </c>
+      <c r="O22" s="1">
+        <v>64</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="86"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1" t="str">
+        <f>SUBSTITUTE(E22,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-mq01-nic</v>
+      </c>
+      <c r="U22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>1</v>
+      </c>
       <c r="Z22" s="1"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="87"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="86"/>
+      <c r="AA22" s="1"/>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="1" t="str" cm="1">
+        <f t="array" ref="B23">UPPER(INDEX(_xlfn.TEXTSPLIT($C23, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G23" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
+      <c r="I23" s="1">
+        <v>8</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N23" s="1" t="str">
+        <f>SUBSTITUTE(E23,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-admweb01-osdisk</v>
+      </c>
+      <c r="O23" s="1">
+        <v>64</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
-      <c r="S23" s="86"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1" t="str">
+        <f>SUBSTITUTE(E23,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-admweb01-nic</v>
+      </c>
+      <c r="U23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>1</v>
+      </c>
       <c r="Z23" s="1"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="86"/>
+      <c r="AA23" s="1"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="1" t="str" cm="1">
+        <f t="array" ref="B24">UPPER(INDEX(_xlfn.TEXTSPLIT($C24, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H24" s="1">
+        <v>2</v>
+      </c>
+      <c r="I24" s="1">
+        <v>8</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K24" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N24" s="1" t="str">
+        <f>SUBSTITUTE(E24,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-admap01-osdisk</v>
+      </c>
+      <c r="O24" s="1">
+        <v>64</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
-      <c r="S24" s="86"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1" t="str">
+        <f>SUBSTITUTE(E24,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-admap01-nic</v>
+      </c>
+      <c r="U24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>1</v>
+      </c>
       <c r="Z24" s="1"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="86"/>
+      <c r="AA24" s="1"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="1" t="str" cm="1">
+        <f t="array" ref="B25">UPPER(INDEX(_xlfn.TEXTSPLIT($C25, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="G25" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2</v>
+      </c>
+      <c r="I25" s="1">
+        <v>8</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N25" s="1" t="str">
+        <f>SUBSTITUTE(E25,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-dtoms01-osdisk</v>
+      </c>
+      <c r="O25" s="1">
+        <v>64</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
-      <c r="S25" s="86"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1" t="str">
+        <f>SUBSTITUTE(E25,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-dtoms01-nic</v>
+      </c>
+      <c r="U25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>1</v>
+      </c>
       <c r="Z25" s="1"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="86"/>
+      <c r="AA25" s="1"/>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1" t="str" cm="1">
+        <f t="array" ref="B26">UPPER(INDEX(_xlfn.TEXTSPLIT($C26, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="G26" s="87" t="s">
+        <v>399</v>
+      </c>
+      <c r="H26" s="1">
+        <v>4</v>
+      </c>
+      <c r="I26" s="1">
+        <v>32</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K26" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N26" s="1" t="str">
+        <f>SUBSTITUTE(E26,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-tsdb01-osdisk</v>
+      </c>
+      <c r="O26" s="1">
+        <v>64</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
-      <c r="S26" s="86"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1" t="str">
+        <f>SUBSTITUTE(E26,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-tsdb01-nic</v>
+      </c>
+      <c r="U26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>1</v>
+      </c>
       <c r="Z26" s="1"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="86"/>
+      <c r="AA26" s="1"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="1" t="str" cm="1">
+        <f t="array" ref="B27">UPPER(INDEX(_xlfn.TEXTSPLIT($C27, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F27" s="87" t="s">
+        <v>402</v>
+      </c>
+      <c r="G27" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H27" s="1">
+        <v>2</v>
+      </c>
+      <c r="I27" s="1">
+        <v>8</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N27" s="1" t="str">
+        <f>SUBSTITUTE(E27,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-web01-osdisk</v>
+      </c>
+      <c r="O27" s="1">
+        <v>64</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
-      <c r="S27" s="86"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1" t="str">
+        <f>SUBSTITUTE(E27,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-web01-nic</v>
+      </c>
+      <c r="U27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>1</v>
+      </c>
       <c r="Z27" s="1"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="86"/>
+      <c r="AA27" s="1"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="1" t="str" cm="1">
+        <f t="array" ref="B28">UPPER(INDEX(_xlfn.TEXTSPLIT($C28, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H28" s="1">
+        <v>2</v>
+      </c>
+      <c r="I28" s="1">
+        <v>8</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K28" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N28" s="1" t="str">
+        <f>SUBSTITUTE(E28,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-zkp01-osdisk</v>
+      </c>
+      <c r="O28" s="1">
+        <v>64</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
-      <c r="S28" s="86"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1" t="str">
+        <f>SUBSTITUTE(E28,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-zkp01-nic</v>
+      </c>
+      <c r="U28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>1</v>
+      </c>
       <c r="Z28" s="1"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="86"/>
+      <c r="AA28" s="1"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="1" t="str" cm="1">
+        <f t="array" ref="B29">UPPER(INDEX(_xlfn.TEXTSPLIT($C29, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="G29" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1">
+        <v>8</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N29" s="1" t="str">
+        <f>SUBSTITUTE(E29,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-zkp02-osdisk</v>
+      </c>
+      <c r="O29" s="1">
+        <v>64</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
-      <c r="S29" s="86"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1" t="str">
+        <f>SUBSTITUTE(E29,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-zkp02-nic</v>
+      </c>
+      <c r="U29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>1</v>
+      </c>
       <c r="Z29" s="1"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="86"/>
+      <c r="AA29" s="1"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="1" t="str" cm="1">
+        <f t="array" ref="B30">UPPER(INDEX(_xlfn.TEXTSPLIT($C30, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="G30" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>8</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K30" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N30" s="1" t="str">
+        <f>SUBSTITUTE(E30,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-zkp03-osdisk</v>
+      </c>
+      <c r="O30" s="1">
+        <v>64</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
-      <c r="S30" s="86"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1" t="str">
+        <f>SUBSTITUTE(E30,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-zkp03-nic</v>
+      </c>
+      <c r="U30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>1</v>
+      </c>
       <c r="Z30" s="1"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="86"/>
+      <c r="AA30" s="1"/>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="1" t="str" cm="1">
+        <f t="array" ref="B31">UPPER(INDEX(_xlfn.TEXTSPLIT($C31, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1">
+        <v>8</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N31" s="1" t="str">
+        <f>SUBSTITUTE(E31,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-kfk01-osdisk</v>
+      </c>
+      <c r="O31" s="1">
+        <v>64</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
-      <c r="S31" s="86"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1" t="str">
+        <f>SUBSTITUTE(E31,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-kfk01-nic</v>
+      </c>
+      <c r="U31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y31" s="1">
+        <v>1</v>
+      </c>
       <c r="Z31" s="1"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="86"/>
+      <c r="AA31" s="1"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="1" t="str" cm="1">
+        <f t="array" ref="B32">UPPER(INDEX(_xlfn.TEXTSPLIT($C32, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="G32" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H32" s="1">
+        <v>2</v>
+      </c>
+      <c r="I32" s="1">
+        <v>8</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K32" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N32" s="1" t="str">
+        <f>SUBSTITUTE(E32,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-kfk02-osdisk</v>
+      </c>
+      <c r="O32" s="1">
+        <v>64</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
-      <c r="S32" s="86"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1" t="str">
+        <f>SUBSTITUTE(E32,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-kfk02-nic</v>
+      </c>
+      <c r="U32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y32" s="1">
+        <v>1</v>
+      </c>
       <c r="Z32" s="1"/>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="86"/>
+      <c r="AA32" s="1"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="1" t="str" cm="1">
+        <f t="array" ref="B33">UPPER(INDEX(_xlfn.TEXTSPLIT($C33, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G33" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>8</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N33" s="1" t="str">
+        <f>SUBSTITUTE(E33,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-kfk03-osdisk</v>
+      </c>
+      <c r="O33" s="1">
+        <v>64</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
-      <c r="S33" s="86"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1" t="str">
+        <f>SUBSTITUTE(E33,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-kfk03-nic</v>
+      </c>
+      <c r="U33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y33" s="1">
+        <v>1</v>
+      </c>
       <c r="Z33" s="1"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="86"/>
+      <c r="AA33" s="1"/>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="str" cm="1">
+        <f t="array" ref="B34">UPPER(INDEX(_xlfn.TEXTSPLIT($C34, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H34" s="1">
+        <v>2</v>
+      </c>
+      <c r="I34" s="1">
+        <v>8</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K34" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N34" s="1" t="str">
+        <f>SUBSTITUTE(E34,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-mdoms01-osdisk</v>
+      </c>
+      <c r="O34" s="1">
+        <v>64</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
-      <c r="S34" s="86"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1" t="str">
+        <f>SUBSTITUTE(E34,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-mdoms01-nic</v>
+      </c>
+      <c r="U34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>1</v>
+      </c>
       <c r="Z34" s="1"/>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="87"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="86"/>
+      <c r="AA34" s="1"/>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="1" t="str" cm="1">
+        <f t="array" ref="B35">UPPER(INDEX(_xlfn.TEXTSPLIT($C35, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G35" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H35" s="1">
+        <v>2</v>
+      </c>
+      <c r="I35" s="1">
+        <v>8</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N35" s="1" t="str">
+        <f>SUBSTITUTE(E35,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-cdmlap01-osdisk</v>
+      </c>
+      <c r="O35" s="1">
+        <v>64</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
-      <c r="S35" s="86"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1" t="str">
+        <f>SUBSTITUTE(E35,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-cdmlap01-nic</v>
+      </c>
+      <c r="U35" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>1</v>
+      </c>
       <c r="Z35" s="1"/>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="88"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="86"/>
+      <c r="AA35" s="1"/>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="1" t="str" cm="1">
+        <f t="array" ref="B36">UPPER(INDEX(_xlfn.TEXTSPLIT($C36, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="G36" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2</v>
+      </c>
+      <c r="I36" s="1">
+        <v>8</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K36" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N36" s="1" t="str">
+        <f>SUBSTITUTE(E36,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-cdstap01-osdisk</v>
+      </c>
+      <c r="O36" s="1">
+        <v>64</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
-      <c r="S36" s="86"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1" t="str">
+        <f>SUBSTITUTE(E36,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-cdstap01-nic</v>
+      </c>
+      <c r="U36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y36" s="1">
+        <v>1</v>
+      </c>
       <c r="Z36" s="1"/>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="87"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="86"/>
+      <c r="AA36" s="1"/>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="1" t="str" cm="1">
+        <f t="array" ref="B37">UPPER(INDEX(_xlfn.TEXTSPLIT($C37, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2</v>
+      </c>
+      <c r="I37" s="1">
+        <v>8</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N37" s="1" t="str">
+        <f>SUBSTITUTE(E37,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-cdsvap01-osdisk</v>
+      </c>
+      <c r="O37" s="1">
+        <v>64</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
-      <c r="S37" s="86"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1" t="str">
+        <f>SUBSTITUTE(E37,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-cdsvap01-nic</v>
+      </c>
+      <c r="U37" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y37" s="1">
+        <v>1</v>
+      </c>
       <c r="Z37" s="1"/>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="86"/>
+      <c r="AA37" s="1"/>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="1" t="str" cm="1">
+        <f t="array" ref="B38">UPPER(INDEX(_xlfn.TEXTSPLIT($C38, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="G38" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2</v>
+      </c>
+      <c r="I38" s="1">
+        <v>8</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K38" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N38" s="1" t="str">
+        <f>SUBSTITUTE(E38,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-diosap01-osdisk</v>
+      </c>
+      <c r="O38" s="1">
+        <v>64</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
-      <c r="S38" s="86"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1" t="str">
+        <f>SUBSTITUTE(E38,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-diosap01-nic</v>
+      </c>
+      <c r="U38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>1</v>
+      </c>
       <c r="Z38" s="1"/>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="87"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="86"/>
+      <c r="AA38" s="1"/>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="1" t="str" cm="1">
+        <f t="array" ref="B39">UPPER(INDEX(_xlfn.TEXTSPLIT($C39, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G39" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2</v>
+      </c>
+      <c r="I39" s="1">
+        <v>8</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N39" s="1" t="str">
+        <f>SUBSTITUTE(E39,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-diosweb01-osdisk</v>
+      </c>
+      <c r="O39" s="1">
+        <v>64</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
-      <c r="S39" s="86"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1" t="str">
+        <f>SUBSTITUTE(E39,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-diosweb01-nic</v>
+      </c>
+      <c r="U39" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>1</v>
+      </c>
       <c r="Z39" s="1"/>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="86"/>
+      <c r="AA39" s="1"/>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="1" t="str" cm="1">
+        <f t="array" ref="B40">UPPER(INDEX(_xlfn.TEXTSPLIT($C40, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2</v>
+      </c>
+      <c r="I40" s="1">
+        <v>8</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K40" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N40" s="1" t="str">
+        <f>SUBSTITUTE(E40,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-dprweb01-osdisk</v>
+      </c>
+      <c r="O40" s="1">
+        <v>64</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
-      <c r="S40" s="86"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1" t="str">
+        <f>SUBSTITUTE(E40,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-dprweb01-nic</v>
+      </c>
+      <c r="U40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>1</v>
+      </c>
       <c r="Z40" s="1"/>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="86"/>
+      <c r="AA40" s="1"/>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="1" t="str" cm="1">
+        <f t="array" ref="B41">UPPER(INDEX(_xlfn.TEXTSPLIT($C41, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G41" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H41" s="1">
+        <v>2</v>
+      </c>
+      <c r="I41" s="1">
+        <v>8</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N41" s="1" t="str">
+        <f>SUBSTITUTE(E41,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dtg-dprap01-osdisk</v>
+      </c>
+      <c r="O41" s="1">
+        <v>64</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
-      <c r="S41" s="86"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1" t="str">
+        <f>SUBSTITUTE(E41,"hazr-","")&amp;"-nic"</f>
+        <v>d-dtg-dprap01-nic</v>
+      </c>
+      <c r="U41" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>1</v>
+      </c>
       <c r="Z41" s="1"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="88"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="86"/>
+      <c r="AA41" s="1"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="1" t="str" cm="1">
+        <f t="array" ref="B42">UPPER(INDEX(_xlfn.TEXTSPLIT($C42, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G42" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2</v>
+      </c>
+      <c r="I42" s="1">
+        <v>8</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K42" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N42" s="1" t="str">
+        <f>SUBSTITUTE(E42,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-bdp-airfw01-osdisk</v>
+      </c>
+      <c r="O42" s="1">
+        <v>64</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
-      <c r="S42" s="86"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1" t="str">
+        <f>SUBSTITUTE(E42,"hazr-","")&amp;"-nic"</f>
+        <v>d-bdp-airfw01-nic</v>
+      </c>
+      <c r="U42" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>1</v>
+      </c>
       <c r="Z42" s="1"/>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="88"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="87"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="86"/>
+      <c r="AA42" s="1"/>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="1" t="str" cm="1">
+        <f t="array" ref="B43">UPPER(INDEX(_xlfn.TEXTSPLIT($C43, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H43" s="1">
+        <v>2</v>
+      </c>
+      <c r="I43" s="1">
+        <v>8</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N43" s="1" t="str">
+        <f>SUBSTITUTE(E43,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-bdp-kepler01-osdisk</v>
+      </c>
+      <c r="O43" s="1">
+        <v>64</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
-      <c r="S43" s="86"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1" t="str">
+        <f>SUBSTITUTE(E43,"hazr-","")&amp;"-nic"</f>
+        <v>d-bdp-kepler01-nic</v>
+      </c>
+      <c r="U43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>1</v>
+      </c>
       <c r="Z43" s="1"/>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="86"/>
+      <c r="AA43" s="1"/>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="1" t="str" cm="1">
+        <f t="array" ref="B44">UPPER(INDEX(_xlfn.TEXTSPLIT($C44, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G44" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2</v>
+      </c>
+      <c r="I44" s="1">
+        <v>8</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K44" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N44" s="1" t="str">
+        <f>SUBSTITUTE(E44,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-bdp-cxmap01-osdisk</v>
+      </c>
+      <c r="O44" s="1">
+        <v>64</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
-      <c r="S44" s="86"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1" t="str">
+        <f>SUBSTITUTE(E44,"hazr-","")&amp;"-nic"</f>
+        <v>d-bdp-cxmap01-nic</v>
+      </c>
+      <c r="U44" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>1</v>
+      </c>
       <c r="Z44" s="1"/>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="88"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="87"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="86"/>
+      <c r="AA44" s="1"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="1" t="str" cm="1">
+        <f t="array" ref="B45">UPPER(INDEX(_xlfn.TEXTSPLIT($C45, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G45" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2</v>
+      </c>
+      <c r="I45" s="1">
+        <v>8</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N45" s="1" t="str">
+        <f>SUBSTITUTE(E45,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-bdp-slap01-osdisk</v>
+      </c>
+      <c r="O45" s="1">
+        <v>64</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="86"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1" t="str">
+        <f>SUBSTITUTE(E45,"hazr-","")&amp;"-nic"</f>
+        <v>d-bdp-slap01-nic</v>
+      </c>
+      <c r="U45" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X45" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>1</v>
+      </c>
       <c r="Z45" s="1"/>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="88"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="86"/>
+      <c r="AA45" s="1"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" s="1" t="str" cm="1">
+        <f t="array" ref="B46">UPPER(INDEX(_xlfn.TEXTSPLIT($C46, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H46" s="1">
+        <v>2</v>
+      </c>
+      <c r="I46" s="1">
+        <v>8</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K46" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N46" s="1" t="str">
+        <f>SUBSTITUTE(E46,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-adm01-osdisk</v>
+      </c>
+      <c r="O46" s="1">
+        <v>64</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
-      <c r="S46" s="86"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1" t="str">
+        <f>SUBSTITUTE(E46,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-adm01-nic</v>
+      </c>
+      <c r="U46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>1</v>
+      </c>
       <c r="Z46" s="1"/>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="87"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="86"/>
+      <c r="AA46" s="1"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="1" t="str" cm="1">
+        <f t="array" ref="B47">UPPER(INDEX(_xlfn.TEXTSPLIT($C47, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G47" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2</v>
+      </c>
+      <c r="I47" s="1">
+        <v>8</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N47" s="1" t="str">
+        <f>SUBSTITUTE(E47,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-ap01-osdisk</v>
+      </c>
+      <c r="O47" s="1">
+        <v>64</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
-      <c r="S47" s="86"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1"/>
-      <c r="W47" s="1"/>
-      <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1" t="str">
+        <f>SUBSTITUTE(E47,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-ap01-nic</v>
+      </c>
+      <c r="U47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X47" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y47" s="1">
+        <v>1</v>
+      </c>
       <c r="Z47" s="1"/>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="86"/>
+      <c r="AA47" s="1"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" s="1" t="str" cm="1">
+        <f t="array" ref="B48">UPPER(INDEX(_xlfn.TEXTSPLIT($C48, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="G48" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="1">
+        <v>8</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K48" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N48" s="1" t="str">
+        <f>SUBSTITUTE(E48,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-flk01-osdisk</v>
+      </c>
+      <c r="O48" s="1">
+        <v>64</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
-      <c r="S48" s="86"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1"/>
-      <c r="W48" s="1"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1" t="str">
+        <f>SUBSTITUTE(E48,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-flk01-nic</v>
+      </c>
+      <c r="U48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V48" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W48" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X48" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>1</v>
+      </c>
       <c r="Z48" s="1"/>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="88"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="87"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="86"/>
+      <c r="AA48" s="1"/>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="1" t="str" cm="1">
+        <f t="array" ref="B49">UPPER(INDEX(_xlfn.TEXTSPLIT($C49, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1">
+        <v>8</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N49" s="1" t="str">
+        <f>SUBSTITUTE(E49,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-flk02-osdisk</v>
+      </c>
+      <c r="O49" s="1">
+        <v>64</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
-      <c r="S49" s="86"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1"/>
-      <c r="W49" s="1"/>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1" t="str">
+        <f>SUBSTITUTE(E49,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-flk02-nic</v>
+      </c>
+      <c r="U49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W49" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X49" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y49" s="1">
+        <v>1</v>
+      </c>
       <c r="Z49" s="1"/>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="86"/>
+      <c r="AA49" s="1"/>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B50" s="1" t="str" cm="1">
+        <f t="array" ref="B50">UPPER(INDEX(_xlfn.TEXTSPLIT($C50, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G50" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2</v>
+      </c>
+      <c r="I50" s="1">
+        <v>8</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K50" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N50" s="1" t="str">
+        <f>SUBSTITUTE(E50,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-flk03-osdisk</v>
+      </c>
+      <c r="O50" s="1">
+        <v>64</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
-      <c r="S50" s="86"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1"/>
-      <c r="W50" s="1"/>
-      <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1" t="str">
+        <f>SUBSTITUTE(E50,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-flk03-nic</v>
+      </c>
+      <c r="U50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W50" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X50" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y50" s="1">
+        <v>1</v>
+      </c>
       <c r="Z50" s="1"/>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="88"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="87"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="86"/>
+      <c r="AA50" s="1"/>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="1" t="str" cm="1">
+        <f t="array" ref="B51">UPPER(INDEX(_xlfn.TEXTSPLIT($C51, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="G51" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2</v>
+      </c>
+      <c r="I51" s="1">
+        <v>8</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N51" s="1" t="str">
+        <f>SUBSTITUTE(E51,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-geoap01-osdisk</v>
+      </c>
+      <c r="O51" s="1">
+        <v>64</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
-      <c r="S51" s="86"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1"/>
-      <c r="W51" s="1"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1" t="str">
+        <f>SUBSTITUTE(E51,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-geoap01-nic</v>
+      </c>
+      <c r="U51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X51" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y51" s="1">
+        <v>1</v>
+      </c>
       <c r="Z51" s="1"/>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="86"/>
+      <c r="AA51" s="1"/>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="1" t="str" cm="1">
+        <f t="array" ref="B52">UPPER(INDEX(_xlfn.TEXTSPLIT($C52, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H52" s="1">
+        <v>2</v>
+      </c>
+      <c r="I52" s="1">
+        <v>8</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K52" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N52" s="1" t="str">
+        <f>SUBSTITUTE(E52,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-kfk01-osdisk</v>
+      </c>
+      <c r="O52" s="1">
+        <v>64</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
-      <c r="S52" s="86"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1"/>
-      <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1" t="str">
+        <f>SUBSTITUTE(E52,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-kfk01-nic</v>
+      </c>
+      <c r="U52" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V52" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W52" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y52" s="1">
+        <v>1</v>
+      </c>
       <c r="Z52" s="1"/>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="87"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="86"/>
+      <c r="AA52" s="1"/>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="1" t="str" cm="1">
+        <f t="array" ref="B53">UPPER(INDEX(_xlfn.TEXTSPLIT($C53, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G53" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H53" s="1">
+        <v>2</v>
+      </c>
+      <c r="I53" s="1">
+        <v>8</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N53" s="1" t="str">
+        <f>SUBSTITUTE(E53,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-kfk01-osdisk</v>
+      </c>
+      <c r="O53" s="1">
+        <v>64</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
-      <c r="S53" s="86"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1"/>
-      <c r="W53" s="1"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1" t="str">
+        <f>SUBSTITUTE(E53,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-kfk01-nic</v>
+      </c>
+      <c r="U53" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W53" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y53" s="1">
+        <v>1</v>
+      </c>
       <c r="Z53" s="1"/>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="86"/>
+      <c r="AA53" s="1"/>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="1" t="str" cm="1">
+        <f t="array" ref="B54">UPPER(INDEX(_xlfn.TEXTSPLIT($C54, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="G54" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H54" s="1">
+        <v>2</v>
+      </c>
+      <c r="I54" s="1">
+        <v>8</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K54" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N54" s="1" t="str">
+        <f>SUBSTITUTE(E54,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-kfk02-osdisk</v>
+      </c>
+      <c r="O54" s="1">
+        <v>64</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
-      <c r="S54" s="86"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
-      <c r="W54" s="1"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1" t="str">
+        <f>SUBSTITUTE(E54,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-kfk02-nic</v>
+      </c>
+      <c r="U54" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X54" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y54" s="1">
+        <v>1</v>
+      </c>
       <c r="Z54" s="1"/>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="88"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="87"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="86"/>
+      <c r="AA54" s="1"/>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" s="1" t="str" cm="1">
+        <f t="array" ref="B55">UPPER(INDEX(_xlfn.TEXTSPLIT($C55, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H55" s="1">
+        <v>2</v>
+      </c>
+      <c r="I55" s="1">
+        <v>8</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N55" s="1" t="str">
+        <f>SUBSTITUTE(E55,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-mqap01-osdisk</v>
+      </c>
+      <c r="O55" s="1">
+        <v>64</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
-      <c r="S55" s="86"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1" t="str">
+        <f>SUBSTITUTE(E55,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-mqap01-nic</v>
+      </c>
+      <c r="U55" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V55" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W55" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X55" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y55" s="1">
+        <v>1</v>
+      </c>
       <c r="Z55" s="1"/>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="86"/>
+      <c r="AA55" s="1"/>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="1" t="str" cm="1">
+        <f t="array" ref="B56">UPPER(INDEX(_xlfn.TEXTSPLIT($C56, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="G56" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H56" s="1">
+        <v>2</v>
+      </c>
+      <c r="I56" s="1">
+        <v>8</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K56" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N56" s="1" t="str">
+        <f>SUBSTITUTE(E56,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-mqweb01-osdisk</v>
+      </c>
+      <c r="O56" s="1">
+        <v>64</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
-      <c r="S56" s="86"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1" t="str">
+        <f>SUBSTITUTE(E56,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-mqweb01-nic</v>
+      </c>
+      <c r="U56" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W56" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X56" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y56" s="1">
+        <v>1</v>
+      </c>
       <c r="Z56" s="1"/>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="88"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="87"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="86"/>
+      <c r="AA56" s="1"/>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="1" t="str" cm="1">
+        <f t="array" ref="B57">UPPER(INDEX(_xlfn.TEXTSPLIT($C57, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G57" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2</v>
+      </c>
+      <c r="I57" s="1">
+        <v>8</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N57" s="1" t="str">
+        <f>SUBSTITUTE(E57,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-oms01-osdisk</v>
+      </c>
+      <c r="O57" s="1">
+        <v>64</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
-      <c r="S57" s="86"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1"/>
-      <c r="W57" s="1"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1" t="str">
+        <f>SUBSTITUTE(E57,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-oms01-nic</v>
+      </c>
+      <c r="U57" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V57" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W57" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X57" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y57" s="1">
+        <v>1</v>
+      </c>
       <c r="Z57" s="1"/>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="88"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="86"/>
+      <c r="AA57" s="1"/>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="1" t="str" cm="1">
+        <f t="array" ref="B58">UPPER(INDEX(_xlfn.TEXTSPLIT($C58, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H58" s="1">
+        <v>2</v>
+      </c>
+      <c r="I58" s="1">
+        <v>8</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K58" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N58" s="1" t="str">
+        <f>SUBSTITUTE(E58,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-dip-web01-osdisk</v>
+      </c>
+      <c r="O58" s="1">
+        <v>64</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
-      <c r="S58" s="86"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1"/>
-      <c r="W58" s="1"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1" t="str">
+        <f>SUBSTITUTE(E58,"hazr-","")&amp;"-nic"</f>
+        <v>d-dip-web01-nic</v>
+      </c>
+      <c r="U58" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V58" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W58" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X58" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y58" s="1">
+        <v>1</v>
+      </c>
       <c r="Z58" s="1"/>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="87"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="86"/>
+      <c r="AA58" s="1"/>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="1" t="str" cm="1">
+        <f t="array" ref="B59">UPPER(INDEX(_xlfn.TEXTSPLIT($C59, "-"), 3))</f>
+        <v>COM</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G59" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H59" s="1">
+        <v>2</v>
+      </c>
+      <c r="I59" s="1">
+        <v>8</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N59" s="1" t="str">
+        <f>SUBSTITUTE(E59,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-com-auth01-osdisk</v>
+      </c>
+      <c r="O59" s="1">
+        <v>64</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
-      <c r="S59" s="86"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1" t="str">
+        <f>SUBSTITUTE(E59,"hazr-","")&amp;"-nic"</f>
+        <v>d-com-auth01-nic</v>
+      </c>
+      <c r="U59" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X59" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="Y59" s="1">
+        <v>1</v>
+      </c>
       <c r="Z59" s="1"/>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="88"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="86"/>
+      <c r="AA59" s="1"/>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" s="1" t="str" cm="1">
+        <f t="array" ref="B60">UPPER(INDEX(_xlfn.TEXTSPLIT($C60, "-"), 3))</f>
+        <v>COM</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G60" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H60" s="1">
+        <v>2</v>
+      </c>
+      <c r="I60" s="1">
+        <v>8</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K60" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N60" s="1" t="str">
+        <f>SUBSTITUTE(E60,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-com-proxy01-osdisk</v>
+      </c>
+      <c r="O60" s="1">
+        <v>64</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
-      <c r="S60" s="86"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1" t="str">
+        <f>SUBSTITUTE(E60,"hazr-","")&amp;"-nic"</f>
+        <v>d-com-proxy01-nic</v>
+      </c>
+      <c r="U60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y60" s="1">
+        <v>1</v>
+      </c>
       <c r="Z60" s="1"/>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="88"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="87"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="86"/>
+      <c r="AA60" s="1"/>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="1" t="str" cm="1">
+        <f t="array" ref="B61">UPPER(INDEX(_xlfn.TEXTSPLIT($C61, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H61" s="1">
+        <v>2</v>
+      </c>
+      <c r="I61" s="1">
+        <v>8</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N61" s="1" t="str">
+        <f>SUBSTITUTE(E61,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-if-gramon01-osdisk</v>
+      </c>
+      <c r="O61" s="1">
+        <v>64</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
-      <c r="S61" s="86"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1"/>
-      <c r="W61" s="1"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1" t="str">
+        <f>SUBSTITUTE(E61,"hazr-","")&amp;"-nic"</f>
+        <v>d-if-gramon01-nic</v>
+      </c>
+      <c r="U61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W61" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="Y61" s="1">
+        <v>1</v>
+      </c>
       <c r="Z61" s="1"/>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="86"/>
+      <c r="AA61" s="1"/>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="1" t="str" cm="1">
+        <f t="array" ref="B62">UPPER(INDEX(_xlfn.TEXTSPLIT($C62, "-"), 3))</f>
+        <v>COM</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G62" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H62" s="1">
+        <v>2</v>
+      </c>
+      <c r="I62" s="1">
+        <v>8</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K62" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N62" s="1" t="str">
+        <f>SUBSTITUTE(E62,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-cs-chtap01-osdisk</v>
+      </c>
+      <c r="O62" s="1">
+        <v>64</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
-      <c r="S62" s="86"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1" t="str">
+        <f>SUBSTITUTE(E62,"hazr-","")&amp;"-nic"</f>
+        <v>d-cs-chtap01-nic</v>
+      </c>
+      <c r="U62" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X62" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="Y62" s="1">
+        <v>1</v>
+      </c>
       <c r="Z62" s="1"/>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="87"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="86"/>
+      <c r="AA62" s="1"/>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="1" t="str" cm="1">
+        <f t="array" ref="B63">UPPER(INDEX(_xlfn.TEXTSPLIT($C63, "-"), 3))</f>
+        <v>CS</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="G63" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H63" s="1">
+        <v>2</v>
+      </c>
+      <c r="I63" s="1">
+        <v>8</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N63" s="1" t="str">
+        <f>SUBSTITUTE(E63,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-cs-chtweb01-osdisk</v>
+      </c>
+      <c r="O63" s="1">
+        <v>64</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
-      <c r="S63" s="86"/>
-      <c r="T63" s="1"/>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1" t="str">
+        <f>SUBSTITUTE(E63,"hazr-","")&amp;"-nic"</f>
+        <v>d-cs-chtweb01-nic</v>
+      </c>
+      <c r="U63" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W63" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X63" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>1</v>
+      </c>
       <c r="Z63" s="1"/>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="88"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="86"/>
+      <c r="AA63" s="1"/>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="1" t="str" cm="1">
+        <f t="array" ref="B64">UPPER(INDEX(_xlfn.TEXTSPLIT($C64, "-"), 3))</f>
+        <v>CS</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H64" s="1">
+        <v>2</v>
+      </c>
+      <c r="I64" s="1">
+        <v>8</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K64" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N64" s="1" t="str">
+        <f>SUBSTITUTE(E64,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-cs-chtintweb01-osdisk</v>
+      </c>
+      <c r="O64" s="1">
+        <v>64</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
-      <c r="S64" s="86"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1"/>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1" t="str">
+        <f>SUBSTITUTE(E64,"hazr-","")&amp;"-nic"</f>
+        <v>d-cs-chtintweb01-nic</v>
+      </c>
+      <c r="U64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X64" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="Y64" s="1">
+        <v>1</v>
+      </c>
       <c r="Z64" s="1"/>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="87"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="86"/>
+      <c r="AA64" s="1"/>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" s="1" t="str" cm="1">
+        <f t="array" ref="B65">UPPER(INDEX(_xlfn.TEXTSPLIT($C65, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="G65" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H65" s="1">
+        <v>2</v>
+      </c>
+      <c r="I65" s="1">
+        <v>8</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N65" s="1" t="str">
+        <f>SUBSTITUTE(E65,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-doip-web01-osdisk</v>
+      </c>
+      <c r="O65" s="1">
+        <v>64</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
-      <c r="S65" s="86"/>
-      <c r="T65" s="1"/>
-      <c r="U65" s="1"/>
-      <c r="V65" s="1"/>
-      <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1" t="str">
+        <f>SUBSTITUTE(E65,"hazr-","")&amp;"-nic"</f>
+        <v>d-doip-web01-nic</v>
+      </c>
+      <c r="U65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X65" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="Y65" s="1">
+        <v>1</v>
+      </c>
       <c r="Z65" s="1"/>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="88"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="86"/>
+      <c r="AA65" s="1"/>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" s="1" t="str" cm="1">
+        <f t="array" ref="B66">UPPER(INDEX(_xlfn.TEXTSPLIT($C66, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="G66" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H66" s="1">
+        <v>2</v>
+      </c>
+      <c r="I66" s="1">
+        <v>8</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K66" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N66" s="1" t="str">
+        <f t="shared" ref="N66:N70" si="1">SUBSTITUTE(E66,"hazr-","")&amp;"-osdisk"</f>
+        <v>d-doip-ap01-osdisk</v>
+      </c>
+      <c r="O66" s="1">
+        <v>64</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
-      <c r="S66" s="86"/>
-      <c r="T66" s="1"/>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1"/>
-      <c r="W66" s="1"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="1"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1" t="str">
+        <f>SUBSTITUTE(E66,"hazr-","")&amp;"-nic"</f>
+        <v>d-doip-ap01-nic</v>
+      </c>
+      <c r="U66" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X66" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>1</v>
+      </c>
       <c r="Z66" s="1"/>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="88"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="87"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="86"/>
+      <c r="AA66" s="1"/>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67" s="1" t="str" cm="1">
+        <f t="array" ref="B67">UPPER(INDEX(_xlfn.TEXTSPLIT($C67, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H67" s="1">
+        <v>2</v>
+      </c>
+      <c r="I67" s="1">
+        <v>8</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N67" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>d-doip-adm01-osdisk</v>
+      </c>
+      <c r="O67" s="1">
+        <v>64</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
-      <c r="S67" s="86"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1"/>
-      <c r="W67" s="1"/>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="1"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1" t="str">
+        <f t="shared" ref="T67:T70" si="2">SUBSTITUTE(E67,"hazr-","")&amp;"-nic"</f>
+        <v>d-doip-adm01-nic</v>
+      </c>
+      <c r="U67" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W67" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X67" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="Y67" s="1">
+        <v>1</v>
+      </c>
       <c r="Z67" s="1"/>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="86"/>
+      <c r="AA67" s="1"/>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B68" s="1" t="str" cm="1">
+        <f t="array" ref="B68">UPPER(INDEX(_xlfn.TEXTSPLIT($C68, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G68" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H68" s="1">
+        <v>2</v>
+      </c>
+      <c r="I68" s="1">
+        <v>8</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K68" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N68" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>d-bdp-crkweb01-osdisk</v>
+      </c>
+      <c r="O68" s="1">
+        <v>64</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
-      <c r="S68" s="86"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1"/>
-      <c r="W68" s="1"/>
-      <c r="X68" s="1"/>
-      <c r="Y68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>d-bdp-crkweb01-nic</v>
+      </c>
+      <c r="U68" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W68" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="X68" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>1</v>
+      </c>
       <c r="Z68" s="1"/>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="88"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="87"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="86"/>
+      <c r="AA68" s="1"/>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B69" s="1" t="str" cm="1">
+        <f t="array" ref="B69">UPPER(INDEX(_xlfn.TEXTSPLIT($C69, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G69" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="H69" s="1">
+        <v>2</v>
+      </c>
+      <c r="I69" s="1">
+        <v>8</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N69" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>d-bdp-crkap01-osdisk</v>
+      </c>
+      <c r="O69" s="1">
+        <v>64</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
-      <c r="S69" s="86"/>
-      <c r="T69" s="1"/>
-      <c r="U69" s="1"/>
-      <c r="V69" s="1"/>
-      <c r="W69" s="1"/>
-      <c r="X69" s="1"/>
-      <c r="Y69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>d-bdp-crkap01-nic</v>
+      </c>
+      <c r="U69" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W69" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X69" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>1</v>
+      </c>
       <c r="Z69" s="1"/>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="88"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="86"/>
+      <c r="AA69" s="1"/>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B70" s="1" t="str" cm="1">
+        <f t="array" ref="B70">UPPER(INDEX(_xlfn.TEXTSPLIT($C70, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H70" s="1">
+        <v>2</v>
+      </c>
+      <c r="I70" s="1">
+        <v>8</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="K70" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N70" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>d-bdp-crkml01-osdisk</v>
+      </c>
+      <c r="O70" s="1">
+        <v>64</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
-      <c r="S70" s="86"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1"/>
-      <c r="W70" s="1"/>
-      <c r="X70" s="1"/>
-      <c r="Y70" s="1"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>d-bdp-crkml01-nic</v>
+      </c>
+      <c r="U70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="V70" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="W70" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="X70" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>1</v>
+      </c>
       <c r="Z70" s="1"/>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="87"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="86"/>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1"/>
-      <c r="S71" s="86"/>
-      <c r="T71" s="1"/>
-      <c r="U71" s="1"/>
-      <c r="V71" s="1"/>
-      <c r="W71" s="1"/>
-      <c r="X71" s="1"/>
-      <c r="Y71" s="1"/>
-      <c r="Z71" s="1"/>
+      <c r="AA70" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10722,21 +14552,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -10880,31 +14695,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10920,4 +14726,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEB6D1F-8CB8-40D7-8A5C-313ABA03A4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB43F3B-CDF9-4523-B03F-042467D55FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1655,7 +1655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="504">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3437,6 +3437,14 @@
   </si>
   <si>
     <t>10.156.156.60</t>
+  </si>
+  <si>
+    <t>StandardSSD_LRS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4119,452 +4127,6 @@
   <dxfs count="57">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -5019,6 +4581,452 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5033,83 +5041,83 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:AA70" totalsRowShown="0" headerRowDxfId="56" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:AA70" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A1:AA70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="53">
       <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($C2, "-"), 3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="23"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="22"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="21"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="15">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="49"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="48"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="47"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="42"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="41">
       <calculatedColumnFormula>SUBSTITUTE(E2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="13"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="12"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="11"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="9">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="37"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="36"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="35">
       <calculatedColumnFormula>SUBSTITUTE(E2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="7"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="6"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="5"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="4"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="3"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="33"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="32"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="31"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="30"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="29"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:Z5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="49"/>
-    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="48"/>
-    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="47"/>
-    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="42"/>
-    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="41">
+    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="21"/>
+    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="20"/>
+    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="19"/>
+    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="13">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="39"/>
-    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="38">
+    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="10">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-disk"&amp;"01"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="37"/>
-    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="36"/>
-    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="35">
+    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="7">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="33"/>
-    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="32"/>
-    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="31"/>
-    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="30"/>
-    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="29"/>
-    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="3"/>
+    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6527,7 +6535,7 @@
         <v>343</v>
       </c>
       <c r="N2" s="1" t="str">
-        <f>SUBSTITUTE(E2,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="N2:N33" si="0">SUBSTITUTE(E2,"hazr-","")&amp;"-osdisk"</f>
         <v>d-dis-ap01-osdisk</v>
       </c>
       <c r="O2" s="1">
@@ -6540,7 +6548,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="str">
-        <f t="shared" ref="T2" si="0">SUBSTITUTE(E2,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="T2" si="1">SUBSTITUTE(E2,"hazr-","")&amp;"-nic"</f>
         <v>d-dis-ap01-nic</v>
       </c>
       <c r="U2" s="1" t="b">
@@ -6603,7 +6611,7 @@
         <v>343</v>
       </c>
       <c r="N3" s="1" t="str">
-        <f>SUBSTITUTE(E3,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-adm01-osdisk</v>
       </c>
       <c r="O3" s="1">
@@ -6616,7 +6624,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1" t="str">
-        <f>SUBSTITUTE(E3,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="T3:T34" si="2">SUBSTITUTE(E3,"hazr-","")&amp;"-nic"</f>
         <v>d-dis-adm01-nic</v>
       </c>
       <c r="U3" s="1" t="b">
@@ -6679,7 +6687,7 @@
         <v>349</v>
       </c>
       <c r="N4" s="1" t="str">
-        <f>SUBSTITUTE(E4,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-bbiweb01-osdisk</v>
       </c>
       <c r="O4" s="1">
@@ -6692,7 +6700,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="str">
-        <f>SUBSTITUTE(E4,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-bbiweb01-nic</v>
       </c>
       <c r="U4" s="1" t="b">
@@ -6755,7 +6763,7 @@
         <v>349</v>
       </c>
       <c r="N5" s="1" t="str">
-        <f>SUBSTITUTE(E5,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-bbicltap01-osdisk</v>
       </c>
       <c r="O5" s="1">
@@ -6768,7 +6776,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1" t="str">
-        <f>SUBSTITUTE(E5,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-bbicltap01-nic</v>
       </c>
       <c r="U5" s="1" t="b">
@@ -6831,7 +6839,7 @@
         <v>349</v>
       </c>
       <c r="N6" s="1" t="str">
-        <f>SUBSTITUTE(E6,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-bbimsgap01-osdisk</v>
       </c>
       <c r="O6" s="1">
@@ -6844,7 +6852,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1" t="str">
-        <f>SUBSTITUTE(E6,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-bbimsgap01-nic</v>
       </c>
       <c r="U6" s="1" t="b">
@@ -6907,7 +6915,7 @@
         <v>349</v>
       </c>
       <c r="N7" s="1" t="str">
-        <f>SUBSTITUTE(E7,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-walkap01-osdisk</v>
       </c>
       <c r="O7" s="1">
@@ -6920,7 +6928,7 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1" t="str">
-        <f>SUBSTITUTE(E7,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-walkap01-nic</v>
       </c>
       <c r="U7" s="1" t="b">
@@ -6983,7 +6991,7 @@
         <v>349</v>
       </c>
       <c r="N8" s="1" t="str">
-        <f>SUBSTITUTE(E8,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-bat01-osdisk</v>
       </c>
       <c r="O8" s="1">
@@ -6996,7 +7004,7 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1" t="str">
-        <f>SUBSTITUTE(E8,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-bat01-nic</v>
       </c>
       <c r="U8" s="1" t="b">
@@ -7059,7 +7067,7 @@
         <v>349</v>
       </c>
       <c r="N9" s="1" t="str">
-        <f>SUBSTITUTE(E9,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-bat02-osdisk</v>
       </c>
       <c r="O9" s="1">
@@ -7072,7 +7080,7 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1" t="str">
-        <f>SUBSTITUTE(E9,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-bat02-nic</v>
       </c>
       <c r="U9" s="1" t="b">
@@ -7135,7 +7143,7 @@
         <v>349</v>
       </c>
       <c r="N10" s="1" t="str">
-        <f>SUBSTITUTE(E10,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-drvcltap01-osdisk</v>
       </c>
       <c r="O10" s="1">
@@ -7148,7 +7156,7 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1" t="str">
-        <f>SUBSTITUTE(E10,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-drvcltap01-nic</v>
       </c>
       <c r="U10" s="1" t="b">
@@ -7211,7 +7219,7 @@
         <v>349</v>
       </c>
       <c r="N11" s="1" t="str">
-        <f>SUBSTITUTE(E11,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-walkweb01-osdisk</v>
       </c>
       <c r="O11" s="1">
@@ -7224,7 +7232,7 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1" t="str">
-        <f>SUBSTITUTE(E11,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-walkweb01-nic</v>
       </c>
       <c r="U11" s="1" t="b">
@@ -7287,7 +7295,7 @@
         <v>349</v>
       </c>
       <c r="N12" s="1" t="str">
-        <f>SUBSTITUTE(E12,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-drvmsgap01-osdisk</v>
       </c>
       <c r="O12" s="1">
@@ -7300,7 +7308,7 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1" t="str">
-        <f>SUBSTITUTE(E12,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-drvmsgap01-nic</v>
       </c>
       <c r="U12" s="1" t="b">
@@ -7363,7 +7371,7 @@
         <v>349</v>
       </c>
       <c r="N13" s="1" t="str">
-        <f>SUBSTITUTE(E13,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-web01-osdisk</v>
       </c>
       <c r="O13" s="1">
@@ -7376,7 +7384,7 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1" t="str">
-        <f>SUBSTITUTE(E13,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-web01-nic</v>
       </c>
       <c r="U13" s="1" t="b">
@@ -7439,7 +7447,7 @@
         <v>349</v>
       </c>
       <c r="N14" s="1" t="str">
-        <f>SUBSTITUTE(E14,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-cmsadm01-osdisk</v>
       </c>
       <c r="O14" s="1">
@@ -7452,7 +7460,7 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1" t="str">
-        <f>SUBSTITUTE(E14,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-cmsadm01-nic</v>
       </c>
       <c r="U14" s="1" t="b">
@@ -7515,7 +7523,7 @@
         <v>349</v>
       </c>
       <c r="N15" s="1" t="str">
-        <f>SUBSTITUTE(E15,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-cmsap01-osdisk</v>
       </c>
       <c r="O15" s="1">
@@ -7528,7 +7536,7 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1" t="str">
-        <f>SUBSTITUTE(E15,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-cmsap01-nic</v>
       </c>
       <c r="U15" s="1" t="b">
@@ -7591,7 +7599,7 @@
         <v>349</v>
       </c>
       <c r="N16" s="1" t="str">
-        <f>SUBSTITUTE(E16,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-cmsweb01-osdisk</v>
       </c>
       <c r="O16" s="1">
@@ -7604,7 +7612,7 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1" t="str">
-        <f>SUBSTITUTE(E16,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-cmsweb01-nic</v>
       </c>
       <c r="U16" s="1" t="b">
@@ -7667,7 +7675,7 @@
         <v>349</v>
       </c>
       <c r="N17" s="1" t="str">
-        <f>SUBSTITUTE(E17,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dis-cmbsap01-osdisk</v>
       </c>
       <c r="O17" s="1">
@@ -7680,7 +7688,7 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1" t="str">
-        <f>SUBSTITUTE(E17,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dis-cmbsap01-nic</v>
       </c>
       <c r="U17" s="1" t="b">
@@ -7743,20 +7751,20 @@
         <v>349</v>
       </c>
       <c r="N18" s="1" t="str">
-        <f>SUBSTITUTE(E18,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-ingap01-osdisk</v>
       </c>
       <c r="O18" s="1">
         <v>64</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1" t="str">
-        <f>SUBSTITUTE(E18,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-ingap01-nic</v>
       </c>
       <c r="U18" s="1" t="b">
@@ -7819,20 +7827,20 @@
         <v>349</v>
       </c>
       <c r="N19" s="1" t="str">
-        <f>SUBSTITUTE(E19,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-ap01-osdisk</v>
       </c>
       <c r="O19" s="1">
         <v>64</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1" t="str">
-        <f>SUBSTITUTE(E19,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-ap01-nic</v>
       </c>
       <c r="U19" s="1" t="b">
@@ -7895,20 +7903,20 @@
         <v>349</v>
       </c>
       <c r="N20" s="1" t="str">
-        <f>SUBSTITUTE(E20,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-extgeoap01-osdisk</v>
       </c>
       <c r="O20" s="1">
         <v>64</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1" t="str">
-        <f>SUBSTITUTE(E20,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-extgeoap01-nic</v>
       </c>
       <c r="U20" s="1" t="b">
@@ -7971,20 +7979,20 @@
         <v>349</v>
       </c>
       <c r="N21" s="1" t="str">
-        <f>SUBSTITUTE(E21,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-geoap01-osdisk</v>
       </c>
       <c r="O21" s="1">
         <v>64</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1" t="str">
-        <f>SUBSTITUTE(E21,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-geoap01-nic</v>
       </c>
       <c r="U21" s="1" t="b">
@@ -8047,20 +8055,20 @@
         <v>349</v>
       </c>
       <c r="N22" s="1" t="str">
-        <f>SUBSTITUTE(E22,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-mq01-osdisk</v>
       </c>
       <c r="O22" s="1">
         <v>64</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1" t="str">
-        <f>SUBSTITUTE(E22,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-mq01-nic</v>
       </c>
       <c r="U22" s="1" t="b">
@@ -8123,20 +8131,20 @@
         <v>349</v>
       </c>
       <c r="N23" s="1" t="str">
-        <f>SUBSTITUTE(E23,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-admweb01-osdisk</v>
       </c>
       <c r="O23" s="1">
         <v>64</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1" t="str">
-        <f>SUBSTITUTE(E23,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-admweb01-nic</v>
       </c>
       <c r="U23" s="1" t="b">
@@ -8199,20 +8207,20 @@
         <v>349</v>
       </c>
       <c r="N24" s="1" t="str">
-        <f>SUBSTITUTE(E24,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-admap01-osdisk</v>
       </c>
       <c r="O24" s="1">
         <v>64</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1" t="str">
-        <f>SUBSTITUTE(E24,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-admap01-nic</v>
       </c>
       <c r="U24" s="1" t="b">
@@ -8275,20 +8283,20 @@
         <v>349</v>
       </c>
       <c r="N25" s="1" t="str">
-        <f>SUBSTITUTE(E25,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-dtoms01-osdisk</v>
       </c>
       <c r="O25" s="1">
         <v>64</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1" t="str">
-        <f>SUBSTITUTE(E25,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-dtoms01-nic</v>
       </c>
       <c r="U25" s="1" t="b">
@@ -8351,20 +8359,20 @@
         <v>349</v>
       </c>
       <c r="N26" s="1" t="str">
-        <f>SUBSTITUTE(E26,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-tsdb01-osdisk</v>
       </c>
       <c r="O26" s="1">
         <v>64</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1" t="str">
-        <f>SUBSTITUTE(E26,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-tsdb01-nic</v>
       </c>
       <c r="U26" s="1" t="b">
@@ -8427,20 +8435,20 @@
         <v>349</v>
       </c>
       <c r="N27" s="1" t="str">
-        <f>SUBSTITUTE(E27,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-web01-osdisk</v>
       </c>
       <c r="O27" s="1">
         <v>64</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1" t="str">
-        <f>SUBSTITUTE(E27,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-web01-nic</v>
       </c>
       <c r="U27" s="1" t="b">
@@ -8503,20 +8511,20 @@
         <v>349</v>
       </c>
       <c r="N28" s="1" t="str">
-        <f>SUBSTITUTE(E28,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-zkp01-osdisk</v>
       </c>
       <c r="O28" s="1">
         <v>64</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1" t="str">
-        <f>SUBSTITUTE(E28,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-zkp01-nic</v>
       </c>
       <c r="U28" s="1" t="b">
@@ -8579,20 +8587,20 @@
         <v>349</v>
       </c>
       <c r="N29" s="1" t="str">
-        <f>SUBSTITUTE(E29,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-zkp02-osdisk</v>
       </c>
       <c r="O29" s="1">
         <v>64</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1" t="str">
-        <f>SUBSTITUTE(E29,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-zkp02-nic</v>
       </c>
       <c r="U29" s="1" t="b">
@@ -8655,20 +8663,20 @@
         <v>349</v>
       </c>
       <c r="N30" s="1" t="str">
-        <f>SUBSTITUTE(E30,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-zkp03-osdisk</v>
       </c>
       <c r="O30" s="1">
         <v>64</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1" t="str">
-        <f>SUBSTITUTE(E30,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-zkp03-nic</v>
       </c>
       <c r="U30" s="1" t="b">
@@ -8731,20 +8739,20 @@
         <v>349</v>
       </c>
       <c r="N31" s="1" t="str">
-        <f>SUBSTITUTE(E31,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-kfk01-osdisk</v>
       </c>
       <c r="O31" s="1">
         <v>64</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1" t="str">
-        <f>SUBSTITUTE(E31,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-kfk01-nic</v>
       </c>
       <c r="U31" s="1" t="b">
@@ -8807,20 +8815,20 @@
         <v>349</v>
       </c>
       <c r="N32" s="1" t="str">
-        <f>SUBSTITUTE(E32,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-kfk02-osdisk</v>
       </c>
       <c r="O32" s="1">
         <v>64</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1" t="str">
-        <f>SUBSTITUTE(E32,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-kfk02-nic</v>
       </c>
       <c r="U32" s="1" t="b">
@@ -8883,20 +8891,20 @@
         <v>349</v>
       </c>
       <c r="N33" s="1" t="str">
-        <f>SUBSTITUTE(E33,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="0"/>
         <v>d-dtg-kfk03-osdisk</v>
       </c>
       <c r="O33" s="1">
         <v>64</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1" t="str">
-        <f>SUBSTITUTE(E33,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-kfk03-nic</v>
       </c>
       <c r="U33" s="1" t="b">
@@ -8959,20 +8967,20 @@
         <v>349</v>
       </c>
       <c r="N34" s="1" t="str">
-        <f>SUBSTITUTE(E34,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="N34:N65" si="3">SUBSTITUTE(E34,"hazr-","")&amp;"-osdisk"</f>
         <v>d-dtg-mdoms01-osdisk</v>
       </c>
       <c r="O34" s="1">
         <v>64</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1" t="str">
-        <f>SUBSTITUTE(E34,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="2"/>
         <v>d-dtg-mdoms01-nic</v>
       </c>
       <c r="U34" s="1" t="b">
@@ -9035,20 +9043,20 @@
         <v>349</v>
       </c>
       <c r="N35" s="1" t="str">
-        <f>SUBSTITUTE(E35,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dtg-cdmlap01-osdisk</v>
       </c>
       <c r="O35" s="1">
         <v>64</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1" t="str">
-        <f>SUBSTITUTE(E35,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="T35:T66" si="4">SUBSTITUTE(E35,"hazr-","")&amp;"-nic"</f>
         <v>d-dtg-cdmlap01-nic</v>
       </c>
       <c r="U35" s="1" t="b">
@@ -9111,20 +9119,20 @@
         <v>349</v>
       </c>
       <c r="N36" s="1" t="str">
-        <f>SUBSTITUTE(E36,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dtg-cdstap01-osdisk</v>
       </c>
       <c r="O36" s="1">
         <v>64</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1" t="str">
-        <f>SUBSTITUTE(E36,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dtg-cdstap01-nic</v>
       </c>
       <c r="U36" s="1" t="b">
@@ -9187,20 +9195,20 @@
         <v>349</v>
       </c>
       <c r="N37" s="1" t="str">
-        <f>SUBSTITUTE(E37,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dtg-cdsvap01-osdisk</v>
       </c>
       <c r="O37" s="1">
         <v>64</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1" t="str">
-        <f>SUBSTITUTE(E37,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dtg-cdsvap01-nic</v>
       </c>
       <c r="U37" s="1" t="b">
@@ -9263,20 +9271,20 @@
         <v>349</v>
       </c>
       <c r="N38" s="1" t="str">
-        <f>SUBSTITUTE(E38,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dtg-diosap01-osdisk</v>
       </c>
       <c r="O38" s="1">
         <v>64</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1" t="str">
-        <f>SUBSTITUTE(E38,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dtg-diosap01-nic</v>
       </c>
       <c r="U38" s="1" t="b">
@@ -9339,20 +9347,20 @@
         <v>349</v>
       </c>
       <c r="N39" s="1" t="str">
-        <f>SUBSTITUTE(E39,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dtg-diosweb01-osdisk</v>
       </c>
       <c r="O39" s="1">
         <v>64</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1" t="str">
-        <f>SUBSTITUTE(E39,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dtg-diosweb01-nic</v>
       </c>
       <c r="U39" s="1" t="b">
@@ -9415,20 +9423,20 @@
         <v>349</v>
       </c>
       <c r="N40" s="1" t="str">
-        <f>SUBSTITUTE(E40,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dtg-dprweb01-osdisk</v>
       </c>
       <c r="O40" s="1">
         <v>64</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1" t="str">
-        <f>SUBSTITUTE(E40,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dtg-dprweb01-nic</v>
       </c>
       <c r="U40" s="1" t="b">
@@ -9491,20 +9499,20 @@
         <v>349</v>
       </c>
       <c r="N41" s="1" t="str">
-        <f>SUBSTITUTE(E41,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dtg-dprap01-osdisk</v>
       </c>
       <c r="O41" s="1">
         <v>64</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1" t="str">
-        <f>SUBSTITUTE(E41,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dtg-dprap01-nic</v>
       </c>
       <c r="U41" s="1" t="b">
@@ -9567,7 +9575,7 @@
         <v>349</v>
       </c>
       <c r="N42" s="1" t="str">
-        <f>SUBSTITUTE(E42,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-bdp-airfw01-osdisk</v>
       </c>
       <c r="O42" s="1">
@@ -9580,7 +9588,7 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="T42" s="1" t="str">
-        <f>SUBSTITUTE(E42,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-bdp-airfw01-nic</v>
       </c>
       <c r="U42" s="1" t="b">
@@ -9643,7 +9651,7 @@
         <v>349</v>
       </c>
       <c r="N43" s="1" t="str">
-        <f>SUBSTITUTE(E43,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-bdp-kepler01-osdisk</v>
       </c>
       <c r="O43" s="1">
@@ -9656,7 +9664,7 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="T43" s="1" t="str">
-        <f>SUBSTITUTE(E43,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-bdp-kepler01-nic</v>
       </c>
       <c r="U43" s="1" t="b">
@@ -9719,7 +9727,7 @@
         <v>349</v>
       </c>
       <c r="N44" s="1" t="str">
-        <f>SUBSTITUTE(E44,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-bdp-cxmap01-osdisk</v>
       </c>
       <c r="O44" s="1">
@@ -9732,7 +9740,7 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1" t="str">
-        <f>SUBSTITUTE(E44,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-bdp-cxmap01-nic</v>
       </c>
       <c r="U44" s="1" t="b">
@@ -9795,7 +9803,7 @@
         <v>349</v>
       </c>
       <c r="N45" s="1" t="str">
-        <f>SUBSTITUTE(E45,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-bdp-slap01-osdisk</v>
       </c>
       <c r="O45" s="1">
@@ -9808,7 +9816,7 @@
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
       <c r="T45" s="1" t="str">
-        <f>SUBSTITUTE(E45,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-bdp-slap01-nic</v>
       </c>
       <c r="U45" s="1" t="b">
@@ -9835,10 +9843,10 @@
       </c>
       <c r="B46" s="1" t="str" cm="1">
         <f t="array" ref="B46">UPPER(INDEX(_xlfn.TEXTSPLIT($C46, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>24</v>
@@ -9871,7 +9879,7 @@
         <v>349</v>
       </c>
       <c r="N46" s="1" t="str">
-        <f>SUBSTITUTE(E46,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-adm01-osdisk</v>
       </c>
       <c r="O46" s="1">
@@ -9884,7 +9892,7 @@
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
       <c r="T46" s="1" t="str">
-        <f>SUBSTITUTE(E46,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-adm01-nic</v>
       </c>
       <c r="U46" s="1" t="b">
@@ -9911,10 +9919,10 @@
       </c>
       <c r="B47" s="1" t="str" cm="1">
         <f t="array" ref="B47">UPPER(INDEX(_xlfn.TEXTSPLIT($C47, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>24</v>
@@ -9947,7 +9955,7 @@
         <v>349</v>
       </c>
       <c r="N47" s="1" t="str">
-        <f>SUBSTITUTE(E47,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-ap01-osdisk</v>
       </c>
       <c r="O47" s="1">
@@ -9960,7 +9968,7 @@
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1" t="str">
-        <f>SUBSTITUTE(E47,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-ap01-nic</v>
       </c>
       <c r="U47" s="1" t="b">
@@ -9987,10 +9995,10 @@
       </c>
       <c r="B48" s="1" t="str" cm="1">
         <f t="array" ref="B48">UPPER(INDEX(_xlfn.TEXTSPLIT($C48, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>24</v>
@@ -10023,7 +10031,7 @@
         <v>349</v>
       </c>
       <c r="N48" s="1" t="str">
-        <f>SUBSTITUTE(E48,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-flk01-osdisk</v>
       </c>
       <c r="O48" s="1">
@@ -10036,7 +10044,7 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1" t="str">
-        <f>SUBSTITUTE(E48,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-flk01-nic</v>
       </c>
       <c r="U48" s="1" t="b">
@@ -10063,10 +10071,10 @@
       </c>
       <c r="B49" s="1" t="str" cm="1">
         <f t="array" ref="B49">UPPER(INDEX(_xlfn.TEXTSPLIT($C49, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>24</v>
@@ -10099,7 +10107,7 @@
         <v>349</v>
       </c>
       <c r="N49" s="1" t="str">
-        <f>SUBSTITUTE(E49,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-flk02-osdisk</v>
       </c>
       <c r="O49" s="1">
@@ -10112,7 +10120,7 @@
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" s="1" t="str">
-        <f>SUBSTITUTE(E49,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-flk02-nic</v>
       </c>
       <c r="U49" s="1" t="b">
@@ -10139,10 +10147,10 @@
       </c>
       <c r="B50" s="1" t="str" cm="1">
         <f t="array" ref="B50">UPPER(INDEX(_xlfn.TEXTSPLIT($C50, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>24</v>
@@ -10175,7 +10183,7 @@
         <v>349</v>
       </c>
       <c r="N50" s="1" t="str">
-        <f>SUBSTITUTE(E50,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-flk03-osdisk</v>
       </c>
       <c r="O50" s="1">
@@ -10188,7 +10196,7 @@
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" s="1" t="str">
-        <f>SUBSTITUTE(E50,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-flk03-nic</v>
       </c>
       <c r="U50" s="1" t="b">
@@ -10215,10 +10223,10 @@
       </c>
       <c r="B51" s="1" t="str" cm="1">
         <f t="array" ref="B51">UPPER(INDEX(_xlfn.TEXTSPLIT($C51, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>24</v>
@@ -10251,7 +10259,7 @@
         <v>349</v>
       </c>
       <c r="N51" s="1" t="str">
-        <f>SUBSTITUTE(E51,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-geoap01-osdisk</v>
       </c>
       <c r="O51" s="1">
@@ -10264,7 +10272,7 @@
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
       <c r="T51" s="1" t="str">
-        <f>SUBSTITUTE(E51,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-geoap01-nic</v>
       </c>
       <c r="U51" s="1" t="b">
@@ -10291,10 +10299,10 @@
       </c>
       <c r="B52" s="1" t="str" cm="1">
         <f t="array" ref="B52">UPPER(INDEX(_xlfn.TEXTSPLIT($C52, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>24</v>
@@ -10327,7 +10335,7 @@
         <v>349</v>
       </c>
       <c r="N52" s="1" t="str">
-        <f>SUBSTITUTE(E52,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-kfk01-osdisk</v>
       </c>
       <c r="O52" s="1">
@@ -10340,7 +10348,7 @@
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1" t="str">
-        <f>SUBSTITUTE(E52,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-kfk01-nic</v>
       </c>
       <c r="U52" s="1" t="b">
@@ -10367,10 +10375,10 @@
       </c>
       <c r="B53" s="1" t="str" cm="1">
         <f t="array" ref="B53">UPPER(INDEX(_xlfn.TEXTSPLIT($C53, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>24</v>
@@ -10403,7 +10411,7 @@
         <v>349</v>
       </c>
       <c r="N53" s="1" t="str">
-        <f>SUBSTITUTE(E53,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-kfk01-osdisk</v>
       </c>
       <c r="O53" s="1">
@@ -10416,7 +10424,7 @@
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1" t="str">
-        <f>SUBSTITUTE(E53,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-kfk01-nic</v>
       </c>
       <c r="U53" s="1" t="b">
@@ -10443,10 +10451,10 @@
       </c>
       <c r="B54" s="1" t="str" cm="1">
         <f t="array" ref="B54">UPPER(INDEX(_xlfn.TEXTSPLIT($C54, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>24</v>
@@ -10479,7 +10487,7 @@
         <v>349</v>
       </c>
       <c r="N54" s="1" t="str">
-        <f>SUBSTITUTE(E54,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-kfk02-osdisk</v>
       </c>
       <c r="O54" s="1">
@@ -10492,7 +10500,7 @@
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
       <c r="T54" s="1" t="str">
-        <f>SUBSTITUTE(E54,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-kfk02-nic</v>
       </c>
       <c r="U54" s="1" t="b">
@@ -10519,10 +10527,10 @@
       </c>
       <c r="B55" s="1" t="str" cm="1">
         <f t="array" ref="B55">UPPER(INDEX(_xlfn.TEXTSPLIT($C55, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>24</v>
@@ -10555,7 +10563,7 @@
         <v>349</v>
       </c>
       <c r="N55" s="1" t="str">
-        <f>SUBSTITUTE(E55,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-mqap01-osdisk</v>
       </c>
       <c r="O55" s="1">
@@ -10568,7 +10576,7 @@
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
       <c r="T55" s="1" t="str">
-        <f>SUBSTITUTE(E55,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-mqap01-nic</v>
       </c>
       <c r="U55" s="1" t="b">
@@ -10595,10 +10603,10 @@
       </c>
       <c r="B56" s="1" t="str" cm="1">
         <f t="array" ref="B56">UPPER(INDEX(_xlfn.TEXTSPLIT($C56, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>24</v>
@@ -10631,7 +10639,7 @@
         <v>349</v>
       </c>
       <c r="N56" s="1" t="str">
-        <f>SUBSTITUTE(E56,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-mqweb01-osdisk</v>
       </c>
       <c r="O56" s="1">
@@ -10644,7 +10652,7 @@
       <c r="R56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" s="1" t="str">
-        <f>SUBSTITUTE(E56,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-mqweb01-nic</v>
       </c>
       <c r="U56" s="1" t="b">
@@ -10671,10 +10679,10 @@
       </c>
       <c r="B57" s="1" t="str" cm="1">
         <f t="array" ref="B57">UPPER(INDEX(_xlfn.TEXTSPLIT($C57, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>24</v>
@@ -10707,7 +10715,7 @@
         <v>349</v>
       </c>
       <c r="N57" s="1" t="str">
-        <f>SUBSTITUTE(E57,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-oms01-osdisk</v>
       </c>
       <c r="O57" s="1">
@@ -10720,7 +10728,7 @@
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
       <c r="T57" s="1" t="str">
-        <f>SUBSTITUTE(E57,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-oms01-nic</v>
       </c>
       <c r="U57" s="1" t="b">
@@ -10747,10 +10755,10 @@
       </c>
       <c r="B58" s="1" t="str" cm="1">
         <f t="array" ref="B58">UPPER(INDEX(_xlfn.TEXTSPLIT($C58, "-"), 3))</f>
-        <v>BDP</v>
+        <v>DIP</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>431</v>
+        <v>503</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>24</v>
@@ -10783,7 +10791,7 @@
         <v>349</v>
       </c>
       <c r="N58" s="1" t="str">
-        <f>SUBSTITUTE(E58,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-dip-web01-osdisk</v>
       </c>
       <c r="O58" s="1">
@@ -10796,7 +10804,7 @@
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
       <c r="T58" s="1" t="str">
-        <f>SUBSTITUTE(E58,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-dip-web01-nic</v>
       </c>
       <c r="U58" s="1" t="b">
@@ -10859,7 +10867,7 @@
         <v>349</v>
       </c>
       <c r="N59" s="1" t="str">
-        <f>SUBSTITUTE(E59,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-com-auth01-osdisk</v>
       </c>
       <c r="O59" s="1">
@@ -10872,7 +10880,7 @@
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
       <c r="T59" s="1" t="str">
-        <f>SUBSTITUTE(E59,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-com-auth01-nic</v>
       </c>
       <c r="U59" s="1" t="b">
@@ -10935,7 +10943,7 @@
         <v>349</v>
       </c>
       <c r="N60" s="1" t="str">
-        <f>SUBSTITUTE(E60,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-com-proxy01-osdisk</v>
       </c>
       <c r="O60" s="1">
@@ -10948,7 +10956,7 @@
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
       <c r="T60" s="1" t="str">
-        <f>SUBSTITUTE(E60,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-com-proxy01-nic</v>
       </c>
       <c r="U60" s="1" t="b">
@@ -11011,7 +11019,7 @@
         <v>349</v>
       </c>
       <c r="N61" s="1" t="str">
-        <f>SUBSTITUTE(E61,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-if-gramon01-osdisk</v>
       </c>
       <c r="O61" s="1">
@@ -11024,7 +11032,7 @@
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
       <c r="T61" s="1" t="str">
-        <f>SUBSTITUTE(E61,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-if-gramon01-nic</v>
       </c>
       <c r="U61" s="1" t="b">
@@ -11087,7 +11095,7 @@
         <v>349</v>
       </c>
       <c r="N62" s="1" t="str">
-        <f>SUBSTITUTE(E62,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-cs-chtap01-osdisk</v>
       </c>
       <c r="O62" s="1">
@@ -11100,7 +11108,7 @@
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
       <c r="T62" s="1" t="str">
-        <f>SUBSTITUTE(E62,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-cs-chtap01-nic</v>
       </c>
       <c r="U62" s="1" t="b">
@@ -11163,7 +11171,7 @@
         <v>349</v>
       </c>
       <c r="N63" s="1" t="str">
-        <f>SUBSTITUTE(E63,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-cs-chtweb01-osdisk</v>
       </c>
       <c r="O63" s="1">
@@ -11176,7 +11184,7 @@
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
       <c r="T63" s="1" t="str">
-        <f>SUBSTITUTE(E63,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-cs-chtweb01-nic</v>
       </c>
       <c r="U63" s="1" t="b">
@@ -11239,7 +11247,7 @@
         <v>349</v>
       </c>
       <c r="N64" s="1" t="str">
-        <f>SUBSTITUTE(E64,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-cs-chtintweb01-osdisk</v>
       </c>
       <c r="O64" s="1">
@@ -11252,7 +11260,7 @@
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
       <c r="T64" s="1" t="str">
-        <f>SUBSTITUTE(E64,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-cs-chtintweb01-nic</v>
       </c>
       <c r="U64" s="1" t="b">
@@ -11315,7 +11323,7 @@
         <v>349</v>
       </c>
       <c r="N65" s="1" t="str">
-        <f>SUBSTITUTE(E65,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" si="3"/>
         <v>d-doip-web01-osdisk</v>
       </c>
       <c r="O65" s="1">
@@ -11328,7 +11336,7 @@
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
       <c r="T65" s="1" t="str">
-        <f>SUBSTITUTE(E65,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-doip-web01-nic</v>
       </c>
       <c r="U65" s="1" t="b">
@@ -11391,7 +11399,7 @@
         <v>349</v>
       </c>
       <c r="N66" s="1" t="str">
-        <f t="shared" ref="N66:N70" si="1">SUBSTITUTE(E66,"hazr-","")&amp;"-osdisk"</f>
+        <f t="shared" ref="N66:N70" si="5">SUBSTITUTE(E66,"hazr-","")&amp;"-osdisk"</f>
         <v>d-doip-ap01-osdisk</v>
       </c>
       <c r="O66" s="1">
@@ -11404,7 +11412,7 @@
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
       <c r="T66" s="1" t="str">
-        <f>SUBSTITUTE(E66,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="4"/>
         <v>d-doip-ap01-nic</v>
       </c>
       <c r="U66" s="1" t="b">
@@ -11467,7 +11475,7 @@
         <v>349</v>
       </c>
       <c r="N67" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>d-doip-adm01-osdisk</v>
       </c>
       <c r="O67" s="1">
@@ -11480,7 +11488,7 @@
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
       <c r="T67" s="1" t="str">
-        <f t="shared" ref="T67:T70" si="2">SUBSTITUTE(E67,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="T67:T70" si="6">SUBSTITUTE(E67,"hazr-","")&amp;"-nic"</f>
         <v>d-doip-adm01-nic</v>
       </c>
       <c r="U67" s="1" t="b">
@@ -11543,7 +11551,7 @@
         <v>349</v>
       </c>
       <c r="N68" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>d-bdp-crkweb01-osdisk</v>
       </c>
       <c r="O68" s="1">
@@ -11556,7 +11564,7 @@
       <c r="R68" s="1"/>
       <c r="S68" s="1"/>
       <c r="T68" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>d-bdp-crkweb01-nic</v>
       </c>
       <c r="U68" s="1" t="b">
@@ -11619,7 +11627,7 @@
         <v>349</v>
       </c>
       <c r="N69" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>d-bdp-crkap01-osdisk</v>
       </c>
       <c r="O69" s="1">
@@ -11632,7 +11640,7 @@
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
       <c r="T69" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>d-bdp-crkap01-nic</v>
       </c>
       <c r="U69" s="1" t="b">
@@ -11695,7 +11703,7 @@
         <v>349</v>
       </c>
       <c r="N70" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>d-bdp-crkml01-osdisk</v>
       </c>
       <c r="O70" s="1">
@@ -11708,7 +11716,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
       <c r="T70" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>d-bdp-crkml01-nic</v>
       </c>
       <c r="U70" s="1" t="b">
@@ -14552,6 +14560,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -14695,15 +14712,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -14711,6 +14719,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14724,14 +14740,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB43F3B-CDF9-4523-B03F-042467D55FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845D07A2-2AA6-45B3-BE31-54AE8B1671B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6542,7 +6542,7 @@
         <v>64</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -6618,7 +6618,7 @@
         <v>64</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -6694,7 +6694,7 @@
         <v>64</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -6770,7 +6770,7 @@
         <v>64</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -6846,7 +6846,7 @@
         <v>64</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
@@ -6922,7 +6922,7 @@
         <v>64</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
@@ -6998,7 +6998,7 @@
         <v>64</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
@@ -7074,7 +7074,7 @@
         <v>64</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -7150,7 +7150,7 @@
         <v>64</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -7226,7 +7226,7 @@
         <v>64</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -7302,7 +7302,7 @@
         <v>64</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -7378,7 +7378,7 @@
         <v>64</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -7454,7 +7454,7 @@
         <v>64</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
@@ -7530,7 +7530,7 @@
         <v>64</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -7606,7 +7606,7 @@
         <v>64</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -7682,7 +7682,7 @@
         <v>64</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -9582,7 +9582,7 @@
         <v>64</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
@@ -9658,7 +9658,7 @@
         <v>64</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
@@ -9734,7 +9734,7 @@
         <v>64</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
@@ -9810,7 +9810,7 @@
         <v>64</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
@@ -9886,7 +9886,7 @@
         <v>64</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
@@ -9962,7 +9962,7 @@
         <v>64</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
@@ -10038,7 +10038,7 @@
         <v>64</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
@@ -10114,7 +10114,7 @@
         <v>64</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
@@ -10190,7 +10190,7 @@
         <v>64</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
@@ -10266,7 +10266,7 @@
         <v>64</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
@@ -10342,7 +10342,7 @@
         <v>64</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
@@ -10418,7 +10418,7 @@
         <v>64</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
@@ -10494,7 +10494,7 @@
         <v>64</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
@@ -10570,7 +10570,7 @@
         <v>64</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
@@ -10646,7 +10646,7 @@
         <v>64</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
@@ -10722,7 +10722,7 @@
         <v>64</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
@@ -10798,7 +10798,7 @@
         <v>64</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
@@ -10874,7 +10874,7 @@
         <v>64</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
@@ -10950,7 +10950,7 @@
         <v>64</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
@@ -11026,7 +11026,7 @@
         <v>64</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
@@ -11102,7 +11102,7 @@
         <v>64</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
@@ -11178,7 +11178,7 @@
         <v>64</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
@@ -11254,7 +11254,7 @@
         <v>64</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
@@ -11330,7 +11330,7 @@
         <v>64</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
@@ -11406,7 +11406,7 @@
         <v>64</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
@@ -11482,7 +11482,7 @@
         <v>64</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
@@ -11558,7 +11558,7 @@
         <v>64</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
@@ -11634,7 +11634,7 @@
         <v>64</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
@@ -11710,7 +11710,7 @@
         <v>64</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
@@ -14560,12 +14560,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14713,15 +14710,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14745,17 +14753,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845D07A2-2AA6-45B3-BE31-54AE8B1671B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2E200A-CD34-46C1-A184-1C6ACEBFAF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1655,7 +1655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="505">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3304,146 +3304,151 @@
     <t>10.156.159.52</t>
   </si>
   <si>
+    <t>10.156.159.53</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-mqap01</t>
+  </si>
+  <si>
+    <t>10.156.159.60</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-mqweb01</t>
+  </si>
+  <si>
+    <t>10.156.159.70</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-oms01</t>
+  </si>
+  <si>
+    <t>10.156.159.80</t>
+  </si>
+  <si>
+    <t>hazr-d-dip-web01</t>
+  </si>
+  <si>
+    <t>10.156.159.90</t>
+  </si>
+  <si>
+    <t>hazr-d-com-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-com-auth01</t>
+  </si>
+  <si>
+    <t>10.156.162.10</t>
+  </si>
+  <si>
+    <t>d-com-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-com-proxy01</t>
+  </si>
+  <si>
+    <t>10.156.134.10</t>
+  </si>
+  <si>
+    <t>d-com-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-if-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-if-gramon01</t>
+  </si>
+  <si>
+    <t>10.156.165.10</t>
+  </si>
+  <si>
+    <t>d-if-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-cs-chtap01</t>
+  </si>
+  <si>
+    <t>10.156.168.10</t>
+  </si>
+  <si>
+    <t>d-cs-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-cs-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-cs-chtweb01</t>
+  </si>
+  <si>
+    <t>10.156.136.10</t>
+  </si>
+  <si>
+    <t>d-cs-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-cs-chtintweb01</t>
+  </si>
+  <si>
+    <t>10.156.168.20</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-web01</t>
+  </si>
+  <si>
+    <t>10.156.150.10</t>
+  </si>
+  <si>
+    <t>d-doip-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-ap01</t>
+  </si>
+  <si>
+    <t>10.156.150.20</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-adm01</t>
+  </si>
+  <si>
+    <t>10.156.150.30</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkweb01</t>
+  </si>
+  <si>
+    <t>10.156.132.10</t>
+  </si>
+  <si>
+    <t>d-bdp-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkap01</t>
+  </si>
+  <si>
+    <t>10.156.156.50</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkml01</t>
+  </si>
+  <si>
+    <t>10.156.156.60</t>
+  </si>
+  <si>
+    <t>StandardSSD_LRS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>hazr-d-dip-kfk02</t>
-  </si>
-  <si>
-    <t>10.156.159.53</t>
-  </si>
-  <si>
-    <t>hazr-d-dip-mqap01</t>
-  </si>
-  <si>
-    <t>10.156.159.60</t>
-  </si>
-  <si>
-    <t>hazr-d-dip-mqweb01</t>
-  </si>
-  <si>
-    <t>10.156.159.70</t>
-  </si>
-  <si>
-    <t>hazr-d-dip-oms01</t>
-  </si>
-  <si>
-    <t>10.156.159.80</t>
-  </si>
-  <si>
-    <t>hazr-d-dip-web01</t>
-  </si>
-  <si>
-    <t>10.156.159.90</t>
-  </si>
-  <si>
-    <t>hazr-d-com-rg</t>
-  </si>
-  <si>
-    <t>hazr-d-com-auth01</t>
-  </si>
-  <si>
-    <t>10.156.162.10</t>
-  </si>
-  <si>
-    <t>d-com-ap-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-com-proxy01</t>
-  </si>
-  <si>
-    <t>10.156.134.10</t>
-  </si>
-  <si>
-    <t>d-com-web-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-if-rg</t>
-  </si>
-  <si>
-    <t>hazr-d-if-gramon01</t>
-  </si>
-  <si>
-    <t>10.156.165.10</t>
-  </si>
-  <si>
-    <t>d-if-ap-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-cs-chtap01</t>
-  </si>
-  <si>
-    <t>10.156.168.10</t>
-  </si>
-  <si>
-    <t>d-cs-ap-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-cs-rg</t>
-  </si>
-  <si>
-    <t>hazr-d-cs-chtweb01</t>
-  </si>
-  <si>
-    <t>10.156.136.10</t>
-  </si>
-  <si>
-    <t>d-cs-web-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-cs-chtintweb01</t>
-  </si>
-  <si>
-    <t>10.156.168.20</t>
-  </si>
-  <si>
-    <t>hazr-d-doip-rg</t>
-  </si>
-  <si>
-    <t>hazr-d-doip-web01</t>
-  </si>
-  <si>
-    <t>10.156.150.10</t>
-  </si>
-  <si>
-    <t>d-doip-ap-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-doip-ap01</t>
-  </si>
-  <si>
-    <t>10.156.150.20</t>
-  </si>
-  <si>
-    <t>hazr-d-doip-adm01</t>
-  </si>
-  <si>
-    <t>10.156.150.30</t>
-  </si>
-  <si>
-    <t>hazr-d-bdp-crkweb01</t>
-  </si>
-  <si>
-    <t>10.156.132.10</t>
-  </si>
-  <si>
-    <t>d-bdp-web-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-bdp-crkap01</t>
-  </si>
-  <si>
-    <t>10.156.156.50</t>
-  </si>
-  <si>
-    <t>hazr-d-bdp-crkml01</t>
-  </si>
-  <si>
-    <t>10.156.156.60</t>
-  </si>
-  <si>
-    <t>StandardSSD_LRS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-kfk03</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5042,7 +5047,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:AA70" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A1:AA70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A1:AA70" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="DIP"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="54"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="53">
@@ -6493,7 +6504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -6542,7 +6553,7 @@
         <v>64</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -6569,7 +6580,7 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>82</v>
       </c>
@@ -6618,7 +6629,7 @@
         <v>64</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -6645,7 +6656,7 @@
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>82</v>
       </c>
@@ -6694,7 +6705,7 @@
         <v>64</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
@@ -6721,7 +6732,7 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>82</v>
       </c>
@@ -6770,7 +6781,7 @@
         <v>64</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -6797,7 +6808,7 @@
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
@@ -6846,7 +6857,7 @@
         <v>64</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
@@ -6873,7 +6884,7 @@
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>82</v>
       </c>
@@ -6922,7 +6933,7 @@
         <v>64</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
@@ -6949,7 +6960,7 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>82</v>
       </c>
@@ -6998,7 +7009,7 @@
         <v>64</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
@@ -7025,7 +7036,7 @@
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>82</v>
       </c>
@@ -7074,7 +7085,7 @@
         <v>64</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -7101,7 +7112,7 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>82</v>
       </c>
@@ -7150,7 +7161,7 @@
         <v>64</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -7177,7 +7188,7 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
@@ -7226,7 +7237,7 @@
         <v>64</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -7253,7 +7264,7 @@
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>82</v>
       </c>
@@ -7302,7 +7313,7 @@
         <v>64</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -7329,7 +7340,7 @@
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>82</v>
       </c>
@@ -7378,7 +7389,7 @@
         <v>64</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -7405,7 +7416,7 @@
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>82</v>
       </c>
@@ -7454,7 +7465,7 @@
         <v>64</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
@@ -7481,7 +7492,7 @@
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,7 +7541,7 @@
         <v>64</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -7557,7 +7568,7 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>82</v>
       </c>
@@ -7606,7 +7617,7 @@
         <v>64</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -7633,7 +7644,7 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>82</v>
       </c>
@@ -7682,7 +7693,7 @@
         <v>64</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -7709,7 +7720,7 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,7 +7769,7 @@
         <v>64</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -7785,7 +7796,7 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
@@ -7834,7 +7845,7 @@
         <v>64</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -7861,7 +7872,7 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
@@ -7910,7 +7921,7 @@
         <v>64</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -7937,7 +7948,7 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,7 +7997,7 @@
         <v>64</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -8013,7 +8024,7 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
@@ -8062,7 +8073,7 @@
         <v>64</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -8089,7 +8100,7 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
@@ -8138,7 +8149,7 @@
         <v>64</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -8165,7 +8176,7 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -8214,7 +8225,7 @@
         <v>64</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -8241,7 +8252,7 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
@@ -8290,7 +8301,7 @@
         <v>64</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
@@ -8317,7 +8328,7 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -8366,7 +8377,7 @@
         <v>64</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
@@ -8393,7 +8404,7 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -8442,7 +8453,7 @@
         <v>64</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
@@ -8469,7 +8480,7 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
@@ -8518,7 +8529,7 @@
         <v>64</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
@@ -8545,7 +8556,7 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -8594,7 +8605,7 @@
         <v>64</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
@@ -8621,7 +8632,7 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -8670,7 +8681,7 @@
         <v>64</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
@@ -8697,7 +8708,7 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -8746,7 +8757,7 @@
         <v>64</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
@@ -8773,7 +8784,7 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -8822,7 +8833,7 @@
         <v>64</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
@@ -8849,7 +8860,7 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -8898,7 +8909,7 @@
         <v>64</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
@@ -8925,7 +8936,7 @@
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -8974,7 +8985,7 @@
         <v>64</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
@@ -9001,7 +9012,7 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -9050,7 +9061,7 @@
         <v>64</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
@@ -9077,7 +9088,7 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -9126,7 +9137,7 @@
         <v>64</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
@@ -9153,7 +9164,7 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>82</v>
       </c>
@@ -9202,7 +9213,7 @@
         <v>64</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -9229,7 +9240,7 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>82</v>
       </c>
@@ -9278,7 +9289,7 @@
         <v>64</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
@@ -9305,7 +9316,7 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>82</v>
       </c>
@@ -9354,7 +9365,7 @@
         <v>64</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
@@ -9381,7 +9392,7 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>82</v>
       </c>
@@ -9430,7 +9441,7 @@
         <v>64</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
@@ -9457,7 +9468,7 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -9506,7 +9517,7 @@
         <v>64</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
@@ -9533,7 +9544,7 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -9582,7 +9593,7 @@
         <v>64</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
@@ -9609,7 +9620,7 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>82</v>
       </c>
@@ -9658,7 +9669,7 @@
         <v>64</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
@@ -9685,7 +9696,7 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>82</v>
       </c>
@@ -9734,7 +9745,7 @@
         <v>64</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
@@ -9761,7 +9772,7 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>82</v>
       </c>
@@ -9810,7 +9821,7 @@
         <v>64</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
@@ -9846,7 +9857,7 @@
         <v>DIP</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>24</v>
@@ -9886,7 +9897,7 @@
         <v>64</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
@@ -9922,7 +9933,7 @@
         <v>DIP</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>24</v>
@@ -9962,7 +9973,7 @@
         <v>64</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
@@ -9998,7 +10009,7 @@
         <v>DIP</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>24</v>
@@ -10038,7 +10049,7 @@
         <v>64</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
@@ -10074,7 +10085,7 @@
         <v>DIP</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>24</v>
@@ -10114,7 +10125,7 @@
         <v>64</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
@@ -10150,7 +10161,7 @@
         <v>DIP</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>24</v>
@@ -10190,7 +10201,7 @@
         <v>64</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
@@ -10226,7 +10237,7 @@
         <v>DIP</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>24</v>
@@ -10266,7 +10277,7 @@
         <v>64</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
@@ -10302,7 +10313,7 @@
         <v>DIP</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>24</v>
@@ -10342,7 +10353,7 @@
         <v>64</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
@@ -10378,13 +10389,13 @@
         <v>DIP</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>456</v>
@@ -10412,20 +10423,20 @@
       </c>
       <c r="N53" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>d-dip-kfk01-osdisk</v>
+        <v>d-dip-kfk02-osdisk</v>
       </c>
       <c r="O53" s="1">
         <v>64</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>d-dip-kfk01-nic</v>
+        <v>d-dip-kfk02-nic</v>
       </c>
       <c r="U53" s="1" t="b">
         <v>1</v>
@@ -10454,16 +10465,16 @@
         <v>DIP</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="G54" s="87" t="s">
         <v>348</v>
@@ -10488,20 +10499,20 @@
       </c>
       <c r="N54" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>d-dip-kfk02-osdisk</v>
+        <v>d-dip-kfk03-osdisk</v>
       </c>
       <c r="O54" s="1">
         <v>64</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q54" s="1"/>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
       <c r="T54" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>d-dip-kfk02-nic</v>
+        <v>d-dip-kfk03-nic</v>
       </c>
       <c r="U54" s="1" t="b">
         <v>1</v>
@@ -10530,16 +10541,16 @@
         <v>DIP</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>460</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>348</v>
@@ -10570,7 +10581,7 @@
         <v>64</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q55" s="1"/>
       <c r="R55" s="1"/>
@@ -10606,16 +10617,16 @@
         <v>DIP</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>461</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="G56" s="87" t="s">
         <v>348</v>
@@ -10646,7 +10657,7 @@
         <v>64</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
@@ -10682,16 +10693,16 @@
         <v>DIP</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="G57" s="87" t="s">
         <v>348</v>
@@ -10722,7 +10733,7 @@
         <v>64</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
@@ -10758,16 +10769,16 @@
         <v>DIP</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>348</v>
@@ -10798,7 +10809,7 @@
         <v>64</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q58" s="1"/>
       <c r="R58" s="1"/>
@@ -10825,7 +10836,7 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>82</v>
       </c>
@@ -10834,16 +10845,16 @@
         <v>COM</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="G59" s="87" t="s">
         <v>348</v>
@@ -10874,7 +10885,7 @@
         <v>64</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q59" s="1"/>
       <c r="R59" s="1"/>
@@ -10893,7 +10904,7 @@
         <v>339</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Y59" s="1">
         <v>1</v>
@@ -10901,7 +10912,7 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>82</v>
       </c>
@@ -10910,16 +10921,16 @@
         <v>COM</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E60" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>472</v>
       </c>
       <c r="G60" s="87" t="s">
         <v>348</v>
@@ -10950,7 +10961,7 @@
         <v>64</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q60" s="1"/>
       <c r="R60" s="1"/>
@@ -10969,7 +10980,7 @@
         <v>350</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Y60" s="1">
         <v>1</v>
@@ -10977,7 +10988,7 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>82</v>
       </c>
@@ -10986,16 +10997,16 @@
         <v>IF</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>348</v>
@@ -11026,7 +11037,7 @@
         <v>64</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q61" s="1"/>
       <c r="R61" s="1"/>
@@ -11045,7 +11056,7 @@
         <v>339</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Y61" s="1">
         <v>1</v>
@@ -11053,7 +11064,7 @@
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>82</v>
       </c>
@@ -11062,16 +11073,16 @@
         <v>COM</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>478</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>479</v>
       </c>
       <c r="G62" s="87" t="s">
         <v>348</v>
@@ -11102,7 +11113,7 @@
         <v>64</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q62" s="1"/>
       <c r="R62" s="1"/>
@@ -11121,7 +11132,7 @@
         <v>339</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Y62" s="1">
         <v>1</v>
@@ -11129,7 +11140,7 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>82</v>
       </c>
@@ -11138,16 +11149,16 @@
         <v>CS</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="G63" s="87" t="s">
         <v>348</v>
@@ -11178,7 +11189,7 @@
         <v>64</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q63" s="1"/>
       <c r="R63" s="1"/>
@@ -11197,7 +11208,7 @@
         <v>350</v>
       </c>
       <c r="X63" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Y63" s="1">
         <v>1</v>
@@ -11205,7 +11216,7 @@
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>82</v>
       </c>
@@ -11214,16 +11225,16 @@
         <v>CS</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>486</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>348</v>
@@ -11254,7 +11265,7 @@
         <v>64</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q64" s="1"/>
       <c r="R64" s="1"/>
@@ -11273,7 +11284,7 @@
         <v>339</v>
       </c>
       <c r="X64" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Y64" s="1">
         <v>1</v>
@@ -11281,7 +11292,7 @@
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>82</v>
       </c>
@@ -11290,16 +11301,16 @@
         <v>DOIP</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="G65" s="87" t="s">
         <v>348</v>
@@ -11330,7 +11341,7 @@
         <v>64</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q65" s="1"/>
       <c r="R65" s="1"/>
@@ -11349,7 +11360,7 @@
         <v>339</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Y65" s="1">
         <v>1</v>
@@ -11357,7 +11368,7 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>82</v>
       </c>
@@ -11366,16 +11377,16 @@
         <v>DOIP</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="G66" s="87" t="s">
         <v>348</v>
@@ -11406,7 +11417,7 @@
         <v>64</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
@@ -11425,7 +11436,7 @@
         <v>339</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Y66" s="1">
         <v>1</v>
@@ -11433,7 +11444,7 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>82</v>
       </c>
@@ -11442,16 +11453,16 @@
         <v>DOIP</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>348</v>
@@ -11482,7 +11493,7 @@
         <v>64</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q67" s="1"/>
       <c r="R67" s="1"/>
@@ -11501,7 +11512,7 @@
         <v>339</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Y67" s="1">
         <v>1</v>
@@ -11509,7 +11520,7 @@
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>82</v>
       </c>
@@ -11524,10 +11535,10 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>495</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>496</v>
       </c>
       <c r="G68" s="87" t="s">
         <v>348</v>
@@ -11558,7 +11569,7 @@
         <v>64</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q68" s="1"/>
       <c r="R68" s="1"/>
@@ -11577,7 +11588,7 @@
         <v>350</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y68" s="1">
         <v>1</v>
@@ -11585,7 +11596,7 @@
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>82</v>
       </c>
@@ -11600,10 +11611,10 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="G69" s="87" t="s">
         <v>348</v>
@@ -11634,7 +11645,7 @@
         <v>64</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
@@ -11661,7 +11672,7 @@
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>82</v>
       </c>
@@ -11676,10 +11687,10 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>348</v>
@@ -11710,7 +11721,7 @@
         <v>64</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
@@ -14560,9 +14571,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14710,26 +14724,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14753,9 +14756,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2E200A-CD34-46C1-A184-1C6ACEBFAF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F839C47-58A8-42F3-8362-9E960DB6316F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1655,7 +1655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="506">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3449,6 +3449,10 @@
   </si>
   <si>
     <t>hazr-d-dip-kfk03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5047,13 +5051,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:AA70" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A1:AA70" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="DIP"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AA70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="54"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="53">
@@ -6504,7 +6502,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
@@ -6580,7 +6578,7 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>82</v>
       </c>
@@ -6656,7 +6654,7 @@
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
     </row>
-    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>82</v>
       </c>
@@ -6732,7 +6730,7 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
-    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>82</v>
       </c>
@@ -6808,7 +6806,7 @@
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
     </row>
-    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>82</v>
       </c>
@@ -6884,7 +6882,7 @@
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
-    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>82</v>
       </c>
@@ -6960,7 +6958,7 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>82</v>
       </c>
@@ -7036,7 +7034,7 @@
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
     </row>
-    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>82</v>
       </c>
@@ -7112,7 +7110,7 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
-    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>82</v>
       </c>
@@ -7188,7 +7186,7 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
@@ -7264,7 +7262,7 @@
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
     </row>
-    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>82</v>
       </c>
@@ -7340,7 +7338,7 @@
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
     </row>
-    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>82</v>
       </c>
@@ -7416,7 +7414,7 @@
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
     </row>
-    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>82</v>
       </c>
@@ -7492,7 +7490,7 @@
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
     </row>
-    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>82</v>
       </c>
@@ -7568,7 +7566,7 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>82</v>
       </c>
@@ -7644,7 +7642,7 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>82</v>
       </c>
@@ -7720,7 +7718,7 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>82</v>
       </c>
@@ -7796,7 +7794,7 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
@@ -7872,7 +7870,7 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
@@ -7948,7 +7946,7 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -8024,7 +8022,7 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
@@ -8100,7 +8098,7 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
@@ -8176,7 +8174,7 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
@@ -8252,7 +8250,7 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>82</v>
       </c>
@@ -8328,7 +8326,7 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -8404,7 +8402,7 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>82</v>
       </c>
@@ -8480,7 +8478,7 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>82</v>
       </c>
@@ -8556,7 +8554,7 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -8632,7 +8630,7 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>82</v>
       </c>
@@ -8708,7 +8706,7 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>82</v>
       </c>
@@ -8784,7 +8782,7 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -8860,7 +8858,7 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
     </row>
-    <row r="33" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>82</v>
       </c>
@@ -8936,7 +8934,7 @@
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
     </row>
-    <row r="34" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -9012,7 +9010,7 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -9088,7 +9086,7 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>82</v>
       </c>
@@ -9164,7 +9162,7 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>82</v>
       </c>
@@ -9240,7 +9238,7 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>82</v>
       </c>
@@ -9316,7 +9314,7 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>82</v>
       </c>
@@ -9392,7 +9390,7 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>82</v>
       </c>
@@ -9468,7 +9466,7 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -9544,7 +9542,7 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -9620,7 +9618,7 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>82</v>
       </c>
@@ -9696,7 +9694,7 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
     </row>
-    <row r="44" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>82</v>
       </c>
@@ -9772,7 +9770,7 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>82</v>
       </c>
@@ -10836,7 +10834,7 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
-    <row r="59" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>82</v>
       </c>
@@ -10912,7 +10910,7 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
     </row>
-    <row r="60" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>82</v>
       </c>
@@ -10988,7 +10986,7 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
-    <row r="61" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>82</v>
       </c>
@@ -11064,16 +11062,15 @@
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
     </row>
-    <row r="62" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="1" t="str" cm="1">
-        <f t="array" ref="B62">UPPER(INDEX(_xlfn.TEXTSPLIT($C62, "-"), 3))</f>
-        <v>COM</v>
+      <c r="B62" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>466</v>
+        <v>190</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>24</v>
@@ -11140,7 +11137,7 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
     </row>
-    <row r="63" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>82</v>
       </c>
@@ -11216,7 +11213,7 @@
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
     </row>
-    <row r="64" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>82</v>
       </c>
@@ -11292,7 +11289,7 @@
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
     </row>
-    <row r="65" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>82</v>
       </c>
@@ -11368,7 +11365,7 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
     </row>
-    <row r="66" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>82</v>
       </c>
@@ -11444,7 +11441,7 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
     </row>
-    <row r="67" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>82</v>
       </c>
@@ -11520,7 +11517,7 @@
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
     </row>
-    <row r="68" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>82</v>
       </c>
@@ -11596,7 +11593,7 @@
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
     </row>
-    <row r="69" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>82</v>
       </c>
@@ -11672,7 +11669,7 @@
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
     </row>
-    <row r="70" spans="1:27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>82</v>
       </c>
@@ -14571,12 +14568,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14724,15 +14718,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14756,17 +14761,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CDF7CC-03A0-40E9-A515-1330145A42F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33ABFD4F-BB12-4118-A1F3-9519AC92B6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1655,7 +1655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="531">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3517,40 +3517,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>260417-test-rg</t>
-  </si>
-  <si>
     <t>temp-vm02</t>
   </si>
   <si>
     <t>10.156.156.246</t>
   </si>
   <si>
-    <t>260418-test-rg</t>
-  </si>
-  <si>
     <t>temp-vm03</t>
   </si>
   <si>
     <t>10.156.156.247</t>
   </si>
   <si>
-    <t>260419-test-rg</t>
-  </si>
-  <si>
     <t>temp-vm04</t>
   </si>
   <si>
     <t>10.156.156.248</t>
   </si>
   <si>
-    <t>260420-test-rg</t>
-  </si>
-  <si>
     <t>temp-vm05</t>
   </si>
   <si>
     <t>10.156.156.249</t>
+  </si>
+  <si>
+    <t>260416-test-rg</t>
   </si>
 </sst>
 </file>
@@ -3981,7 +3972,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4246,25 +4237,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4272,22 +4254,6 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="57">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4872,6 +4838,22 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5214,58 +5196,58 @@
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="39"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="38"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="37"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="0"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="36">
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="36"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="35">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="34"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="33"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="32"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="31"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="30"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="33"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="32"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="31"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="30"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="29"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DBC02633-0386-420C-92E0-C4AA8D0BE61C}" name="표1_3" displayName="표1_3" ref="A1:Z5" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:Z5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="22"/>
-    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="21"/>
-    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="20"/>
-    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{4CED117F-26CE-4E02-9C3D-FCDC9A3A6AE3}" name="Stage" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{F5B3ECA3-C35E-4862-9CF8-9DF645B874B0}" name="RGname" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{D3BFF33A-D12D-46A3-AF34-B72CEEF3A7CC}" name="Location" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{B2614111-FEE0-4B84-BBCD-D914905D5A3A}" name="Name" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{D5D518E8-A2B6-451B-A65E-A929C8F6553A}" name="PrivateIP" dataDxfId="21"/>
+    <tableColumn id="22" xr3:uid="{2581E355-2962-46E9-A9CD-E188E57E41A6}" name="VmSize" dataDxfId="20"/>
+    <tableColumn id="23" xr3:uid="{A5DB8AB4-722C-450A-AC8D-5AC9DA9EACB7}" name="CPU" dataDxfId="19"/>
+    <tableColumn id="34" xr3:uid="{AFE7E843-66BB-47B6-9247-9D29BAD8807D}" name="RAM" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{59C4B219-83F6-4EFE-A394-B255CDFFD45B}" name="AdminUsername" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{2AE885CB-4D7C-4D96-AFF3-793DDA444A94}" name="AdminPassword" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{212247ED-E787-4308-9B76-EF6B13719266}" name="OsType" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{2CDD36D5-D8B1-4584-AB69-420D4C9BC0A1}" name="ImageResourceId" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{15E01662-969C-4596-AB4A-4FBA9BFA4DAE}" name="OsDiskName" dataDxfId="13">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="11">
+    <tableColumn id="13" xr3:uid="{BC8FF9DF-82E6-48EA-BA69-9E00AFF25613}" name="OsDiskSize" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{894720E0-82E8-439C-974E-33B231EFD52A}" name="OsDiskStorageType" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{0B80057F-26E7-4557-B5A3-CCC0B84D937C}" name="DataDiskName" dataDxfId="10">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-disk"&amp;"01"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="10"/>
-    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="8">
+    <tableColumn id="25" xr3:uid="{945A8D40-5286-40B8-A779-096BAACCE422}" name="DataDiskSize" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{9CD555CE-BA32-467A-BA54-CB67AAB6EADF}" name="DataDiskStorageType" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{C5A2122F-7340-4899-BAFD-5F7A71064D06}" name="NicName" dataDxfId="7">
       <calculatedColumnFormula>SUBSTITUTE(D2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{DDCE5B2F-7877-41D1-BFCD-B37FDEB60FA8}" name="IsStatic" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{6CD99E95-D86C-472B-8ED2-70C1BC48947D}" name="VnetRG" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{AC696498-1001-4F87-BC49-E0176818EA0B}" name="VnetName" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{DA61F538-5D93-44DA-B85F-CE2922D16433}" name="SubnetName" dataDxfId="3"/>
+    <tableColumn id="36" xr3:uid="{1D9FEDCC-DD30-4690-9FB5-589483A2C9D1}" name="Zones" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{97BCCD92-07E3-456A-93D5-1C6B667C8898}" name="SubscriptionName" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{ADB2288C-1F40-4671-920F-0D5C366F8F7A}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5823,7 +5805,7 @@
       </c>
     </row>
     <row r="2" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="56" t="s">
         <v>82</v>
       </c>
@@ -5936,7 +5918,7 @@
       <c r="BK2" s="52"/>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A3" s="92"/>
+      <c r="A3" s="90"/>
       <c r="B3" s="56" t="s">
         <v>82</v>
       </c>
@@ -6123,7 +6105,6 @@
       </c>
     </row>
     <row r="4" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A4" s="93"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -6161,206 +6142,8 @@
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
     </row>
-    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A5" s="93"/>
-    </row>
-    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A6" s="93"/>
-    </row>
-    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A7" s="93"/>
-    </row>
-    <row r="8" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A8" s="93"/>
-    </row>
-    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A9" s="93"/>
-    </row>
-    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A10" s="93"/>
-    </row>
-    <row r="11" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A11" s="93"/>
-    </row>
-    <row r="12" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
-    </row>
-    <row r="13" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A13" s="93"/>
-    </row>
-    <row r="14" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A14" s="93"/>
-    </row>
-    <row r="15" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A15" s="93"/>
-    </row>
-    <row r="16" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A16" s="93"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="93"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="93"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="93"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="93"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="93"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="93"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="93"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="93"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="93"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="93"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="93"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="93"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="93"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="93"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="93"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="93"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="93"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="93"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="93"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="93"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="93"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="93"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="93"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="93"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="93"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="93"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="93"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="93"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="93"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="93"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="93"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="93"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="93"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="93"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="93"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="93"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="93"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="93"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="93"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="93"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="93"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="93"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="93"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="93"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="93"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="93"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="93"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="93"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="93"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="93"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="93"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="93"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="93"/>
-    </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="94"/>
+      <c r="A71" s="91"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6558,7 +6341,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="56" t="s">
         <v>82</v>
       </c>
@@ -6574,7 +6357,7 @@
       <c r="F2" s="56"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="92"/>
+      <c r="A3" s="90"/>
       <c r="B3" s="56" t="s">
         <v>82</v>
       </c>
@@ -6590,7 +6373,7 @@
       <c r="F3" s="56"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="89"/>
+      <c r="A4" s="88"/>
       <c r="B4" s="56" t="s">
         <v>82</v>
       </c>
@@ -6606,7 +6389,7 @@
       <c r="F4" s="56"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="92"/>
+      <c r="A5" s="90"/>
       <c r="B5" s="56" t="s">
         <v>82</v>
       </c>
@@ -6622,7 +6405,7 @@
       <c r="F5" s="56"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="89"/>
+      <c r="A6" s="88"/>
       <c r="B6" s="56" t="s">
         <v>82</v>
       </c>
@@ -6638,7 +6421,7 @@
       <c r="F6" s="56"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="92"/>
+      <c r="A7" s="90"/>
       <c r="B7" s="56" t="s">
         <v>82</v>
       </c>
@@ -6654,7 +6437,7 @@
       <c r="F7" s="56"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="89"/>
+      <c r="A8" s="88"/>
       <c r="B8" s="56" t="s">
         <v>82</v>
       </c>
@@ -6670,219 +6453,39 @@
       <c r="F8" s="56"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="89"/>
-      <c r="B9" s="91" t="s">
+      <c r="A9" s="88"/>
+      <c r="B9" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="91" t="s">
+      <c r="C9" s="56" t="s">
         <v>515</v>
       </c>
-      <c r="D9" s="91" t="s">
+      <c r="D9" s="56" t="s">
         <v>331</v>
       </c>
-      <c r="E9" s="91" t="s">
+      <c r="E9" s="56" t="s">
         <v>24</v>
       </c>
       <c r="F9" s="52"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="92"/>
-      <c r="B10" s="91" t="s">
+      <c r="A10" s="90"/>
+      <c r="B10" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="91" t="s">
+      <c r="C10" s="56" t="s">
         <v>516</v>
       </c>
-      <c r="D10" s="91" t="s">
+      <c r="D10" s="56" t="s">
         <v>517</v>
       </c>
-      <c r="E10" s="91" t="s">
+      <c r="E10" s="56" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="52"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="93"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="93"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="93"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="93"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="93"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="93"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="93"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="93"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="93"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="93"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="93"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="93"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="93"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="93"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="93"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="93"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="93"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="93"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="93"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="93"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="93"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="93"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="93"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="93"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="93"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="93"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="93"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="93"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="93"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="93"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="93"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="93"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="93"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="93"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="93"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="93"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="93"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="93"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="93"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="93"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="93"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="93"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="93"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="93"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="93"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="93"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="93"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="93"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="93"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="93"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="93"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="93"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="93"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="93"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="93"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="93"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="93"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="93"/>
-    </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="94"/>
+      <c r="A71" s="91"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7010,7 +6613,7 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="1" t="s">
         <v>82</v>
       </c>
@@ -7087,7 +6690,7 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="89"/>
+      <c r="A3" s="88"/>
       <c r="B3" s="1" t="s">
         <v>82</v>
       </c>
@@ -7164,7 +6767,7 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="89"/>
+      <c r="A4" s="88"/>
       <c r="B4" s="1" t="s">
         <v>82</v>
       </c>
@@ -7241,7 +6844,7 @@
       <c r="AB4" s="1"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" s="89"/>
+      <c r="A5" s="88"/>
       <c r="B5" s="1" t="s">
         <v>82</v>
       </c>
@@ -7318,7 +6921,7 @@
       <c r="AB5" s="1"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="89"/>
+      <c r="A6" s="88"/>
       <c r="B6" s="1" t="s">
         <v>82</v>
       </c>
@@ -7395,7 +6998,7 @@
       <c r="AB6" s="1"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="89"/>
+      <c r="A7" s="88"/>
       <c r="B7" s="1" t="s">
         <v>82</v>
       </c>
@@ -7472,7 +7075,7 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="89"/>
+      <c r="A8" s="88"/>
       <c r="B8" s="1" t="s">
         <v>82</v>
       </c>
@@ -7549,7 +7152,7 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="89"/>
+      <c r="A9" s="88"/>
       <c r="B9" s="1" t="s">
         <v>82</v>
       </c>
@@ -7626,7 +7229,7 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="89"/>
+      <c r="A10" s="88"/>
       <c r="B10" s="1" t="s">
         <v>82</v>
       </c>
@@ -7703,7 +7306,7 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="89"/>
+      <c r="A11" s="88"/>
       <c r="B11" s="1" t="s">
         <v>82</v>
       </c>
@@ -7780,7 +7383,7 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="89"/>
+      <c r="A12" s="88"/>
       <c r="B12" s="1" t="s">
         <v>82</v>
       </c>
@@ -7857,7 +7460,7 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="89"/>
+      <c r="A13" s="88"/>
       <c r="B13" s="1" t="s">
         <v>82</v>
       </c>
@@ -7934,7 +7537,7 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="89"/>
+      <c r="A14" s="88"/>
       <c r="B14" s="1" t="s">
         <v>82</v>
       </c>
@@ -8011,7 +7614,7 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="89"/>
+      <c r="A15" s="88"/>
       <c r="B15" s="1" t="s">
         <v>82</v>
       </c>
@@ -8088,7 +7691,7 @@
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
+      <c r="A16" s="88"/>
       <c r="B16" s="1" t="s">
         <v>82</v>
       </c>
@@ -8165,7 +7768,7 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="89"/>
+      <c r="A17" s="88"/>
       <c r="B17" s="1" t="s">
         <v>82</v>
       </c>
@@ -8242,7 +7845,7 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="89"/>
+      <c r="A18" s="88"/>
       <c r="B18" s="1" t="s">
         <v>82</v>
       </c>
@@ -8319,7 +7922,7 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A19" s="89"/>
+      <c r="A19" s="88"/>
       <c r="B19" s="1" t="s">
         <v>82</v>
       </c>
@@ -8396,7 +7999,7 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="89"/>
+      <c r="A20" s="88"/>
       <c r="B20" s="1" t="s">
         <v>82</v>
       </c>
@@ -8473,7 +8076,7 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="1" t="s">
         <v>82</v>
       </c>
@@ -8550,7 +8153,7 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" s="89"/>
+      <c r="A22" s="88"/>
       <c r="B22" s="1" t="s">
         <v>82</v>
       </c>
@@ -8627,7 +8230,7 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
+      <c r="A23" s="88"/>
       <c r="B23" s="1" t="s">
         <v>82</v>
       </c>
@@ -8704,7 +8307,7 @@
       <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
+      <c r="A24" s="88"/>
       <c r="B24" s="1" t="s">
         <v>82</v>
       </c>
@@ -8781,7 +8384,7 @@
       <c r="AB24" s="1"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A25" s="89"/>
+      <c r="A25" s="88"/>
       <c r="B25" s="1" t="s">
         <v>82</v>
       </c>
@@ -8858,7 +8461,7 @@
       <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A26" s="89"/>
+      <c r="A26" s="88"/>
       <c r="B26" s="1" t="s">
         <v>82</v>
       </c>
@@ -8935,7 +8538,7 @@
       <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
+      <c r="A27" s="88"/>
       <c r="B27" s="1" t="s">
         <v>82</v>
       </c>
@@ -9012,7 +8615,7 @@
       <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
+      <c r="A28" s="88"/>
       <c r="B28" s="1" t="s">
         <v>82</v>
       </c>
@@ -9089,7 +8692,7 @@
       <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
+      <c r="A29" s="88"/>
       <c r="B29" s="1" t="s">
         <v>82</v>
       </c>
@@ -9166,7 +8769,7 @@
       <c r="AB29" s="1"/>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A30" s="89"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="1" t="s">
         <v>82</v>
       </c>
@@ -9243,7 +8846,7 @@
       <c r="AB30" s="1"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A31" s="89"/>
+      <c r="A31" s="88"/>
       <c r="B31" s="1" t="s">
         <v>82</v>
       </c>
@@ -9320,7 +8923,7 @@
       <c r="AB31" s="1"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" s="89"/>
+      <c r="A32" s="88"/>
       <c r="B32" s="1" t="s">
         <v>82</v>
       </c>
@@ -9397,7 +9000,7 @@
       <c r="AB32" s="1"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A33" s="89"/>
+      <c r="A33" s="88"/>
       <c r="B33" s="1" t="s">
         <v>82</v>
       </c>
@@ -9474,7 +9077,7 @@
       <c r="AB33" s="1"/>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A34" s="89"/>
+      <c r="A34" s="88"/>
       <c r="B34" s="1" t="s">
         <v>82</v>
       </c>
@@ -9551,7 +9154,7 @@
       <c r="AB34" s="1"/>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A35" s="89"/>
+      <c r="A35" s="88"/>
       <c r="B35" s="1" t="s">
         <v>82</v>
       </c>
@@ -9628,7 +9231,7 @@
       <c r="AB35" s="1"/>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A36" s="89"/>
+      <c r="A36" s="88"/>
       <c r="B36" s="1" t="s">
         <v>82</v>
       </c>
@@ -9705,7 +9308,7 @@
       <c r="AB36" s="1"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A37" s="89"/>
+      <c r="A37" s="88"/>
       <c r="B37" s="1" t="s">
         <v>82</v>
       </c>
@@ -9782,7 +9385,7 @@
       <c r="AB37" s="1"/>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A38" s="89"/>
+      <c r="A38" s="88"/>
       <c r="B38" s="1" t="s">
         <v>82</v>
       </c>
@@ -9859,7 +9462,7 @@
       <c r="AB38" s="1"/>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A39" s="89"/>
+      <c r="A39" s="88"/>
       <c r="B39" s="1" t="s">
         <v>82</v>
       </c>
@@ -9936,7 +9539,7 @@
       <c r="AB39" s="1"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A40" s="89"/>
+      <c r="A40" s="88"/>
       <c r="B40" s="1" t="s">
         <v>82</v>
       </c>
@@ -10013,7 +9616,7 @@
       <c r="AB40" s="1"/>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A41" s="89"/>
+      <c r="A41" s="88"/>
       <c r="B41" s="1" t="s">
         <v>82</v>
       </c>
@@ -10090,7 +9693,7 @@
       <c r="AB41" s="1"/>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A42" s="89"/>
+      <c r="A42" s="88"/>
       <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
@@ -10167,7 +9770,7 @@
       <c r="AB42" s="1"/>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A43" s="89"/>
+      <c r="A43" s="88"/>
       <c r="B43" s="1" t="s">
         <v>82</v>
       </c>
@@ -10244,7 +9847,7 @@
       <c r="AB43" s="1"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A44" s="89"/>
+      <c r="A44" s="88"/>
       <c r="B44" s="1" t="s">
         <v>82</v>
       </c>
@@ -10321,7 +9924,7 @@
       <c r="AB44" s="1"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A45" s="89"/>
+      <c r="A45" s="88"/>
       <c r="B45" s="1" t="s">
         <v>82</v>
       </c>
@@ -10398,7 +10001,7 @@
       <c r="AB45" s="1"/>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A46" s="89"/>
+      <c r="A46" s="88"/>
       <c r="B46" s="1" t="s">
         <v>82</v>
       </c>
@@ -10475,7 +10078,7 @@
       <c r="AB46" s="1"/>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A47" s="89"/>
+      <c r="A47" s="88"/>
       <c r="B47" s="1" t="s">
         <v>82</v>
       </c>
@@ -10552,7 +10155,7 @@
       <c r="AB47" s="1"/>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A48" s="89"/>
+      <c r="A48" s="88"/>
       <c r="B48" s="1" t="s">
         <v>82</v>
       </c>
@@ -10629,7 +10232,7 @@
       <c r="AB48" s="1"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A49" s="89"/>
+      <c r="A49" s="88"/>
       <c r="B49" s="1" t="s">
         <v>82</v>
       </c>
@@ -10706,7 +10309,7 @@
       <c r="AB49" s="1"/>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A50" s="89"/>
+      <c r="A50" s="88"/>
       <c r="B50" s="1" t="s">
         <v>82</v>
       </c>
@@ -10783,7 +10386,7 @@
       <c r="AB50" s="1"/>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A51" s="89"/>
+      <c r="A51" s="88"/>
       <c r="B51" s="1" t="s">
         <v>82</v>
       </c>
@@ -10860,7 +10463,7 @@
       <c r="AB51" s="1"/>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A52" s="89"/>
+      <c r="A52" s="88"/>
       <c r="B52" s="1" t="s">
         <v>82</v>
       </c>
@@ -10937,7 +10540,7 @@
       <c r="AB52" s="1"/>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A53" s="89"/>
+      <c r="A53" s="88"/>
       <c r="B53" s="1" t="s">
         <v>82</v>
       </c>
@@ -11014,7 +10617,7 @@
       <c r="AB53" s="1"/>
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A54" s="89"/>
+      <c r="A54" s="88"/>
       <c r="B54" s="1" t="s">
         <v>82</v>
       </c>
@@ -11091,7 +10694,7 @@
       <c r="AB54" s="1"/>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A55" s="89"/>
+      <c r="A55" s="88"/>
       <c r="B55" s="1" t="s">
         <v>82</v>
       </c>
@@ -11168,7 +10771,7 @@
       <c r="AB55" s="1"/>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A56" s="89"/>
+      <c r="A56" s="88"/>
       <c r="B56" s="1" t="s">
         <v>82</v>
       </c>
@@ -11245,7 +10848,7 @@
       <c r="AB56" s="1"/>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A57" s="89"/>
+      <c r="A57" s="88"/>
       <c r="B57" s="1" t="s">
         <v>82</v>
       </c>
@@ -11322,7 +10925,7 @@
       <c r="AB57" s="1"/>
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A58" s="89"/>
+      <c r="A58" s="88"/>
       <c r="B58" s="1" t="s">
         <v>82</v>
       </c>
@@ -11399,7 +11002,7 @@
       <c r="AB58" s="1"/>
     </row>
     <row r="59" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A59" s="89"/>
+      <c r="A59" s="88"/>
       <c r="B59" s="1" t="s">
         <v>82</v>
       </c>
@@ -11476,7 +11079,7 @@
       <c r="AB59" s="1"/>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A60" s="89"/>
+      <c r="A60" s="88"/>
       <c r="B60" s="1" t="s">
         <v>82</v>
       </c>
@@ -11553,7 +11156,7 @@
       <c r="AB60" s="1"/>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A61" s="89"/>
+      <c r="A61" s="88"/>
       <c r="B61" s="1" t="s">
         <v>82</v>
       </c>
@@ -11630,7 +11233,7 @@
       <c r="AB61" s="1"/>
     </row>
     <row r="62" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A62" s="89"/>
+      <c r="A62" s="88"/>
       <c r="B62" s="1" t="s">
         <v>82</v>
       </c>
@@ -11706,7 +11309,7 @@
       <c r="AB62" s="1"/>
     </row>
     <row r="63" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A63" s="89"/>
+      <c r="A63" s="88"/>
       <c r="B63" s="1" t="s">
         <v>82</v>
       </c>
@@ -11783,7 +11386,7 @@
       <c r="AB63" s="1"/>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A64" s="89"/>
+      <c r="A64" s="88"/>
       <c r="B64" s="1" t="s">
         <v>82</v>
       </c>
@@ -11860,7 +11463,7 @@
       <c r="AB64" s="1"/>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A65" s="89"/>
+      <c r="A65" s="88"/>
       <c r="B65" s="1" t="s">
         <v>82</v>
       </c>
@@ -11937,7 +11540,7 @@
       <c r="AB65" s="1"/>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A66" s="89"/>
+      <c r="A66" s="88"/>
       <c r="B66" s="1" t="s">
         <v>82</v>
       </c>
@@ -12014,7 +11617,7 @@
       <c r="AB66" s="1"/>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A67" s="89"/>
+      <c r="A67" s="88"/>
       <c r="B67" s="1" t="s">
         <v>82</v>
       </c>
@@ -12091,7 +11694,7 @@
       <c r="AB67" s="1"/>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A68" s="89"/>
+      <c r="A68" s="88"/>
       <c r="B68" s="1" t="s">
         <v>82</v>
       </c>
@@ -12168,7 +11771,7 @@
       <c r="AB68" s="1"/>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A69" s="89"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="1" t="s">
         <v>82</v>
       </c>
@@ -12245,7 +11848,7 @@
       <c r="AB69" s="1"/>
     </row>
     <row r="70" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A70" s="89"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="1" t="s">
         <v>82</v>
       </c>
@@ -12322,7 +11925,7 @@
       <c r="AB70" s="1"/>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A71" s="90"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="1" t="s">
         <v>82</v>
       </c>
@@ -12402,7 +12005,7 @@
       <c r="C72" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D72" s="88" t="s">
+      <c r="D72" s="1" t="s">
         <v>519</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -12435,7 +12038,7 @@
       <c r="N72" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="O72" s="88" t="str">
+      <c r="O72" s="1" t="str">
         <f>SUBSTITUTE(F72,"hazr-","")&amp;"-osdisk"</f>
         <v>temp-vm01-osdisk</v>
       </c>
@@ -12445,10 +12048,10 @@
       <c r="Q72" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R72" s="88"/>
+      <c r="R72" s="1"/>
       <c r="S72" s="1"/>
-      <c r="T72" s="88"/>
-      <c r="U72" s="88" t="str">
+      <c r="T72" s="1"/>
+      <c r="U72" s="1" t="str">
         <f>SUBSTITUTE(F72,"hazr-","")&amp;"-nic"</f>
         <v>temp-vm01-nic</v>
       </c>
@@ -12477,17 +12080,17 @@
       <c r="C73" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D73" s="88" t="s">
-        <v>522</v>
+      <c r="D73" s="1" t="s">
+        <v>519</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F73" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>524</v>
       </c>
       <c r="H73" s="87" t="s">
         <v>336</v>
@@ -12510,7 +12113,7 @@
       <c r="N73" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="O73" s="88" t="str">
+      <c r="O73" s="1" t="str">
         <f t="shared" ref="O73:O76" si="7">SUBSTITUTE(F73,"hazr-","")&amp;"-osdisk"</f>
         <v>temp-vm02-osdisk</v>
       </c>
@@ -12520,10 +12123,10 @@
       <c r="Q73" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R73" s="88"/>
+      <c r="R73" s="1"/>
       <c r="S73" s="1"/>
-      <c r="T73" s="88"/>
-      <c r="U73" s="88" t="str">
+      <c r="T73" s="1"/>
+      <c r="U73" s="1" t="str">
         <f t="shared" ref="U73:U76" si="8">SUBSTITUTE(F73,"hazr-","")&amp;"-nic"</f>
         <v>temp-vm02-nic</v>
       </c>
@@ -12552,17 +12155,17 @@
       <c r="C74" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D74" s="88" t="s">
-        <v>525</v>
+      <c r="D74" s="1" t="s">
+        <v>530</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H74" s="87" t="s">
         <v>336</v>
@@ -12585,7 +12188,7 @@
       <c r="N74" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="O74" s="88" t="str">
+      <c r="O74" s="1" t="str">
         <f t="shared" si="7"/>
         <v>temp-vm03-osdisk</v>
       </c>
@@ -12595,10 +12198,10 @@
       <c r="Q74" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R74" s="88"/>
+      <c r="R74" s="1"/>
       <c r="S74" s="1"/>
-      <c r="T74" s="88"/>
-      <c r="U74" s="88" t="str">
+      <c r="T74" s="1"/>
+      <c r="U74" s="1" t="str">
         <f t="shared" si="8"/>
         <v>temp-vm03-nic</v>
       </c>
@@ -12627,17 +12230,17 @@
       <c r="C75" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D75" s="88" t="s">
-        <v>528</v>
+      <c r="D75" s="1" t="s">
+        <v>530</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H75" s="87" t="s">
         <v>336</v>
@@ -12660,7 +12263,7 @@
       <c r="N75" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="O75" s="88" t="str">
+      <c r="O75" s="1" t="str">
         <f t="shared" si="7"/>
         <v>temp-vm04-osdisk</v>
       </c>
@@ -12670,10 +12273,10 @@
       <c r="Q75" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R75" s="88"/>
+      <c r="R75" s="1"/>
       <c r="S75" s="1"/>
-      <c r="T75" s="88"/>
-      <c r="U75" s="88" t="str">
+      <c r="T75" s="1"/>
+      <c r="U75" s="1" t="str">
         <f t="shared" si="8"/>
         <v>temp-vm04-nic</v>
       </c>
@@ -12702,17 +12305,17 @@
       <c r="C76" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D76" s="88" t="s">
-        <v>531</v>
+      <c r="D76" s="1" t="s">
+        <v>530</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H76" s="87" t="s">
         <v>336</v>
@@ -12735,7 +12338,7 @@
       <c r="N76" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="O76" s="88" t="str">
+      <c r="O76" s="1" t="str">
         <f t="shared" si="7"/>
         <v>temp-vm05-osdisk</v>
       </c>
@@ -12745,10 +12348,10 @@
       <c r="Q76" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R76" s="88"/>
+      <c r="R76" s="1"/>
       <c r="S76" s="1"/>
-      <c r="T76" s="88"/>
-      <c r="U76" s="88" t="str">
+      <c r="T76" s="1"/>
+      <c r="U76" s="1" t="str">
         <f t="shared" si="8"/>
         <v>temp-vm05-nic</v>
       </c>
@@ -15593,9 +15196,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15743,26 +15349,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15786,9 +15381,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33ABFD4F-BB12-4118-A1F3-9519AC92B6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EF6EC0-F8A4-4C9B-B60B-152069A18EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1655,7 +1655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="542">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3542,6 +3542,45 @@
   </si>
   <si>
     <t>260416-test-rg</t>
+  </si>
+  <si>
+    <t>temp-vm01-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-vm02-disk02</t>
+  </si>
+  <si>
+    <t>temp-vm02-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-vm01-disk02</t>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/Windows_Server_2025_Base_Image/versions/0.0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-vm03-disk02</t>
+  </si>
+  <si>
+    <t>temp-vm03-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-vm04-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-vm05-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-vm04-disk02</t>
+  </si>
+  <si>
+    <t>temp-vm05-disk02</t>
   </si>
 </sst>
 </file>
@@ -3711,13 +3750,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3972,7 +4011,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4237,16 +4276,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5918,7 +5960,7 @@
       <c r="BK2" s="52"/>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.3">
-      <c r="A3" s="90"/>
+      <c r="A3" s="89"/>
       <c r="B3" s="56" t="s">
         <v>82</v>
       </c>
@@ -6143,7 +6185,7 @@
       <c r="AK4" s="1"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="91"/>
+      <c r="A71" s="90"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6357,7 +6399,7 @@
       <c r="F2" s="56"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="90"/>
+      <c r="A3" s="89"/>
       <c r="B3" s="56" t="s">
         <v>82</v>
       </c>
@@ -6389,7 +6431,7 @@
       <c r="F4" s="56"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="90"/>
+      <c r="A5" s="89"/>
       <c r="B5" s="56" t="s">
         <v>82</v>
       </c>
@@ -6421,7 +6463,7 @@
       <c r="F6" s="56"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="90"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="56" t="s">
         <v>82</v>
       </c>
@@ -6469,7 +6511,7 @@
       <c r="F9" s="52"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
+      <c r="A10" s="89"/>
       <c r="B10" s="56" t="s">
         <v>82</v>
       </c>
@@ -6485,7 +6527,7 @@
       <c r="F10" s="52"/>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="91"/>
+      <c r="A71" s="90"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6515,8 +6557,7 @@
     <col min="15" max="15" width="19.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.625" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="21" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.25" bestFit="1" customWidth="1"/>
@@ -11887,7 +11928,7 @@
         <v>342</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="O70" s="1" t="str">
         <f t="shared" si="5"/>
@@ -11925,7 +11966,7 @@
       <c r="AB70" s="1"/>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A71" s="89"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="1" t="s">
         <v>82</v>
       </c>
@@ -11962,7 +12003,9 @@
       <c r="M71" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="N71" s="1"/>
+      <c r="N71" s="1" t="s">
+        <v>535</v>
+      </c>
       <c r="O71" s="1" t="str">
         <f>SUBSTITUTE(F71,"hazr-","")&amp;"-osdisk"</f>
         <v>d-dis-dfir01-osdisk</v>
@@ -11999,6 +12042,7 @@
       <c r="AB71" s="1"/>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A72" s="91"/>
       <c r="B72" s="1" t="s">
         <v>82</v>
       </c>
@@ -12048,8 +12092,12 @@
       <c r="Q72" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
+      <c r="R72" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="S72" s="1" t="s">
+        <v>534</v>
+      </c>
       <c r="T72" s="1"/>
       <c r="U72" s="1" t="str">
         <f>SUBSTITUTE(F72,"hazr-","")&amp;"-nic"</f>
@@ -12074,6 +12122,7 @@
       <c r="AB72" s="1"/>
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A73" s="91"/>
       <c r="B73" s="1" t="s">
         <v>82</v>
       </c>
@@ -12123,8 +12172,12 @@
       <c r="Q73" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R73" s="1"/>
-      <c r="S73" s="1"/>
+      <c r="R73" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="S73" s="1" t="s">
+        <v>532</v>
+      </c>
       <c r="T73" s="1"/>
       <c r="U73" s="1" t="str">
         <f t="shared" ref="U73:U76" si="8">SUBSTITUTE(F73,"hazr-","")&amp;"-nic"</f>
@@ -12149,6 +12202,7 @@
       <c r="AB73" s="1"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A74" s="91"/>
       <c r="B74" s="1" t="s">
         <v>82</v>
       </c>
@@ -12198,8 +12252,12 @@
       <c r="Q74" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R74" s="1"/>
-      <c r="S74" s="1"/>
+      <c r="R74" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="S74" s="1" t="s">
+        <v>536</v>
+      </c>
       <c r="T74" s="1"/>
       <c r="U74" s="1" t="str">
         <f t="shared" si="8"/>
@@ -12224,6 +12282,7 @@
       <c r="AB74" s="1"/>
     </row>
     <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A75" s="91"/>
       <c r="B75" s="1" t="s">
         <v>82</v>
       </c>
@@ -12273,8 +12332,12 @@
       <c r="Q75" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R75" s="1"/>
-      <c r="S75" s="1"/>
+      <c r="R75" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="S75" s="1" t="s">
+        <v>540</v>
+      </c>
       <c r="T75" s="1"/>
       <c r="U75" s="1" t="str">
         <f t="shared" si="8"/>
@@ -12299,6 +12362,7 @@
       <c r="AB75" s="1"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A76" s="91"/>
       <c r="B76" s="1" t="s">
         <v>82</v>
       </c>
@@ -12348,8 +12412,12 @@
       <c r="Q76" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
+      <c r="R76" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="S76" s="1" t="s">
+        <v>541</v>
+      </c>
       <c r="T76" s="1"/>
       <c r="U76" s="1" t="str">
         <f t="shared" si="8"/>
@@ -15196,12 +15264,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15349,15 +15414,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -15381,17 +15457,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EF6EC0-F8A4-4C9B-B60B-152069A18EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6DB724-40A8-4521-BD9A-23066B79951C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1655,7 +1655,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="548">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3462,9 +3462,6 @@
     <t>10.156.144.130</t>
   </si>
   <si>
-    <t>Windows</t>
-  </si>
-  <si>
     <t>DIS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3581,6 +3578,32 @@
   </si>
   <si>
     <t>temp-vm05-disk02</t>
+  </si>
+  <si>
+    <t>Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hwgiifadmin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-vm06</t>
+  </si>
+  <si>
+    <t>10.156.156.250</t>
+  </si>
+  <si>
+    <t>temp-vm06-disk02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-vm06-disk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ABC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5213,8 +5236,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AB76" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="B1:AB76" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AB77" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+  <autoFilter ref="B1:AB77" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="54"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="53">
@@ -6388,7 +6411,7 @@
         <v>82</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D2" s="56" t="s">
         <v>188</v>
@@ -6404,7 +6427,7 @@
         <v>82</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D3" s="56" t="s">
         <v>189</v>
@@ -6436,7 +6459,7 @@
         <v>82</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D5" s="56" t="s">
         <v>191</v>
@@ -6452,7 +6475,7 @@
         <v>82</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D6" s="56" t="s">
         <v>192</v>
@@ -6468,7 +6491,7 @@
         <v>82</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D7" s="56" t="s">
         <v>193</v>
@@ -6484,7 +6507,7 @@
         <v>82</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D8" s="56" t="s">
         <v>194</v>
@@ -6500,7 +6523,7 @@
         <v>82</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D9" s="56" t="s">
         <v>331</v>
@@ -6516,10 +6539,10 @@
         <v>82</v>
       </c>
       <c r="C10" s="56" t="s">
+        <v>515</v>
+      </c>
+      <c r="D10" s="56" t="s">
         <v>516</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>517</v>
       </c>
       <c r="E10" s="56" t="s">
         <v>24</v>
@@ -6537,7 +6560,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB76"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -6684,7 +6707,7 @@
         <v>8</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>321</v>
@@ -6761,7 +6784,7 @@
         <v>8</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L3" s="86" t="s">
         <v>321</v>
@@ -6838,7 +6861,7 @@
         <v>8</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>320</v>
@@ -6915,7 +6938,7 @@
         <v>8</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L5" s="86" t="s">
         <v>320</v>
@@ -6992,7 +7015,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>320</v>
@@ -7069,7 +7092,7 @@
         <v>8</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L7" s="86" t="s">
         <v>320</v>
@@ -7146,7 +7169,7 @@
         <v>8</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>320</v>
@@ -7223,7 +7246,7 @@
         <v>8</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L9" s="86" t="s">
         <v>320</v>
@@ -7300,7 +7323,7 @@
         <v>8</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>320</v>
@@ -7377,7 +7400,7 @@
         <v>8</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L11" s="86" t="s">
         <v>320</v>
@@ -7454,7 +7477,7 @@
         <v>8</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>320</v>
@@ -7531,7 +7554,7 @@
         <v>8</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L13" s="86" t="s">
         <v>320</v>
@@ -7608,7 +7631,7 @@
         <v>8</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>320</v>
@@ -7685,7 +7708,7 @@
         <v>8</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L15" s="86" t="s">
         <v>320</v>
@@ -7762,7 +7785,7 @@
         <v>8</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>320</v>
@@ -7839,7 +7862,7 @@
         <v>8</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L17" s="86" t="s">
         <v>320</v>
@@ -7916,7 +7939,7 @@
         <v>8</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L18" s="86" t="s">
         <v>320</v>
@@ -7993,7 +8016,7 @@
         <v>8</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>320</v>
@@ -8070,7 +8093,7 @@
         <v>8</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L20" s="86" t="s">
         <v>320</v>
@@ -8147,7 +8170,7 @@
         <v>8</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>320</v>
@@ -8224,7 +8247,7 @@
         <v>8</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L22" s="86" t="s">
         <v>320</v>
@@ -8301,7 +8324,7 @@
         <v>8</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>320</v>
@@ -8378,7 +8401,7 @@
         <v>8</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L24" s="86" t="s">
         <v>320</v>
@@ -8455,7 +8478,7 @@
         <v>8</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>320</v>
@@ -8532,7 +8555,7 @@
         <v>32</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L26" s="86" t="s">
         <v>320</v>
@@ -8609,7 +8632,7 @@
         <v>8</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>320</v>
@@ -8686,7 +8709,7 @@
         <v>8</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L28" s="86" t="s">
         <v>320</v>
@@ -8763,7 +8786,7 @@
         <v>8</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>320</v>
@@ -8840,7 +8863,7 @@
         <v>8</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L30" s="86" t="s">
         <v>320</v>
@@ -8917,7 +8940,7 @@
         <v>8</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>320</v>
@@ -8994,7 +9017,7 @@
         <v>8</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L32" s="86" t="s">
         <v>320</v>
@@ -9071,7 +9094,7 @@
         <v>8</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>320</v>
@@ -9148,7 +9171,7 @@
         <v>8</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L34" s="86" t="s">
         <v>320</v>
@@ -9225,7 +9248,7 @@
         <v>8</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>320</v>
@@ -9302,7 +9325,7 @@
         <v>8</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L36" s="86" t="s">
         <v>320</v>
@@ -9379,7 +9402,7 @@
         <v>8</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>320</v>
@@ -9456,7 +9479,7 @@
         <v>8</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L38" s="86" t="s">
         <v>320</v>
@@ -9533,7 +9556,7 @@
         <v>8</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>320</v>
@@ -9610,7 +9633,7 @@
         <v>8</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L40" s="86" t="s">
         <v>320</v>
@@ -9687,7 +9710,7 @@
         <v>8</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>320</v>
@@ -9764,7 +9787,7 @@
         <v>8</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L42" s="86" t="s">
         <v>320</v>
@@ -9841,7 +9864,7 @@
         <v>8</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>320</v>
@@ -9918,7 +9941,7 @@
         <v>8</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L44" s="86" t="s">
         <v>320</v>
@@ -9995,7 +10018,7 @@
         <v>8</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>320</v>
@@ -10072,7 +10095,7 @@
         <v>8</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L46" s="86" t="s">
         <v>320</v>
@@ -10149,7 +10172,7 @@
         <v>8</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>320</v>
@@ -10226,7 +10249,7 @@
         <v>8</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L48" s="86" t="s">
         <v>320</v>
@@ -10303,7 +10326,7 @@
         <v>8</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>320</v>
@@ -10380,7 +10403,7 @@
         <v>8</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L50" s="86" t="s">
         <v>320</v>
@@ -10457,7 +10480,7 @@
         <v>8</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>320</v>
@@ -10534,7 +10557,7 @@
         <v>8</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L52" s="86" t="s">
         <v>320</v>
@@ -10611,7 +10634,7 @@
         <v>8</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>320</v>
@@ -10688,7 +10711,7 @@
         <v>8</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L54" s="86" t="s">
         <v>320</v>
@@ -10765,7 +10788,7 @@
         <v>8</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>320</v>
@@ -10788,7 +10811,9 @@
       </c>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
+      <c r="T55" s="1" t="s">
+        <v>541</v>
+      </c>
       <c r="U55" s="1" t="str">
         <f t="shared" si="4"/>
         <v>d-dip-mqap01-nic</v>
@@ -10842,7 +10867,7 @@
         <v>8</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L56" s="86" t="s">
         <v>320</v>
@@ -10919,7 +10944,7 @@
         <v>8</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>320</v>
@@ -10940,7 +10965,10 @@
       <c r="Q57" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="R57" s="1"/>
+      <c r="R57" s="1" cm="1">
+        <f t="array" aca="1" ref="R57" ca="1">+R56:TL57</f>
+        <v>0</v>
+      </c>
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1" t="str">
@@ -10996,7 +11024,7 @@
         <v>8</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L58" s="86" t="s">
         <v>320</v>
@@ -11073,7 +11101,7 @@
         <v>8</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>320</v>
@@ -11150,7 +11178,7 @@
         <v>8</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L60" s="86" t="s">
         <v>320</v>
@@ -11227,7 +11255,7 @@
         <v>8</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>320</v>
@@ -11303,7 +11331,7 @@
         <v>8</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L62" s="86" t="s">
         <v>320</v>
@@ -11380,7 +11408,7 @@
         <v>8</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>320</v>
@@ -11457,7 +11485,7 @@
         <v>8</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L64" s="86" t="s">
         <v>320</v>
@@ -11534,7 +11562,7 @@
         <v>8</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>320</v>
@@ -11611,7 +11639,7 @@
         <v>8</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L66" s="86" t="s">
         <v>320</v>
@@ -11688,7 +11716,7 @@
         <v>8</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>320</v>
@@ -11765,7 +11793,7 @@
         <v>8</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L68" s="86" t="s">
         <v>320</v>
@@ -11842,7 +11870,7 @@
         <v>8</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>320</v>
@@ -11919,7 +11947,7 @@
         <v>8</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L70" s="86" t="s">
         <v>320</v>
@@ -11971,7 +11999,7 @@
         <v>82</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>337</v>
@@ -11995,16 +12023,16 @@
         <v>8</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>320</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>508</v>
+        <v>328</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="O71" s="1" t="str">
         <f>SUBSTITUTE(F71,"hazr-","")&amp;"-osdisk"</f>
@@ -12047,19 +12075,19 @@
         <v>82</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F72" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>521</v>
       </c>
       <c r="H72" s="87" t="s">
         <v>336</v>
@@ -12071,7 +12099,7 @@
         <v>8</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L72" s="86" t="s">
         <v>320</v>
@@ -12093,10 +12121,10 @@
         <v>501</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="T72" s="1"/>
       <c r="U72" s="1" t="str">
@@ -12127,19 +12155,19 @@
         <v>82</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F73" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="H73" s="87" t="s">
         <v>336</v>
@@ -12151,7 +12179,7 @@
         <v>8</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L73" s="86" t="s">
         <v>321</v>
@@ -12173,10 +12201,10 @@
         <v>501</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="T73" s="1"/>
       <c r="U73" s="1" t="str">
@@ -12207,19 +12235,19 @@
         <v>82</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F74" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="H74" s="87" t="s">
         <v>336</v>
@@ -12231,7 +12259,7 @@
         <v>8</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L74" s="86" t="s">
         <v>320</v>
@@ -12253,10 +12281,10 @@
         <v>501</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T74" s="1"/>
       <c r="U74" s="1" t="str">
@@ -12287,19 +12315,19 @@
         <v>82</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F75" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="H75" s="87" t="s">
         <v>336</v>
@@ -12311,7 +12339,7 @@
         <v>8</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L75" s="86" t="s">
         <v>321</v>
@@ -12333,10 +12361,10 @@
         <v>501</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="S75" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T75" s="1"/>
       <c r="U75" s="1" t="str">
@@ -12367,19 +12395,19 @@
         <v>82</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F76" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="H76" s="87" t="s">
         <v>336</v>
@@ -12391,7 +12419,7 @@
         <v>8</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>322</v>
+        <v>542</v>
       </c>
       <c r="L76" s="86" t="s">
         <v>320</v>
@@ -12413,10 +12441,10 @@
         <v>501</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="T76" s="1"/>
       <c r="U76" s="1" t="str">
@@ -12440,6 +12468,85 @@
       </c>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="H77" s="87" t="s">
+        <v>336</v>
+      </c>
+      <c r="I77" s="1">
+        <v>2</v>
+      </c>
+      <c r="J77" s="1">
+        <v>8</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="L77" s="86" t="s">
+        <v>321</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="O77" s="1" t="str">
+        <f t="shared" ref="O77" si="9">SUBSTITUTE(F77,"hazr-","")&amp;"-osdisk"</f>
+        <v>temp-vm06-osdisk</v>
+      </c>
+      <c r="P77" s="1">
+        <v>65</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="S77" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1" t="str">
+        <f t="shared" ref="U77" si="10">SUBSTITUTE(F77,"hazr-","")&amp;"-nic"</f>
+        <v>temp-vm06-nic</v>
+      </c>
+      <c r="V77" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W77" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="X77" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y77" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="Z77" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA77" s="1"/>
+      <c r="AB77" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12498,7 +12605,7 @@
         <v>82</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>101</v>

--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6089C657-7335-4D4D-B720-55718B98CDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC150232-794B-4FE0-9DB4-2B94C3AFBAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET_DEV" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="LB_DEV_Probe" sheetId="10" r:id="rId8"/>
     <sheet name="LB_DEV_Rule" sheetId="11" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2442" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="524">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3513,6 +3513,14 @@
   </si>
   <si>
     <t>hazr-d-bdp-crkap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>temp-zenithcloud-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4284,6 +4292,36 @@
   <dxfs count="33">
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -4424,41 +4462,11 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -4863,17 +4871,17 @@
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="11">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="1"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="0"/>
-    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="2"/>
+    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="4"/>
     <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="3"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="6"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="5"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5962,7 +5970,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF73"/>
+  <dimension ref="A1:AF75"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -12397,7 +12405,7 @@
         <v>180</v>
       </c>
       <c r="Z72" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AA72" s="1" t="b">
         <v>1</v>
@@ -12501,6 +12509,11 @@
       </c>
       <c r="AE73" s="1"/>
       <c r="AF73" s="1"/>
+    </row>
+    <row r="75" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>522</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -18704,12 +18717,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18857,15 +18867,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18889,17 +18910,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC150232-794B-4FE0-9DB4-2B94C3AFBAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264487F8-6293-4259-B865-482A9C89D178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="523">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3505,10 +3505,6 @@
   </si>
   <si>
     <t>10.156.143.11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>temp-zentihcloud-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -12405,7 +12401,7 @@
         <v>180</v>
       </c>
       <c r="Z72" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AA72" s="1" t="b">
         <v>1</v>
@@ -12493,7 +12489,7 @@
         <v>180</v>
       </c>
       <c r="Z73" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA73" s="1" t="b">
         <v>1</v>
@@ -12512,7 +12508,7 @@
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -16098,7 +16094,7 @@
         <v>24</v>
       </c>
       <c r="F69" s="90" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G69" s="90" t="str">
         <f>SUBSTITUTE($F69,"hazr-","")&amp;"-disk01"</f>
@@ -18717,9 +18713,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18867,26 +18866,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18910,9 +18898,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260320_샘플_리소스배포_정리.xlsx
+++ b/서버정보/20260320_샘플_리소스배포_정리.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264487F8-6293-4259-B865-482A9C89D178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10CA891-A9A0-4EA8-8803-52CE067859EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VNET_DEV" sheetId="4" r:id="rId1"/>
-    <sheet name="RG_DEV" sheetId="5" r:id="rId2"/>
-    <sheet name="VM_DEV" sheetId="1" r:id="rId3"/>
-    <sheet name="VM_DEV_Datadisk" sheetId="14" r:id="rId4"/>
-    <sheet name="NSG_DEV" sheetId="2" r:id="rId5"/>
-    <sheet name="NSG_DEV_Rule" sheetId="3" r:id="rId6"/>
-    <sheet name="LB_DEV" sheetId="6" r:id="rId7"/>
-    <sheet name="LB_DEV_Probe" sheetId="10" r:id="rId8"/>
-    <sheet name="LB_DEV_Rule" sheetId="11" r:id="rId9"/>
+    <sheet name="VNET" sheetId="4" r:id="rId1"/>
+    <sheet name="RG" sheetId="5" r:id="rId2"/>
+    <sheet name="VM" sheetId="1" r:id="rId3"/>
+    <sheet name="VM_Datadisk" sheetId="14" r:id="rId4"/>
+    <sheet name="NSG" sheetId="2" r:id="rId5"/>
+    <sheet name="NSG_Rule" sheetId="3" r:id="rId6"/>
+    <sheet name="LB" sheetId="6" r:id="rId7"/>
+    <sheet name="LB_Probe" sheetId="10" r:id="rId8"/>
+    <sheet name="LB_Rule" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="522">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3509,10 +3509,6 @@
   </si>
   <si>
     <t>hazr-d-bdp-crkap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -5966,7 +5962,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF75"/>
+  <dimension ref="A1:AF73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -12401,7 +12397,7 @@
         <v>180</v>
       </c>
       <c r="Z72" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AA72" s="1" t="b">
         <v>1</v>
@@ -12489,7 +12485,7 @@
         <v>180</v>
       </c>
       <c r="Z73" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AA73" s="1" t="b">
         <v>1</v>
@@ -12505,11 +12501,6 @@
       </c>
       <c r="AE73" s="1"/>
       <c r="AF73" s="1"/>
-    </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>521</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12527,7 +12518,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F281E7-0665-4BB7-80DB-4208A01A998B}">
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" style="91" customWidth="1"/>
@@ -12541,10 +12532,10 @@
     <col min="9" max="9" width="12.25" style="91" customWidth="1"/>
     <col min="10" max="10" width="21.5" style="91" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="91" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="14.125" style="91" customWidth="1"/>
+    <col min="12" max="17" width="14.125" style="91" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="92"/>
       <c r="B1" s="93" t="s">
         <v>0</v>
@@ -12586,16 +12577,19 @@
         <v>506</v>
       </c>
       <c r="O1" s="88" t="s">
+        <v>511</v>
+      </c>
+      <c r="P1" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="P1" s="88" t="s">
+      <c r="Q1" s="88" t="s">
         <v>505</v>
       </c>
-      <c r="Q1" s="55" t="s">
+      <c r="R1" s="55" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="94"/>
       <c r="B2" s="89" t="s">
         <v>81</v>
@@ -12640,14 +12634,17 @@
         <v>507</v>
       </c>
       <c r="O2" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P2" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P2" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="87"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q2" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" s="87"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="96"/>
       <c r="B3" s="90" t="s">
         <v>81</v>
@@ -12692,14 +12689,17 @@
         <v>507</v>
       </c>
       <c r="O3" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P3" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P3" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="56"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q3" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" s="56"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="94"/>
       <c r="B4" s="89" t="s">
         <v>81</v>
@@ -12744,14 +12744,17 @@
         <v>507</v>
       </c>
       <c r="O4" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P4" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="87"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q4" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="87"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="96"/>
       <c r="B5" s="90" t="s">
         <v>81</v>
@@ -12796,14 +12799,17 @@
         <v>507</v>
       </c>
       <c r="O5" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P5" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P5" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="56"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q5" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" s="56"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="94"/>
       <c r="B6" s="89" t="s">
         <v>81</v>
@@ -12848,14 +12854,17 @@
         <v>507</v>
       </c>
       <c r="O6" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P6" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P6" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="87"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q6" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="87"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="96"/>
       <c r="B7" s="90" t="s">
         <v>81</v>
@@ -12900,14 +12909,17 @@
         <v>507</v>
       </c>
       <c r="O7" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P7" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P7" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="56"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q7" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="56"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="94"/>
       <c r="B8" s="89" t="s">
         <v>81</v>
@@ -12952,14 +12964,17 @@
         <v>507</v>
       </c>
       <c r="O8" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P8" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P8" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="87"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q8" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="87"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="94"/>
       <c r="B9" s="90" t="s">
         <v>81</v>
@@ -13004,14 +13019,17 @@
         <v>507</v>
       </c>
       <c r="O9" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P9" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P9" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="56"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q9" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="56"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="96"/>
       <c r="B10" s="89" t="s">
         <v>81</v>
@@ -13056,14 +13074,17 @@
         <v>507</v>
       </c>
       <c r="O10" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P10" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P10" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="87"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q10" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="87"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="94"/>
       <c r="B11" s="90" t="s">
         <v>81</v>
@@ -13108,14 +13129,17 @@
         <v>507</v>
       </c>
       <c r="O11" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P11" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P11" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="56"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q11" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="56"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="96"/>
       <c r="B12" s="89" t="s">
         <v>81</v>
@@ -13160,14 +13184,17 @@
         <v>507</v>
       </c>
       <c r="O12" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P12" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P12" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="87"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q12" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="87"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="94"/>
       <c r="B13" s="90" t="s">
         <v>81</v>
@@ -13212,14 +13239,17 @@
         <v>507</v>
       </c>
       <c r="O13" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P13" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P13" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="56"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q13" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" s="56"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="96"/>
       <c r="B14" s="89" t="s">
         <v>81</v>
@@ -13264,14 +13294,17 @@
         <v>507</v>
       </c>
       <c r="O14" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P14" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P14" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="87"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q14" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="87"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="94"/>
       <c r="B15" s="90" t="s">
         <v>81</v>
@@ -13316,14 +13349,17 @@
         <v>507</v>
       </c>
       <c r="O15" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P15" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P15" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="56"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q15" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" s="56"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="96"/>
       <c r="B16" s="89" t="s">
         <v>81</v>
@@ -13368,14 +13404,17 @@
         <v>507</v>
       </c>
       <c r="O16" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P16" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P16" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="87"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q16" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" s="87"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="94"/>
       <c r="B17" s="90" t="s">
         <v>81</v>
@@ -13420,14 +13459,17 @@
         <v>507</v>
       </c>
       <c r="O17" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P17" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P17" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="56"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q17" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" s="56"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="94"/>
       <c r="B18" s="89" t="s">
         <v>81</v>
@@ -13472,14 +13514,17 @@
         <v>507</v>
       </c>
       <c r="O18" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P18" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P18" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="87"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q18" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" s="87"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="96"/>
       <c r="B19" s="90" t="s">
         <v>81</v>
@@ -13524,14 +13569,17 @@
         <v>507</v>
       </c>
       <c r="O19" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P19" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P19" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="56"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q19" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" s="56"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="94"/>
       <c r="B20" s="89" t="s">
         <v>81</v>
@@ -13576,14 +13624,17 @@
         <v>507</v>
       </c>
       <c r="O20" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P20" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P20" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="87"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q20" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="87"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="96"/>
       <c r="B21" s="90" t="s">
         <v>81</v>
@@ -13628,14 +13679,17 @@
         <v>507</v>
       </c>
       <c r="O21" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P21" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P21" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="56"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q21" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" s="56"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="94"/>
       <c r="B22" s="89" t="s">
         <v>81</v>
@@ -13680,14 +13734,17 @@
         <v>507</v>
       </c>
       <c r="O22" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P22" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P22" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="87"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q22" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" s="87"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="96"/>
       <c r="B23" s="90" t="s">
         <v>81</v>
@@ -13732,14 +13789,17 @@
         <v>507</v>
       </c>
       <c r="O23" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P23" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P23" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="56"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q23" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" s="56"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="94"/>
       <c r="B24" s="89" t="s">
         <v>81</v>
@@ -13784,14 +13844,17 @@
         <v>507</v>
       </c>
       <c r="O24" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P24" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P24" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="87"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q24" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" s="87"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="96"/>
       <c r="B25" s="90" t="s">
         <v>81</v>
@@ -13836,14 +13899,17 @@
         <v>507</v>
       </c>
       <c r="O25" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P25" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P25" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="56"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q25" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" s="56"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="94"/>
       <c r="B26" s="89" t="s">
         <v>81</v>
@@ -13888,14 +13954,17 @@
         <v>507</v>
       </c>
       <c r="O26" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P26" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P26" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="87"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q26" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" s="87"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="94"/>
       <c r="B27" s="90" t="s">
         <v>81</v>
@@ -13940,14 +14009,17 @@
         <v>507</v>
       </c>
       <c r="O27" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P27" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P27" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="56"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q27" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" s="56"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="96"/>
       <c r="B28" s="89" t="s">
         <v>81</v>
@@ -13992,14 +14064,17 @@
         <v>507</v>
       </c>
       <c r="O28" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P28" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P28" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" s="87"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q28" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" s="87"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="94"/>
       <c r="B29" s="90" t="s">
         <v>81</v>
@@ -14044,14 +14119,17 @@
         <v>507</v>
       </c>
       <c r="O29" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P29" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P29" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="56"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q29" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" s="56"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="96"/>
       <c r="B30" s="89" t="s">
         <v>81</v>
@@ -14096,14 +14174,17 @@
         <v>507</v>
       </c>
       <c r="O30" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P30" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P30" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="87"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q30" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" s="87"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="94"/>
       <c r="B31" s="90" t="s">
         <v>81</v>
@@ -14148,14 +14229,17 @@
         <v>507</v>
       </c>
       <c r="O31" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P31" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P31" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="56"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q31" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" s="56"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="96"/>
       <c r="B32" s="89" t="s">
         <v>81</v>
@@ -14200,14 +14284,17 @@
         <v>507</v>
       </c>
       <c r="O32" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P32" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P32" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="87"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q32" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" s="87"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="94"/>
       <c r="B33" s="90" t="s">
         <v>81</v>
@@ -14252,14 +14339,17 @@
         <v>507</v>
       </c>
       <c r="O33" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P33" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P33" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="56"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q33" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" s="56"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="96"/>
       <c r="B34" s="89" t="s">
         <v>81</v>
@@ -14304,14 +14394,17 @@
         <v>507</v>
       </c>
       <c r="O34" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P34" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P34" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="87"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q34" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" s="87"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="94"/>
       <c r="B35" s="90" t="s">
         <v>81</v>
@@ -14356,14 +14449,17 @@
         <v>507</v>
       </c>
       <c r="O35" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P35" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P35" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="56"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q35" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" s="56"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="94"/>
       <c r="B36" s="89" t="s">
         <v>81</v>
@@ -14408,14 +14504,17 @@
         <v>507</v>
       </c>
       <c r="O36" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P36" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P36" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="87"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q36" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" s="87"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="96"/>
       <c r="B37" s="90" t="s">
         <v>81</v>
@@ -14460,14 +14559,17 @@
         <v>507</v>
       </c>
       <c r="O37" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P37" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P37" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="56"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q37" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" s="56"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="94"/>
       <c r="B38" s="89" t="s">
         <v>81</v>
@@ -14512,14 +14614,17 @@
         <v>507</v>
       </c>
       <c r="O38" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P38" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P38" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q38" s="87"/>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q38" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" s="87"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="96"/>
       <c r="B39" s="90" t="s">
         <v>81</v>
@@ -14564,14 +14669,17 @@
         <v>507</v>
       </c>
       <c r="O39" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P39" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P39" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q39" s="56"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q39" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" s="56"/>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="94"/>
       <c r="B40" s="89" t="s">
         <v>81</v>
@@ -14616,14 +14724,17 @@
         <v>507</v>
       </c>
       <c r="O40" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P40" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P40" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="87"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q40" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" s="87"/>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="96"/>
       <c r="B41" s="90" t="s">
         <v>81</v>
@@ -14668,14 +14779,17 @@
         <v>507</v>
       </c>
       <c r="O41" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P41" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P41" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="56"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q41" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" s="56"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="94"/>
       <c r="B42" s="89" t="s">
         <v>81</v>
@@ -14720,14 +14834,17 @@
         <v>507</v>
       </c>
       <c r="O42" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P42" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P42" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="87"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q42" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R42" s="87"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="96"/>
       <c r="B43" s="90" t="s">
         <v>81</v>
@@ -14772,14 +14889,17 @@
         <v>507</v>
       </c>
       <c r="O43" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P43" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P43" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q43" s="56"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q43" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R43" s="56"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="94"/>
       <c r="B44" s="89" t="s">
         <v>81</v>
@@ -14824,14 +14944,17 @@
         <v>507</v>
       </c>
       <c r="O44" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P44" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P44" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q44" s="87"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q44" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R44" s="87"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="94"/>
       <c r="B45" s="90" t="s">
         <v>81</v>
@@ -14876,14 +14999,17 @@
         <v>507</v>
       </c>
       <c r="O45" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P45" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P45" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q45" s="56"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q45" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R45" s="56"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="96"/>
       <c r="B46" s="89" t="s">
         <v>81</v>
@@ -14928,14 +15054,17 @@
         <v>507</v>
       </c>
       <c r="O46" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P46" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P46" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="87"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q46" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R46" s="87"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="94"/>
       <c r="B47" s="90" t="s">
         <v>81</v>
@@ -14980,14 +15109,17 @@
         <v>507</v>
       </c>
       <c r="O47" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P47" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P47" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47" s="56"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q47" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R47" s="56"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="96"/>
       <c r="B48" s="89" t="s">
         <v>81</v>
@@ -15032,14 +15164,17 @@
         <v>507</v>
       </c>
       <c r="O48" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P48" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P48" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="87"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q48" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" s="87"/>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="94"/>
       <c r="B49" s="90" t="s">
         <v>81</v>
@@ -15084,14 +15219,17 @@
         <v>507</v>
       </c>
       <c r="O49" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P49" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P49" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" s="56"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q49" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R49" s="56"/>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="96"/>
       <c r="B50" s="89" t="s">
         <v>81</v>
@@ -15136,14 +15274,17 @@
         <v>507</v>
       </c>
       <c r="O50" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P50" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P50" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="87"/>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q50" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R50" s="87"/>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="94"/>
       <c r="B51" s="90" t="s">
         <v>81</v>
@@ -15188,14 +15329,17 @@
         <v>507</v>
       </c>
       <c r="O51" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P51" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P51" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q51" s="56"/>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q51" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R51" s="56"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="96"/>
       <c r="B52" s="89" t="s">
         <v>81</v>
@@ -15240,14 +15384,17 @@
         <v>507</v>
       </c>
       <c r="O52" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P52" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P52" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="87"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q52" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R52" s="87"/>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="94"/>
       <c r="B53" s="90" t="s">
         <v>81</v>
@@ -15292,14 +15439,17 @@
         <v>507</v>
       </c>
       <c r="O53" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P53" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P53" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q53" s="56"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q53" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R53" s="56"/>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="94"/>
       <c r="B54" s="89" t="s">
         <v>81</v>
@@ -15344,14 +15494,17 @@
         <v>507</v>
       </c>
       <c r="O54" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P54" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P54" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="87"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q54" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R54" s="87"/>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="96"/>
       <c r="B55" s="90" t="s">
         <v>81</v>
@@ -15396,14 +15549,17 @@
         <v>507</v>
       </c>
       <c r="O55" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P55" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P55" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q55" s="56"/>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q55" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R55" s="56"/>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="94"/>
       <c r="B56" s="89" t="s">
         <v>81</v>
@@ -15448,14 +15604,17 @@
         <v>507</v>
       </c>
       <c r="O56" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P56" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P56" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q56" s="87"/>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q56" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R56" s="87"/>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="96"/>
       <c r="B57" s="90" t="s">
         <v>81</v>
@@ -15500,14 +15659,17 @@
         <v>507</v>
       </c>
       <c r="O57" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P57" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P57" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="56"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q57" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R57" s="56"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="94"/>
       <c r="B58" s="89" t="s">
         <v>81</v>
@@ -15552,14 +15714,17 @@
         <v>507</v>
       </c>
       <c r="O58" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P58" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P58" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q58" s="87"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q58" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R58" s="87"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="96"/>
       <c r="B59" s="90" t="s">
         <v>81</v>
@@ -15604,14 +15769,17 @@
         <v>507</v>
       </c>
       <c r="O59" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P59" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P59" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q59" s="56"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q59" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R59" s="56"/>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="94"/>
       <c r="B60" s="89" t="s">
         <v>81</v>
@@ -15656,14 +15824,17 @@
         <v>507</v>
       </c>
       <c r="O60" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P60" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P60" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q60" s="87"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q60" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R60" s="87"/>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="96"/>
       <c r="B61" s="90" t="s">
         <v>81</v>
@@ -15708,14 +15879,17 @@
         <v>507</v>
       </c>
       <c r="O61" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P61" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P61" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="56"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q61" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R61" s="56"/>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="94"/>
       <c r="B62" s="89" t="s">
         <v>81</v>
@@ -15759,14 +15933,17 @@
         <v>507</v>
       </c>
       <c r="O62" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P62" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P62" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="87"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q62" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R62" s="87"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="94"/>
       <c r="B63" s="90" t="s">
         <v>81</v>
@@ -15811,14 +15988,17 @@
         <v>507</v>
       </c>
       <c r="O63" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P63" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P63" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="56"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q63" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R63" s="56"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="96"/>
       <c r="B64" s="89" t="s">
         <v>81</v>
@@ -15863,14 +16043,17 @@
         <v>507</v>
       </c>
       <c r="O64" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P64" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P64" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="87"/>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q64" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R64" s="87"/>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="94"/>
       <c r="B65" s="90" t="s">
         <v>81</v>
@@ -15915,14 +16098,17 @@
         <v>507</v>
       </c>
       <c r="O65" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P65" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P65" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="56"/>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q65" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R65" s="56"/>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="96"/>
       <c r="B66" s="89" t="s">
         <v>81</v>
@@ -15967,14 +16153,17 @@
         <v>507</v>
       </c>
       <c r="O66" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P66" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P66" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q66" s="87"/>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q66" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R66" s="87"/>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="94"/>
       <c r="B67" s="90" t="s">
         <v>81</v>
@@ -16019,14 +16208,17 @@
         <v>507</v>
       </c>
       <c r="O67" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P67" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P67" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="56"/>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q67" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R67" s="56"/>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="96"/>
       <c r="B68" s="89" t="s">
         <v>81</v>
@@ -16071,14 +16263,17 @@
         <v>507</v>
       </c>
       <c r="O68" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P68" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P68" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="87"/>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q68" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R68" s="87"/>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="94"/>
       <c r="B69" s="90" t="s">
         <v>81</v>
@@ -16123,14 +16318,17 @@
         <v>507</v>
       </c>
       <c r="O69" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P69" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P69" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="56"/>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q69" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R69" s="56"/>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="96"/>
       <c r="B70" s="89" t="s">
         <v>81</v>
@@ -16175,14 +16373,17 @@
         <v>507</v>
       </c>
       <c r="O70" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P70" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P70" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="87"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q70" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R70" s="87"/>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="94"/>
       <c r="B71" s="90" t="s">
         <v>81</v>
@@ -16224,14 +16425,17 @@
         <v>514</v>
       </c>
       <c r="O71" s="90" t="s">
-        <v>514</v>
+        <v>173</v>
       </c>
       <c r="P71" s="90" t="s">
         <v>514</v>
       </c>
-      <c r="Q71" s="56"/>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q71" s="90" t="s">
+        <v>514</v>
+      </c>
+      <c r="R71" s="56"/>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="98"/>
       <c r="B72" s="89" t="s">
         <v>81</v>
@@ -16275,14 +16479,17 @@
         <v>507</v>
       </c>
       <c r="O72" s="89" t="s">
+        <v>173</v>
+      </c>
+      <c r="P72" s="89" t="s">
         <v>504</v>
       </c>
-      <c r="P72" s="89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q72" s="87"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q72" s="89" t="b">
+        <v>1</v>
+      </c>
+      <c r="R72" s="87"/>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="98"/>
       <c r="B73" s="90" t="s">
         <v>81</v>
@@ -16326,12 +16533,15 @@
         <v>507</v>
       </c>
       <c r="O73" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="P73" s="90" t="s">
         <v>504</v>
       </c>
-      <c r="P73" s="90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="56"/>
+      <c r="Q73" s="90" t="b">
+        <v>1</v>
+      </c>
+      <c r="R73" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -18713,12 +18923,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18866,15 +19073,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18898,17 +19116,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>